--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -399,7 +399,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11106150"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -429,7 +429,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10506075"/>
+    <ext cx="10125075" cy="10277475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -459,7 +459,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11106150"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -549,7 +549,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10696575"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -609,7 +609,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10544175"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 03:27</t>
+          <t>2026-07-05 06:11</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1173,174 +1173,249 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Twins offense vs New York Yankees defense</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>Minnesota Twins offense vs New York Yankees defense</t>
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B71" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D71" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E71" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F71" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G71" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H71" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I71" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J71" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K71" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L71" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M71" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N71" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O71" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P71" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q71" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A71" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>4.776</v>
+        <v>7.776</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E72" s="31" t="n">
-        <v>5.933</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G72" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J72" s="32" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L72" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M72" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N72" s="31" t="n">
-        <v>4.65</v>
+        <v>10</v>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>4.633</v>
+        <v>12</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>3.744</v>
+        <v>7.609</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>7.776</v>
+        <v>1.061</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>8.667</v>
+        <v>0.5</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -1394,28 +1469,28 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>10.667</v>
+        <v>1.5</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>7.609</v>
+        <v>0.913</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>1.061</v>
+        <v>8.939</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -1469,319 +1544,319 @@
         </is>
       </c>
       <c r="O74" s="31" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>0.913</v>
+        <v>8.435</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>8.939</v>
+        <v>0.714</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="D75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J75" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>9.667</v>
+        <v>0.633</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>8.435</v>
+        <v>0.514</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="C76" s="31" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D76" s="31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E76" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F76" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J76" s="32" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M76" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N76" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O76" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Minnesota Twins defense</t>
+        </is>
+      </c>
+    </row>
     <row r="78">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Minnesota Twins defense</t>
+      <c r="A78" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F78" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G78" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H78" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I78" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J78" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K78" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L78" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M78" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N78" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O78" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P78" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q78" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B79" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C79" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D79" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E79" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F79" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G79" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H79" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I79" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J79" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K79" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L79" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M79" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N79" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O79" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P79" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q79" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A79" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="n">
+        <v>4.734</v>
+      </c>
+      <c r="C79" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H79" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O79" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P79" s="31" t="n">
+        <v>5.117</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>4.744</v>
+        <v>8.109</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D80" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E80" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F80" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H80" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>9.5</v>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L80" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M80" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N80" s="31" t="n">
-        <v>5.6</v>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>5.767</v>
+        <v>9.5</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>5.132</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.109</v>
+        <v>1.413</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>8.333</v>
+        <v>0.5</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -1835,28 +1910,28 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>0.918</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>1.413</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>0.333</v>
+        <v>10.5</v>
       </c>
       <c r="D82" s="31" t="inlineStr">
         <is>
@@ -1910,146 +1985,71 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>1.667</v>
+        <v>12.5</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>0.918</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B83" s="31" t="n">
-        <v>9.130000000000001</v>
+        <v>0.622</v>
       </c>
       <c r="C83" s="31" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="D83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.333</v>
+      </c>
+      <c r="D83" s="31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E83" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H83" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J83" s="35" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L83" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N83" s="31" t="n">
+        <v>0.45</v>
       </c>
       <c r="O83" s="31" t="n">
-        <v>11.667</v>
+        <v>0.633</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>8.265000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B84" s="31" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="C84" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D84" s="31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E84" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H84" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I84" s="31" t="inlineStr"/>
-      <c r="J84" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K84" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L84" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N84" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O84" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P84" s="31" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -2186,51 +2186,51 @@
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.908</v>
+        <v>4.883</v>
       </c>
       <c r="C71" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E71" s="31" t="n">
         <v>5.067</v>
       </c>
-      <c r="D71" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>5.2</v>
-      </c>
       <c r="F71" s="31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G71" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
+        <v>4.2</v>
+      </c>
+      <c r="H71" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>6th</t>
         </is>
       </c>
       <c r="K71" s="31" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>3.867</v>
+        <v>3.933</v>
       </c>
       <c r="N71" s="31" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.367</v>
+        <v>4.167</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.127</v>
+        <v>4.112</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>7.792</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>8.5</v>
+        <v>8.333</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>10.333</v>
+        <v>10</v>
       </c>
       <c r="P72" s="31" t="n">
         <v>7.939</v>
@@ -2323,7 +2323,7 @@
         <v>1.354</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>1.75</v>
+        <v>1.333</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>9.208</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>9</v>
+        <v>9.667</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -2470,22 +2470,22 @@
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>0.581</v>
+        <v>0.587</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D75" s="31" t="n">
         <v>0.4</v>
       </c>
       <c r="E75" s="31" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="F75" s="31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G75" s="31" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H75" s="33" t="inlineStr">
         <is>
@@ -2495,26 +2495,26 @@
       <c r="I75" s="31" t="inlineStr"/>
       <c r="J75" s="35" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K75" s="31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="N75" s="31" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>0.367</v>
+        <v>0.4</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>0.355</v>
+        <v>0.364</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
@@ -2623,36 +2623,36 @@
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>3.949</v>
+        <v>3.913</v>
       </c>
       <c r="C79" s="31" t="n">
         <v>3.7</v>
       </c>
       <c r="D79" s="31" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="E79" s="31" t="n">
-        <v>4.067</v>
+        <v>3.867</v>
       </c>
       <c r="F79" s="31" t="n">
         <v>4</v>
       </c>
       <c r="G79" s="31" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="H79" s="33" t="inlineStr">
         <is>
-          <t>13th</t>
+          <t>20th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
       <c r="J79" s="35" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="K79" s="31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L79" s="31" t="n">
         <v>3.3</v>
@@ -2661,13 +2661,13 @@
         <v>3.467</v>
       </c>
       <c r="N79" s="31" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="O79" s="31" t="n">
         <v>4.333</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.724</v>
+        <v>4.675</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>7.735</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>9.667</v>
+        <v>11.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="P80" s="31" t="n">
         <v>7.854</v>
@@ -2760,7 +2760,7 @@
         <v>0.959</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="P81" s="31" t="n">
         <v>1.062</v>
@@ -2835,7 +2835,7 @@
         <v>8</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>12.667</v>
+        <v>13.5</v>
       </c>
       <c r="D82" s="31" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="P82" s="31" t="n">
         <v>7.938</v>
@@ -2907,13 +2907,13 @@
         </is>
       </c>
       <c r="B83" s="31" t="n">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="C83" s="31" t="n">
-        <v>0.233</v>
+        <v>0.2</v>
       </c>
       <c r="D83" s="31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E83" s="31" t="n">
         <v>0.267</v>
@@ -2924,19 +2924,19 @@
       <c r="G83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
+      <c r="H83" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr"/>
       <c r="J83" s="35" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="K83" s="31" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L83" s="31" t="n">
         <v>0.3</v>
@@ -2951,7 +2951,7 @@
         <v>0.533</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>0.541</v>
+        <v>0.533</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
         <is>
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.64</v>
+        <v>4.618</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.167</v>
+        <v>5.233</v>
       </c>
       <c r="D71" s="31" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="E71" s="31" t="n">
         <v>4.933</v>
@@ -3105,11 +3105,11 @@
         <v>4.7</v>
       </c>
       <c r="G71" s="31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H71" s="35" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr">
@@ -3126,19 +3126,19 @@
         <v>6.4</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>5.2</v>
+        <v>5.067</v>
       </c>
       <c r="N71" s="31" t="n">
         <v>4.6</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.767</v>
+        <v>4.833</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.816</v>
+        <v>4.792</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>7.826</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>7.75</v>
+        <v>8.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>6.333</v>
+        <v>7</v>
       </c>
       <c r="P72" s="31" t="n">
         <v>7.896</v>
@@ -3231,7 +3231,7 @@
         <v>1.109</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="P73" s="31" t="n">
         <v>1.354</v>
@@ -3306,7 +3306,7 @@
         <v>8.196</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>9</v>
+        <v>9.667</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="O74" s="31" t="n">
-        <v>6.667</v>
+        <v>6.5</v>
       </c>
       <c r="P74" s="31" t="n">
         <v>7.708</v>
@@ -3378,51 +3378,51 @@
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>0.556</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="D75" s="31" t="n">
         <v>0.8</v>
       </c>
       <c r="E75" s="31" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="F75" s="31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G75" s="31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H75" s="35" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="I75" s="31" t="inlineStr"/>
       <c r="J75" s="35" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="K75" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M75" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L75" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.133</v>
-      </c>
       <c r="N75" s="31" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>0.333</v>
+        <v>0.367</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>0.44</v>
+        <v>0.447</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
@@ -3531,26 +3531,26 @@
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>5.263</v>
+        <v>5.195</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5.733</v>
+        <v>5.533</v>
       </c>
       <c r="D79" s="31" t="n">
-        <v>7.05</v>
+        <v>6.6</v>
       </c>
       <c r="E79" s="31" t="n">
-        <v>7.667</v>
+        <v>7.533</v>
       </c>
       <c r="F79" s="31" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="G79" s="31" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H79" s="35" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
@@ -3560,22 +3560,22 @@
         </is>
       </c>
       <c r="K79" s="31" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="L79" s="31" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="M79" s="31" t="n">
-        <v>5.133</v>
+        <v>5</v>
       </c>
       <c r="N79" s="31" t="n">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>4.467</v>
+        <v>4.267</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.52</v>
+        <v>4.461</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>8.438000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>7.667</v>
+        <v>5.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P80" s="31" t="n">
         <v>8.651999999999999</v>
@@ -3668,7 +3668,7 @@
         <v>1.104</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="P81" s="31" t="n">
         <v>1.043</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>8.75</v>
+        <v>9.333</v>
       </c>
       <c r="P82" s="31" t="n">
         <v>7.739</v>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="B83" s="31" t="n">
-        <v>0.453</v>
+        <v>0.447</v>
       </c>
       <c r="C83" s="31" t="n">
         <v>0.5</v>
@@ -3824,7 +3824,7 @@
         <v>0.7</v>
       </c>
       <c r="E83" s="31" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="F83" s="31" t="n">
         <v>0.4</v>
@@ -3832,9 +3832,9 @@
       <c r="G83" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
+      <c r="H83" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="J83" s="32" t="inlineStr">
         <is>
-          <t>28th</t>
+          <t>26th</t>
         </is>
       </c>
       <c r="K83" s="31" t="n">
@@ -3857,13 +3857,13 @@
         <v>0.733</v>
       </c>
       <c r="N83" s="31" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O83" s="31" t="n">
         <v>0.6</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>0.597</v>
+        <v>0.589</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
         <is>
@@ -4002,26 +4002,26 @@
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>4.577</v>
+        <v>4.595</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>5.5</v>
+        <v>5.667</v>
       </c>
       <c r="D70" s="31" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="E70" s="31" t="n">
-        <v>6.267</v>
+        <v>6.4</v>
       </c>
       <c r="F70" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G70" s="31" t="n">
         <v>6.4</v>
       </c>
-      <c r="G70" s="31" t="n">
-        <v>6.2</v>
-      </c>
       <c r="H70" s="35" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr">
@@ -4029,28 +4029,28 @@
           <t>★★★</t>
         </is>
       </c>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="K70" s="31" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="M70" s="31" t="n">
         <v>6.8</v>
       </c>
       <c r="N70" s="31" t="n">
-        <v>6.55</v>
+        <v>6.65</v>
       </c>
       <c r="O70" s="31" t="n">
         <v>5.733</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>5.256</v>
+        <v>5.266</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>7.234</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>6.667</v>
+        <v>5</v>
       </c>
       <c r="P71" s="31" t="n">
         <v>8.603999999999999</v>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>1.333</v>
+        <v>2</v>
       </c>
       <c r="P72" s="31" t="n">
         <v>1.25</v>
@@ -4218,7 +4218,7 @@
         <v>8.426</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>10.333</v>
+        <v>11.5</v>
       </c>
       <c r="P73" s="31" t="n">
         <v>8.208</v>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>0.573</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C74" s="31" t="n">
         <v>0.5</v>
@@ -4299,7 +4299,7 @@
         <v>0.6</v>
       </c>
       <c r="E74" s="31" t="n">
-        <v>0.6</v>
+        <v>0.467</v>
       </c>
       <c r="F74" s="31" t="n">
         <v>0.3</v>
@@ -4309,17 +4309,13 @@
       </c>
       <c r="H74" s="33" t="inlineStr">
         <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J74" s="32" t="inlineStr">
-        <is>
-          <t>24th</t>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="K74" s="31" t="n">
@@ -4332,13 +4328,13 @@
         <v>1</v>
       </c>
       <c r="N74" s="31" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>1.033</v>
+        <v>0.9</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>0.827</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
@@ -4447,19 +4443,19 @@
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>4.128</v>
+        <v>4.089</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>4.833</v>
+        <v>4.767</v>
       </c>
       <c r="D78" s="31" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="E78" s="31" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F78" s="31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G78" s="31" t="n">
         <v>2.4</v>
@@ -4470,28 +4466,28 @@
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>21st</t>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="K78" s="31" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>5.267</v>
+        <v>4.533</v>
       </c>
       <c r="N78" s="31" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="O78" s="31" t="n">
-        <v>4.733</v>
+        <v>4.467</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>4.795</v>
+        <v>4.747</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
@@ -4509,7 +4505,7 @@
         <v>7.792</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>8.667</v>
+        <v>9</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -4563,7 +4559,7 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P79" s="31" t="n">
         <v>9.319000000000001</v>
@@ -4584,7 +4580,7 @@
         <v>0.896</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>1.333</v>
+        <v>1.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -4638,7 +4634,7 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P80" s="31" t="n">
         <v>1.17</v>
@@ -4659,7 +4655,7 @@
         <v>8.021000000000001</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -4713,7 +4709,7 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="P81" s="31" t="n">
         <v>9.276999999999999</v>
@@ -4731,7 +4727,7 @@
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>0.467</v>
+        <v>0.461</v>
       </c>
       <c r="C82" s="31" t="n">
         <v>0.833</v>
@@ -4750,7 +4746,7 @@
       </c>
       <c r="H82" s="33" t="inlineStr">
         <is>
-          <t>14th</t>
+          <t>17th</t>
         </is>
       </c>
       <c r="I82" s="31" t="inlineStr"/>
@@ -4766,16 +4762,16 @@
         <v>0.5</v>
       </c>
       <c r="M82" s="31" t="n">
-        <v>0.667</v>
+        <v>0.533</v>
       </c>
       <c r="N82" s="31" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O82" s="31" t="n">
         <v>0.533</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>0.52</v>
+        <v>0.513</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
@@ -4914,26 +4910,26 @@
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.689</v>
+        <v>4.733</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>4.367</v>
+        <v>4.467</v>
       </c>
       <c r="D71" s="31" t="n">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="E71" s="31" t="n">
-        <v>5.133</v>
+        <v>5.4</v>
       </c>
       <c r="F71" s="31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G71" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="31" t="n">
-        <v>5.4</v>
-      </c>
       <c r="H71" s="35" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr">
@@ -4943,26 +4939,26 @@
       </c>
       <c r="J71" s="33" t="inlineStr">
         <is>
-          <t>18th</t>
+          <t>19th</t>
         </is>
       </c>
       <c r="K71" s="31" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="L71" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M71" s="31" t="n">
         <v>4.8</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>4.4</v>
       </c>
       <c r="N71" s="31" t="n">
         <v>4.8</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.936</v>
+        <v>4.975</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
@@ -4980,7 +4976,7 @@
         <v>8.778</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>6.333</v>
+        <v>6</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -5034,7 +5030,7 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="P72" s="31" t="n">
         <v>7.625</v>
@@ -5109,7 +5105,7 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P73" s="31" t="n">
         <v>1.292</v>
@@ -5130,7 +5126,7 @@
         <v>7.244</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -5184,7 +5180,7 @@
         </is>
       </c>
       <c r="O74" s="31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P74" s="31" t="n">
         <v>8.417</v>
@@ -5202,16 +5198,16 @@
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>0.542</v>
+        <v>0.548</v>
       </c>
       <c r="C75" s="31" t="n">
         <v>0.633</v>
       </c>
       <c r="D75" s="31" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="E75" s="31" t="n">
-        <v>0.733</v>
+        <v>0.8</v>
       </c>
       <c r="F75" s="31" t="n">
         <v>1</v>
@@ -5221,36 +5217,36 @@
       </c>
       <c r="H75" s="33" t="inlineStr">
         <is>
-          <t>11th</t>
+          <t>14th</t>
         </is>
       </c>
       <c r="I75" s="31" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="J75" s="32" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>23rd</t>
         </is>
       </c>
       <c r="K75" s="31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>0.467</v>
+        <v>0.533</v>
       </c>
       <c r="N75" s="31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>0.645</v>
+        <v>0.649</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
@@ -5359,51 +5355,51 @@
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>4.808</v>
+        <v>4.873</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>4.333</v>
+        <v>4.667</v>
       </c>
       <c r="D79" s="31" t="n">
         <v>4.3</v>
       </c>
       <c r="E79" s="31" t="n">
-        <v>4.067</v>
+        <v>4.467</v>
       </c>
       <c r="F79" s="31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G79" s="31" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="H79" s="33" t="inlineStr">
         <is>
-          <t>16th</t>
+          <t>14th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
       <c r="J79" s="35" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="K79" s="31" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="L79" s="31" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M79" s="31" t="n">
-        <v>2.933</v>
+        <v>3.267</v>
       </c>
       <c r="N79" s="31" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>3.6</v>
+        <v>3.867</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.351</v>
+        <v>4.427</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
@@ -5421,7 +5417,7 @@
         <v>8.083</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -5475,7 +5471,7 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P80" s="31" t="n">
         <v>8.467000000000001</v>
@@ -5496,7 +5492,7 @@
         <v>1.417</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -5550,7 +5546,7 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P81" s="31" t="n">
         <v>1.444</v>
@@ -5571,7 +5567,7 @@
         <v>7.729</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D82" s="31" t="inlineStr">
         <is>
@@ -5625,7 +5621,7 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>6.667</v>
+        <v>7</v>
       </c>
       <c r="P82" s="31" t="n">
         <v>7.778</v>
@@ -5643,51 +5639,51 @@
         </is>
       </c>
       <c r="B83" s="31" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.701</v>
       </c>
       <c r="C83" s="31" t="n">
-        <v>0.7</v>
+        <v>0.767</v>
       </c>
       <c r="D83" s="31" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="E83" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="F83" s="31" t="n">
-        <v>0.3</v>
-      </c>
       <c r="G83" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="32" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>0.6</v>
+      </c>
+      <c r="H83" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="35" t="inlineStr">
-        <is>
-          <t>8th</t>
+      <c r="J83" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="K83" s="31" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="L83" s="31" t="n">
         <v>0.6</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>0.4</v>
+        <v>0.533</v>
       </c>
       <c r="N83" s="31" t="n">
         <v>0.4</v>
       </c>
       <c r="O83" s="31" t="n">
-        <v>0.433</v>
+        <v>0.5</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>0.486</v>
+        <v>0.507</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
         <is>
@@ -5708,7 +5704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5725,245 +5721,170 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>Detroit Tigers offense vs Texas Rangers defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C69" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E69" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F69" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G69" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H69" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I69" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J69" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K69" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L69" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M69" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N69" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O69" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P69" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q69" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>4.307</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>4.169</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>7.755</v>
+        <v>4.289</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.033</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="O70" s="31" t="n">
-        <v>8.667</v>
+        <v>4.633</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>7.673</v>
+        <v>4.155</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.02</v>
+        <v>7.755</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>2.25</v>
+        <v>9.333</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -6017,28 +5938,28 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.163</v>
+        <v>7.673</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>7.75</v>
+        <v>2.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -6092,323 +6013,319 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8.571</v>
+        <v>1.163</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="n">
+      <c r="B74" s="31" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L74" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L73" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M73" s="31" t="n">
+      <c r="M74" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O74" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="N73" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P73" s="31" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="P74" s="31" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>Texas Rangers offense vs Detroit Tigers defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C77" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F77" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G77" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H77" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="29" t="inlineStr">
+      <c r="I77" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="29" t="inlineStr">
+      <c r="J77" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K77" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L77" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr">
+      <c r="M77" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="29" t="inlineStr">
+      <c r="N77" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="29" t="inlineStr">
+      <c r="O77" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="P77" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="29" t="inlineStr">
+      <c r="Q77" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>4.217</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>7.816</v>
+        <v>4.167</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.233</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>3.55</v>
       </c>
       <c r="O78" s="31" t="n">
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>7.592</v>
+        <v>3.987</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>1.041</v>
+        <v>7.816</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -6462,28 +6379,28 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>0.898</v>
+        <v>7.592</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.592000000000001</v>
+        <v>1.041</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>9.333</v>
+        <v>0</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -6537,71 +6454,146 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>7.25</v>
+        <v>1</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.776</v>
+        <v>0.898</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="n">
+        <v>8.592000000000001</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="P81" s="31" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="C81" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D81" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E81" s="31" t="n">
+      <c r="B82" s="31" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E82" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="F81" s="31" t="n">
+      <c r="F82" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G82" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="H81" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="n">
+      <c r="L82" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L81" s="31" t="n">
+      <c r="M82" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N82" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="M81" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N81" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O81" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P81" s="31" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="O82" s="31" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6738,55 +6730,51 @@
         </is>
       </c>
       <c r="B69" s="31" t="n">
-        <v>4.114</v>
+        <v>4.138</v>
       </c>
       <c r="C69" s="31" t="n">
-        <v>4.733</v>
+        <v>4.833</v>
       </c>
       <c r="D69" s="31" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="E69" s="31" t="n">
-        <v>3.733</v>
+        <v>3.667</v>
       </c>
       <c r="F69" s="31" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G69" s="31" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="H69" s="32" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="I69" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+      <c r="I69" s="31" t="inlineStr"/>
       <c r="J69" s="32" t="inlineStr">
         <is>
-          <t>27th</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="K69" s="31" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>5.6</v>
+        <v>5.467</v>
       </c>
       <c r="N69" s="31" t="n">
         <v>5.65</v>
       </c>
       <c r="O69" s="31" t="n">
-        <v>6.5</v>
+        <v>6.067</v>
       </c>
       <c r="P69" s="31" t="n">
-        <v>5.641</v>
+        <v>5.646</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
@@ -6804,7 +6792,7 @@
         <v>9.239000000000001</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>12.25</v>
+        <v>13.333</v>
       </c>
       <c r="D70" s="31" t="inlineStr">
         <is>
@@ -6858,7 +6846,7 @@
         </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>14</v>
+        <v>8.5</v>
       </c>
       <c r="P70" s="31" t="n">
         <v>9.779999999999999</v>
@@ -6879,7 +6867,7 @@
         <v>0.978</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -6933,7 +6921,7 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>1.333</v>
+        <v>0.5</v>
       </c>
       <c r="P71" s="31" t="n">
         <v>1.24</v>
@@ -6954,7 +6942,7 @@
         <v>7.587</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -7008,7 +6996,7 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>7.333</v>
+        <v>6.5</v>
       </c>
       <c r="P72" s="31" t="n">
         <v>7.28</v>
@@ -7026,51 +7014,55 @@
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>0.347</v>
+        <v>0.397</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.333</v>
+        <v>0.467</v>
       </c>
       <c r="D73" s="31" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="E73" s="31" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F73" s="31" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G73" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
+        <v>0.8</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="K73" s="31" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>0.6</v>
+        <v>0.867</v>
       </c>
       <c r="N73" s="31" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>0.633</v>
+        <v>0.733</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.731</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
@@ -7179,22 +7171,22 @@
         </is>
       </c>
       <c r="B77" s="31" t="n">
-        <v>4.91</v>
+        <v>4.899</v>
       </c>
       <c r="C77" s="31" t="n">
-        <v>6.233</v>
+        <v>6.167</v>
       </c>
       <c r="D77" s="31" t="n">
         <v>6.75</v>
       </c>
       <c r="E77" s="31" t="n">
-        <v>6.267</v>
+        <v>6.133</v>
       </c>
       <c r="F77" s="31" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="G77" s="31" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="H77" s="35" t="inlineStr">
         <is>
@@ -7212,22 +7204,22 @@
         </is>
       </c>
       <c r="K77" s="31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L77" s="31" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>4.467</v>
+        <v>4.6</v>
       </c>
       <c r="N77" s="31" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="O77" s="31" t="n">
-        <v>5.1</v>
+        <v>4.967</v>
       </c>
       <c r="P77" s="31" t="n">
-        <v>4.975</v>
+        <v>4.963</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
@@ -7245,7 +7237,7 @@
         <v>8.32</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>10.667</v>
+        <v>11</v>
       </c>
       <c r="D78" s="31" t="inlineStr">
         <is>
@@ -7299,7 +7291,7 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>13.5</v>
+        <v>13.333</v>
       </c>
       <c r="P78" s="31" t="n">
         <v>8.651999999999999</v>
@@ -7320,7 +7312,7 @@
         <v>0.92</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>1.667</v>
+        <v>2.5</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -7374,7 +7366,7 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>0.75</v>
+        <v>0.333</v>
       </c>
       <c r="P79" s="31" t="n">
         <v>0.978</v>
@@ -7395,7 +7387,7 @@
         <v>8.92</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>9.667</v>
+        <v>9.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -7449,7 +7441,7 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>7.25</v>
+        <v>7.333</v>
       </c>
       <c r="P80" s="31" t="n">
         <v>8.173999999999999</v>
@@ -7467,55 +7459,55 @@
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>0.506</v>
+        <v>0.538</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="D81" s="31" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="E81" s="31" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F81" s="31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="G81" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J81" s="32" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L81" s="31" t="n">
+      <c r="N81" s="31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O81" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M81" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N81" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O81" s="31" t="n">
-        <v>0.667</v>
-      </c>
       <c r="P81" s="31" t="n">
-        <v>0.569</v>
+        <v>0.603</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
@@ -7614,7 +7606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7758,13 +7750,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6558396946564886</v>
+        <v>0.6558518518518518</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-191</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7824,13 +7816,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5679831932773109</v>
+        <v>0.5694871794871795</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7854,7 +7846,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7890,13 +7882,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6857090909090908</v>
+        <v>0.6856787439613526</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-218</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-109</v>
+        <v>-107</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7956,13 +7948,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.680890909090909</v>
+        <v>0.6811004405286344</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-120</v>
+        <v>-127</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7986,7 +7978,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 68.1% (fair -213). Your call.</t>
+          <t>Model 68.1% (fair -214). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8022,13 +8014,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3545820433436532</v>
+        <v>0.3491591591591592</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8052,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 35.5% (fair +182). Your call.</t>
+          <t>Model 34.9% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8088,10 +8080,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6011360189573459</v>
+        <v>0.5986635071090046</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-151</v>
+        <v>-149</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-111</v>
@@ -8118,7 +8110,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8135,32 +8127,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4259315589353613</v>
+        <v>0.5333653846153845</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>135</v>
+        <v>-114</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8184,7 +8176,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8220,13 +8212,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4679411764705882</v>
+        <v>0.4706410256410257</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8250,7 +8242,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8286,10 +8278,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.54635</v>
+        <v>0.5468500000000001</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-120</v>
+        <v>-121</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>100</v>
@@ -8316,7 +8308,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8333,32 +8325,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4862162162162162</v>
+        <v>0.4259523809523809</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8382,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8394,17 +8386,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8414,17 +8406,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4771621621621622</v>
+        <v>0.4920276497695853</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8448,7 +8440,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8526,17 +8518,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8546,17 +8538,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5418173076923077</v>
+        <v>0.4712162162162163</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-118</v>
+        <v>112</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-108</v>
+        <v>122</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8580,7 +8572,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8597,12 +8589,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8612,17 +8604,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4867605633802817</v>
+        <v>0.5421288461538462</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>105</v>
+        <v>-118</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>113</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8646,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8663,32 +8655,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4774654377880185</v>
+        <v>0.5318634146341463</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>117</v>
+        <v>-105</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8712,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +109). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8724,37 +8716,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.6204000000000001</v>
+        <v>0.5317609756097561</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-163</v>
+        <v>-114</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-150</v>
+        <v>-105</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8778,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8795,12 +8787,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -8810,17 +8802,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.438093220338983</v>
+        <v>0.4777419354838709</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8844,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8880,13 +8872,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.51405</v>
+        <v>0.5076960784313725</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-106</v>
+        <v>-103</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8910,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8919,9 +8911,207 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.6204000000000001</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>-163</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-150</v>
+      </c>
+      <c r="I23" s="13">
+        <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="16">
+        <f>IF($H$23="","",$F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>IF($H$23="","",MAX(0,($F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))/IF($H$23&lt;0,-100/$H$23,$H$23/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IF($H$23="","",ROUND(MIN($K$23,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IF($J$23="","",IF($J$23&lt;0,"Pass",IF($J$23&lt;'Settings'!$B$4,"Thin",IF($J$23&lt;0.06,"✅ Sharp band",IF($J$23&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.0% (fair -163). Your call.</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="16">
+        <f>IF(OR($H$23="",$O$23=""),"",(1+IF($H$23&lt;0,-100/$H$23,$H$23/100))/(1+IF($O$23&lt;0,-100/$O$23,$O$23/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.4381702127659575</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>135</v>
+      </c>
+      <c r="I24" s="13">
+        <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>IF($H$24="","",$F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>IF($H$24="","",MAX(0,($F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))/IF($H$24&lt;0,-100/$H$24,$H$24/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L24" s="18">
+        <f>IF($H$24="","",ROUND(MIN($K$24,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IF($J$24="","",IF($J$24&lt;0,"Pass",IF($J$24&lt;'Settings'!$B$4,"Thin",IF($J$24&lt;0.06,"✅ Sharp band",IF($J$24&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.8% (fair +128). Your call.</t>
+        </is>
+      </c>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="16">
+        <f>IF(OR($H$24="",$O$24=""),"",(1+IF($H$24&lt;0,-100/$H$24,$H$24/100))/(1+IF($O$24&lt;0,-100/$O$24,$O$24/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.4926923076923077</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.3% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J22">
+  <conditionalFormatting sqref="J5:J25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9087,13 +9277,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4867605633802817</v>
+        <v>0.4926923076923077</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9117,7 +9307,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9153,13 +9343,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5132303317535545</v>
+        <v>0.5072884615384615</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-105</v>
+        <v>-103</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9183,7 +9373,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9351,13 +9541,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3441605839416058</v>
+        <v>0.3441481481481481</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>191</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9417,13 +9607,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6558396946564886</v>
+        <v>0.6558518518518518</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-191</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9483,13 +9673,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4533640552995392</v>
+        <v>0.4526146788990826</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>121</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9549,7 +9739,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5466369369369369</v>
+        <v>0.5473513513513514</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-121</v>
@@ -9615,13 +9805,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.51405</v>
+        <v>0.5076960784313725</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-106</v>
+        <v>-103</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9645,7 +9835,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9681,13 +9871,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.48595</v>
+        <v>0.4923176470588235</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9711,7 +9901,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9747,13 +9937,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4259315589353613</v>
+        <v>0.4259523809523809</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>135</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9879,10 +10069,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.54635</v>
+        <v>0.5468500000000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-120</v>
+        <v>-121</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>100</v>
@@ -9909,7 +10099,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9945,10 +10135,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.45365</v>
+        <v>0.45315</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>100</v>
@@ -9975,7 +10165,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10011,10 +10201,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.49615</v>
+        <v>0.49975</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>100</v>
@@ -10041,7 +10231,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10077,13 +10267,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5038374384236454</v>
+        <v>0.50025</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-103</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10107,7 +10297,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10143,13 +10333,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4862162162162162</v>
+        <v>0.4920276497695853</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10173,7 +10363,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10209,13 +10399,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5137869955156951</v>
+        <v>0.5080050228310502</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-106</v>
+        <v>-103</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-123</v>
+        <v>-119</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10239,7 +10429,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10275,13 +10465,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4199</v>
+        <v>0.4281</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10305,7 +10495,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10341,13 +10531,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5801000000000001</v>
+        <v>0.5719000000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-138</v>
+        <v>-134</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10371,7 +10561,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10407,13 +10597,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3191085271317829</v>
+        <v>0.3189138576779026</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10437,7 +10627,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 31.9% (fair +213). Your call.</t>
+          <t>Model 31.9% (fair +214). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10473,13 +10663,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.680890909090909</v>
+        <v>0.6811004405286344</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-120</v>
+        <v>-127</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10503,7 +10693,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 68.1% (fair -213). Your call.</t>
+          <t>Model 68.1% (fair -214). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10539,13 +10729,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4679411764705882</v>
+        <v>0.4706410256410257</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10569,7 +10759,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10605,10 +10795,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.532053781512605</v>
+        <v>0.5293865546218487</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-114</v>
+        <v>-112</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-138</v>
@@ -10635,7 +10825,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10671,13 +10861,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5008415841584158</v>
+        <v>0.4992647058823529</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10701,7 +10891,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10737,10 +10927,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4991490196078431</v>
+        <v>0.5007803921568627</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-104</v>
@@ -10767,7 +10957,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -10869,13 +11059,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6857090909090908</v>
+        <v>0.6856787439613526</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-218</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-109</v>
+        <v>-107</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -10935,13 +11125,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.438093220338983</v>
+        <v>0.4381702127659575</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>128</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11001,7 +11191,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5619540983606558</v>
+        <v>0.5618360655737705</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>-128</v>
@@ -11067,13 +11257,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.6391</v>
+        <v>0.5333653846153845</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-177</v>
+        <v>-114</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11097,7 +11287,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11133,13 +11323,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.3609</v>
+        <v>0.4666130434782609</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>177</v>
+        <v>114</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>119</v>
+        <v>-107</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11163,7 +11353,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11199,10 +11389,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.39884</v>
+        <v>0.4013600000000001</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>150</v>
@@ -11229,7 +11419,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11265,10 +11455,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6011360189573459</v>
+        <v>0.5986635071090046</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-151</v>
+        <v>-149</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-111</v>
@@ -11295,7 +11485,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11463,13 +11653,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5318634146341463</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-102</v>
+        <v>-114</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>104</v>
+        <v>-105</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11493,7 +11683,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11529,13 +11719,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4955000000000001</v>
+        <v>0.4681220657276995</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -11559,7 +11749,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11595,13 +11785,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.522537037037037</v>
+        <v>0.5222853211009174</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>-109</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-116</v>
+        <v>-118</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -11625,7 +11815,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -109). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -11661,7 +11851,7 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4774654377880185</v>
+        <v>0.4777419354838709</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>109</v>
@@ -11691,7 +11881,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +109). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -11727,10 +11917,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.513219512195122</v>
+        <v>0.5317609756097561</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-105</v>
+        <v>-114</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>-105</v>
@@ -11757,7 +11947,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -11793,10 +11983,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4867976744186047</v>
+        <v>0.4682372093023256</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>-115</v>
@@ -11823,7 +12013,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -11859,10 +12049,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.6015215686274511</v>
+        <v>0.6000019607843138</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-151</v>
+        <v>-150</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>-155</v>
@@ -11889,7 +12079,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -11925,10 +12115,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.3984347826086957</v>
+        <v>0.4</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>130</v>
@@ -11955,7 +12145,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -11991,7 +12181,7 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5418173076923077</v>
+        <v>0.5421288461538462</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>-118</v>
@@ -12057,13 +12247,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4582211538461539</v>
+        <v>0.4578640776699029</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>118</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12119,17 +12309,17 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4739</v>
+        <v>0.5406</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>111</v>
+        <v>-118</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12153,7 +12343,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12185,17 +12375,17 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5261</v>
+        <v>0.4594</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-111</v>
+        <v>118</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12219,7 +12409,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12255,10 +12445,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4339</v>
+        <v>0.4296</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13">
@@ -12283,7 +12473,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12319,10 +12509,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5661</v>
+        <v>0.5704</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13">
@@ -12347,7 +12537,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12383,10 +12573,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5338586854460093</v>
+        <v>0.5326915492957747</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>-113</v>
@@ -12413,7 +12603,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12449,13 +12639,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.466132075471698</v>
+        <v>0.4672857142857142</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12479,7 +12669,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12515,13 +12705,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.407</v>
+        <v>0.4727</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -12545,7 +12735,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -12581,13 +12771,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.593</v>
+        <v>0.5273</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-146</v>
+        <v>-112</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -12611,7 +12801,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -12647,10 +12837,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4491</v>
+        <v>0.4536</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -12675,7 +12865,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -12711,10 +12901,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5464</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-123</v>
+        <v>-120</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -12739,7 +12929,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -12909,7 +13099,7 @@
         <v>280</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -12975,7 +13165,7 @@
         <v>-280</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -13035,10 +13225,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4078</v>
+        <v>0.4052</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13063,7 +13253,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13099,10 +13289,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.5948</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-145</v>
+        <v>-147</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13127,7 +13317,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13163,13 +13353,13 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5679831932773109</v>
+        <v>0.5694871794871795</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -13193,7 +13383,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13229,10 +13419,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.432</v>
+        <v>0.4305</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -13257,7 +13447,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13293,13 +13483,13 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4932178217821782</v>
+        <v>0.4884803921568628</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -13323,7 +13513,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13359,10 +13549,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5067960784313725</v>
+        <v>0.5114862745098039</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>-104</v>
@@ -13389,7 +13579,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13557,10 +13747,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4771621621621622</v>
+        <v>0.4712162162162163</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>122</v>
@@ -13587,7 +13777,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13623,13 +13813,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5228336405529954</v>
+        <v>0.5287563876651983</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -13653,7 +13843,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -13689,7 +13879,7 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4485650224215246</v>
+        <v>0.4490134529147983</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>123</v>
@@ -13755,13 +13945,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5514491803278688</v>
+        <v>0.5509913580246915</v>
       </c>
       <c r="G76" s="14" t="n">
         <v>-123</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-144</v>
+        <v>-143</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -13821,10 +14011,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4847</v>
+        <v>0.482</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>133</v>
@@ -13851,7 +14041,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -13887,10 +14077,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5153</v>
+        <v>0.518</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-117</v>
@@ -13917,7 +14107,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -13953,10 +14143,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5177</v>
+        <v>0.5216</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>108</v>
@@ -13983,7 +14173,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14019,13 +14209,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4823</v>
+        <v>0.4784</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14049,7 +14239,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14085,7 +14275,7 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4618</v>
+        <v>0.4609</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>117</v>
@@ -14115,7 +14305,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14151,7 +14341,7 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5382</v>
+        <v>0.5391</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>-117</v>
@@ -14181,7 +14371,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14217,7 +14407,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.48835</v>
+        <v>0.4878</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>105</v>
@@ -14283,7 +14473,7 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5116392156862745</v>
+        <v>0.5121999999999999</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>-105</v>
@@ -14349,13 +14539,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.3545820433436532</v>
+        <v>0.3491591591591592</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14379,7 +14569,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 35.5% (fair +182). Your call.</t>
+          <t>Model 34.9% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14415,13 +14605,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.645403003003003</v>
+        <v>0.6508478260869565</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-182</v>
+        <v>-186</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-233</v>
+        <v>-245</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14445,7 +14635,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -182). Your call.</t>
+          <t>Model 65.1% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15132,22 +15322,22 @@
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>3.837</v>
+        <v>3.827</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>4</v>
+        <v>3.767</v>
       </c>
       <c r="D70" s="31" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="E70" s="31" t="n">
-        <v>3.867</v>
+        <v>3.467</v>
       </c>
       <c r="F70" s="31" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G70" s="31" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="H70" s="32" t="inlineStr">
         <is>
@@ -15157,26 +15347,26 @@
       <c r="I70" s="31" t="inlineStr"/>
       <c r="J70" s="33" t="inlineStr">
         <is>
-          <t>15th</t>
+          <t>14th</t>
         </is>
       </c>
       <c r="K70" s="31" t="n">
         <v>4.6</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>4.667</v>
+        <v>4.4</v>
       </c>
       <c r="N70" s="31" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="O70" s="31" t="n">
-        <v>4.267</v>
+        <v>4.3</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>3.813</v>
+        <v>3.803</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
@@ -15194,7 +15384,7 @@
         <v>7.306</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.333</v>
+        <v>3.5</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -15248,7 +15438,7 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="P71" s="31" t="n">
         <v>7.312</v>
@@ -15269,7 +15459,7 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -15323,7 +15513,7 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="P72" s="31" t="n">
         <v>1.062</v>
@@ -15344,7 +15534,7 @@
         <v>8.407999999999999</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -15398,7 +15588,7 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="P73" s="31" t="n">
         <v>8.561999999999999</v>
@@ -15416,13 +15606,13 @@
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>0.526</v>
+        <v>0.519</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>0.467</v>
+        <v>0.433</v>
       </c>
       <c r="D74" s="31" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E74" s="31" t="n">
         <v>0.133</v>
@@ -15435,13 +15625,13 @@
       </c>
       <c r="H74" s="32" t="inlineStr">
         <is>
-          <t>27th</t>
+          <t>28th</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="32" t="inlineStr">
-        <is>
-          <t>23rd</t>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="K74" s="31" t="n">
@@ -15451,7 +15641,7 @@
         <v>0.5</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="N74" s="31" t="n">
         <v>0.65</v>
@@ -15460,7 +15650,7 @@
         <v>0.533</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
@@ -15569,51 +15759,55 @@
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>4.8</v>
+        <v>4.921</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>3.967</v>
+        <v>4.1</v>
       </c>
       <c r="D78" s="31" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="E78" s="31" t="n">
-        <v>3.267</v>
+        <v>4.067</v>
       </c>
       <c r="F78" s="31" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="G78" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
+        <v>6.4</v>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="32" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="K78" s="31" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>5.6</v>
+        <v>6.467</v>
       </c>
       <c r="N78" s="31" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="O78" s="31" t="n">
-        <v>4.967</v>
+        <v>5.4</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>4.588</v>
+        <v>4.704</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
@@ -15631,7 +15825,7 @@
         <v>8.958</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -15685,7 +15879,7 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="P79" s="31" t="n">
         <v>7.918</v>
@@ -15706,7 +15900,7 @@
         <v>1.333</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -15760,7 +15954,7 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>1.667</v>
+        <v>2.5</v>
       </c>
       <c r="P80" s="31" t="n">
         <v>0.918</v>
@@ -15781,7 +15975,7 @@
         <v>7.688</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -15835,7 +16029,7 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>7.333</v>
+        <v>8.5</v>
       </c>
       <c r="P81" s="31" t="n">
         <v>9.061</v>
@@ -15853,16 +16047,16 @@
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>0.589</v>
+        <v>0.581</v>
       </c>
       <c r="C82" s="31" t="n">
         <v>0.6</v>
       </c>
       <c r="D82" s="31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E82" s="31" t="n">
-        <v>0.6</v>
+        <v>0.467</v>
       </c>
       <c r="F82" s="31" t="n">
         <v>0.6</v>
@@ -15872,17 +16066,13 @@
       </c>
       <c r="H82" s="35" t="inlineStr">
         <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>8th</t>
         </is>
       </c>
       <c r="K82" s="31" t="n">
@@ -15901,7 +16091,7 @@
         <v>0.633</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>0.513</v>
+        <v>0.506</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
@@ -15922,7 +16112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15939,170 +16129,245 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B71" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D71" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E71" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F71" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G71" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H71" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I71" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J71" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K71" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L71" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M71" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N71" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O71" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P71" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q71" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A71" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="n">
+        <v>5.085</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>5.433</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>5.062</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E72" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G72" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>9th</t>
+        <v>13</v>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L72" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M72" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N72" s="31" t="n">
-        <v>4.65</v>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>4.567</v>
+        <v>9</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>5.101</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.811999999999999</v>
+        <v>1.188</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -16156,28 +16421,28 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>9.039999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>1.188</v>
+        <v>9.708</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -16231,319 +16496,319 @@
         </is>
       </c>
       <c r="O74" s="31" t="n">
-        <v>2.333</v>
+        <v>8</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>1.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>9.708</v>
+        <v>0.545</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.4</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H75" s="32" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J75" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>8</v>
+        <v>0.433</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="C76" s="31" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="D76" s="31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E76" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F76" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G76" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="32" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr"/>
-      <c r="J76" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M76" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N76" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O76" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
     <row r="78">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
+      <c r="A78" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F78" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G78" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H78" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I78" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J78" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K78" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L78" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M78" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N78" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O78" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P78" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q78" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B79" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C79" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D79" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E79" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F79" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G79" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H79" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I79" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J79" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K79" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L79" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M79" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N79" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O79" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P79" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q79" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A79" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="C79" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O79" s="31" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="P79" s="31" t="n">
+        <v>4.768</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>5.329</v>
+        <v>8.52</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D80" s="31" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E80" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F80" s="31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="G80" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I80" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J80" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="L80" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M80" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N80" s="31" t="n">
-        <v>5.25</v>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="31" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>5.633</v>
+        <v>8</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>4.815</v>
+        <v>7.792</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.52</v>
+        <v>1.26</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>7.667</v>
+        <v>0.5</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -16597,28 +16862,28 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>1.26</v>
+        <v>7.98</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D82" s="31" t="inlineStr">
         <is>
@@ -16672,150 +16937,71 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>0.896</v>
+        <v>9.292</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B83" s="31" t="n">
-        <v>7.98</v>
+        <v>0.833</v>
       </c>
       <c r="C83" s="31" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="D83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.7</v>
+      </c>
+      <c r="D83" s="31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E83" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F83" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="35" t="inlineStr">
+        <is>
+          <t>9th</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J83" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L83" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M83" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N83" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O83" s="31" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>9.292</v>
+        <v>0.416</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B84" s="31" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="C84" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D84" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E84" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F84" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G84" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H84" s="35" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I84" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J84" s="33" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K84" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L84" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N84" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O84" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P84" s="31" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -16834,7 +17020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16851,170 +17037,320 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D66" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F66" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G66" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H66" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I66" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J66" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K66" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L66" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M66" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N66" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O66" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P66" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q66" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles offense vs Cincinnati Reds defense</t>
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="n">
+        <v>4.603</v>
+      </c>
+      <c r="C67" s="31" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="D67" s="31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E67" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F67" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G67" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I67" s="31" t="inlineStr"/>
+      <c r="J67" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K67" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L67" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M67" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="N67" s="31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O67" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="P67" s="31" t="n">
+        <v>4.724</v>
+      </c>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P68" s="31" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B69" s="31" t="n">
-        <v>4.558</v>
+        <v>1.271</v>
       </c>
       <c r="C69" s="31" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H69" s="32" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>2</v>
+      </c>
+      <c r="D69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>4.1</v>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O69" s="31" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="P69" s="31" t="n">
-        <v>4.68</v>
+        <v>1.383</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>8.208</v>
+        <v>8.917</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="D70" s="31" t="inlineStr">
         <is>
@@ -17068,394 +17404,394 @@
         </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>8.333</v>
+        <v>9</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>8.106</v>
+        <v>7.404</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.271</v>
+        <v>0.532</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.833</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>0.45</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>1.667</v>
+        <v>0.6</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.383</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="n">
-        <v>8.917</v>
-      </c>
-      <c r="C72" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="P72" s="31" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Baltimore Orioles defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B74" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E74" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F74" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G74" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H74" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I74" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J74" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K74" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L74" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M74" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N74" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O74" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P74" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q74" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>3.767</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H75" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O75" s="31" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>4.821</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n">
         <v>7.404</v>
       </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L73" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M73" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N73" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P73" s="31" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Baltimore Orioles defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="C76" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P76" s="31" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B77" s="31" t="n">
-        <v>3.987</v>
+        <v>1.213</v>
       </c>
       <c r="C77" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H77" s="32" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>2</v>
+      </c>
+      <c r="D77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>4.1</v>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O77" s="31" t="n">
-        <v>4.267</v>
+        <v>0</v>
       </c>
       <c r="P77" s="31" t="n">
-        <v>4.818</v>
+        <v>1.062</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>7.404</v>
+        <v>9.532</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>6.667</v>
+        <v>11.5</v>
       </c>
       <c r="D78" s="31" t="inlineStr">
         <is>
@@ -17509,221 +17845,71 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>8.833</v>
+        <v>8</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>1.213</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>0.9</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>0.5</v>
+        <v>0.733</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>1.062</v>
+        <v>0.494</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="n">
-        <v>9.532</v>
-      </c>
-      <c r="C80" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P80" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="31" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="C81" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D81" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E81" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F81" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G81" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L81" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M81" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N81" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O81" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P81" s="31" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="Q81" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -429,7 +429,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10277475"/>
+    <ext cx="10125075" cy="10363200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -459,7 +459,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="11106150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -549,7 +549,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10763250"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -579,7 +579,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="10696575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 06:11</t>
+          <t>2026-07-05 08:16</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1173,249 +1173,174 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="28" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>Minnesota Twins offense vs New York Yankees defense</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C70" s="29" t="inlineStr">
+      <c r="C71" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D70" s="29" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E70" s="29" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F70" s="29" t="inlineStr">
+      <c r="F71" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G70" s="29" t="inlineStr">
+      <c r="G71" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H70" s="29" t="inlineStr">
+      <c r="H71" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I70" s="29" t="inlineStr">
+      <c r="I71" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J70" s="29" t="inlineStr">
+      <c r="J71" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K70" s="29" t="inlineStr">
+      <c r="K71" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L70" s="29" t="inlineStr">
+      <c r="L71" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M70" s="29" t="inlineStr">
+      <c r="M71" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N70" s="29" t="inlineStr">
+      <c r="N71" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O70" s="29" t="inlineStr">
+      <c r="O71" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P70" s="29" t="inlineStr">
+      <c r="P71" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q70" s="29" t="inlineStr">
+      <c r="Q71" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>4.857</v>
-      </c>
-      <c r="C71" s="31" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="32" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>3.835</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.776</v>
+        <v>4.857</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.567</v>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G72" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J72" s="32" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M72" s="31" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>4.8</v>
       </c>
       <c r="O72" s="31" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.609</v>
+        <v>3.835</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.061</v>
+        <v>7.776</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -1469,28 +1394,28 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>0.913</v>
+        <v>7.609</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>8.939</v>
+        <v>1.061</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -1544,319 +1469,319 @@
         </is>
       </c>
       <c r="O74" s="31" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>8.435</v>
+        <v>0.913</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>8.939</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>8.435</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B75" s="31" t="n">
+      <c r="B76" s="31" t="n">
         <v>0.714</v>
       </c>
-      <c r="C75" s="31" t="n">
+      <c r="C76" s="31" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="D75" s="31" t="n">
+      <c r="D76" s="31" t="n">
         <v>1.25</v>
       </c>
-      <c r="E75" s="31" t="n">
+      <c r="E76" s="31" t="n">
         <v>1.267</v>
       </c>
-      <c r="F75" s="31" t="n">
+      <c r="F76" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="G75" s="31" t="n">
+      <c r="G76" s="31" t="n">
         <v>1.8</v>
       </c>
-      <c r="H75" s="35" t="inlineStr">
+      <c r="H76" s="35" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I75" s="31" t="inlineStr">
+      <c r="I76" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J75" s="32" t="inlineStr">
+      <c r="J76" s="32" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="K75" s="31" t="n">
+      <c r="K76" s="31" t="n">
         <v>1.8</v>
       </c>
-      <c r="L75" s="31" t="n">
+      <c r="L76" s="31" t="n">
         <v>1.1</v>
       </c>
-      <c r="M75" s="31" t="n">
+      <c r="M76" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="N75" s="31" t="n">
+      <c r="N76" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="O75" s="31" t="n">
+      <c r="O76" s="31" t="n">
         <v>0.633</v>
       </c>
-      <c r="P75" s="31" t="n">
+      <c r="P76" s="31" t="n">
         <v>0.514</v>
       </c>
-      <c r="Q75" s="34" t="inlineStr">
+      <c r="Q76" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>New York Yankees offense vs Minnesota Twins defense</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="29" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
+      <c r="C79" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D78" s="29" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E78" s="29" t="inlineStr">
+      <c r="E79" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F78" s="29" t="inlineStr">
+      <c r="F79" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G78" s="29" t="inlineStr">
+      <c r="G79" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H78" s="29" t="inlineStr">
+      <c r="H79" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I78" s="29" t="inlineStr">
+      <c r="I79" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J78" s="29" t="inlineStr">
+      <c r="J79" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K78" s="29" t="inlineStr">
+      <c r="K79" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L78" s="29" t="inlineStr">
+      <c r="L79" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M78" s="29" t="inlineStr">
+      <c r="M79" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N78" s="29" t="inlineStr">
+      <c r="N79" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O78" s="29" t="inlineStr">
+      <c r="O79" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P78" s="29" t="inlineStr">
+      <c r="P79" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q78" s="29" t="inlineStr">
+      <c r="Q79" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B79" s="31" t="n">
-        <v>4.734</v>
-      </c>
-      <c r="C79" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H79" s="32" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O79" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P79" s="31" t="n">
-        <v>5.117</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.109</v>
+        <v>4.734</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.467</v>
+      </c>
+      <c r="D80" s="31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E80" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H80" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L80" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M80" s="31" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N80" s="31" t="n">
+        <v>5.25</v>
       </c>
       <c r="O80" s="31" t="n">
-        <v>9.5</v>
+        <v>5.6</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>5.117</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.413</v>
+        <v>8.109</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -1910,28 +1835,28 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>0.918</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>9.130000000000001</v>
+        <v>1.413</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="D82" s="31" t="inlineStr">
         <is>
@@ -1985,71 +1910,146 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>8.265000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="C83" s="31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P83" s="31" t="n">
+        <v>8.265000000000001</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B83" s="31" t="n">
+      <c r="B84" s="31" t="n">
         <v>0.622</v>
       </c>
-      <c r="C83" s="31" t="n">
+      <c r="C84" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="D83" s="31" t="n">
+      <c r="D84" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="E83" s="31" t="n">
+      <c r="E84" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="F83" s="31" t="n">
+      <c r="F84" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G83" s="31" t="n">
+      <c r="G84" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="H83" s="32" t="inlineStr">
+      <c r="H84" s="32" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="35" t="inlineStr">
+      <c r="I84" s="31" t="inlineStr"/>
+      <c r="J84" s="35" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="K83" s="31" t="n">
+      <c r="K84" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L83" s="31" t="n">
+      <c r="L84" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M83" s="31" t="n">
+      <c r="M84" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="N83" s="31" t="n">
+      <c r="N84" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="O83" s="31" t="n">
+      <c r="O84" s="31" t="n">
         <v>0.633</v>
       </c>
-      <c r="P83" s="31" t="n">
+      <c r="P84" s="31" t="n">
         <v>0.597</v>
       </c>
-      <c r="Q83" s="34" t="inlineStr">
+      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3884,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3901,249 +3901,174 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.595</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="32" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>5.266</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.234</v>
+        <v>4.595</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.667</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>6.65</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>5</v>
+        <v>5.733</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>8.603999999999999</v>
+        <v>5.266</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.213</v>
+        <v>7.234</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -4197,28 +4122,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.25</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.426</v>
+        <v>1.213</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -4272,315 +4197,315 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.208</v>
+        <v>1.25</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.426</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.8159999999999999</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>4.089</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>4.747</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>7.792</v>
+        <v>4.089</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.767</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H79" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>4.7</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>7</v>
+        <v>4.467</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>9.319000000000001</v>
+        <v>4.747</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>0.896</v>
+        <v>7.792</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -4634,28 +4559,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.17</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.021000000000001</v>
+        <v>0.896</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -4709,71 +4634,146 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>9.276999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8.021000000000001</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>9.276999999999999</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.461</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.833</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="35" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.513</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4792,7 +4792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4809,174 +4809,249 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Houston Astros defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Houston Astros defense</t>
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>4.975</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.733</v>
+        <v>8.778</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G71" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.8</v>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.975</v>
+        <v>7.625</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.778</v>
+        <v>0.956</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -5030,28 +5105,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.625</v>
+        <v>1.292</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>0.956</v>
+        <v>7.244</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -5105,319 +5180,319 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.292</v>
+        <v>8.417</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>7.244</v>
+        <v>0.548</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.633</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J74" s="32" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.5</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>11</v>
+        <v>0.633</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>8.417</v>
+        <v>0.649</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Houston Astros offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>4.873</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I75" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J75" s="32" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Houston Astros offense vs Tampa Bay Rays defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>4.427</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>4.873</v>
+        <v>8.083</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
+        <v>8</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>3.5</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>3.867</v>
+        <v>12</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.427</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.083</v>
+        <v>1.417</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -5471,28 +5546,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.467000000000001</v>
+        <v>1.444</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.417</v>
+        <v>7.729</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -5546,146 +5621,71 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.444</v>
+        <v>7.778</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>7.729</v>
+        <v>0.701</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.767</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>0.4</v>
       </c>
       <c r="O82" s="31" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>7.778</v>
+        <v>0.507</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5694871794871795</v>
+        <v>0.5694893617021276</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-132</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7882,13 +7882,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6856787439613526</v>
+        <v>0.6848746411483253</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-218</v>
+        <v>-217</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 68.6% (fair -218). Your call.</t>
+          <t>Model 68.5% (fair -217). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7948,13 +7948,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6811004405286344</v>
+        <v>0.6827777777777778</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 68.1% (fair -214). Your call.</t>
+          <t>Model 68.3% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8014,13 +8014,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3491591591591592</v>
+        <v>0.3444057971014493</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +186). Your call.</t>
+          <t>Model 34.4% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8080,13 +8080,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5986635071090046</v>
+        <v>0.5986619047619047</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-149</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8127,32 +8127,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5333653846153845</v>
+        <v>0.43296875</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-114</v>
+        <v>131</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8212,13 +8212,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4706410256410257</v>
+        <v>0.4695744680851063</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8259,32 +8259,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5468500000000001</v>
+        <v>0.5304807692307691</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-121</v>
+        <v>-113</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8325,32 +8325,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4259523809523809</v>
+        <v>0.5512509803921568</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>135</v>
+        <v>-123</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>152</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8391,32 +8391,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4920276497695853</v>
+        <v>0.5459999999999999</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>103</v>
+        <v>-120</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8457,32 +8457,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5740255707762557</v>
+        <v>0.4923041474654378</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-135</v>
+        <v>103</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-119</v>
+        <v>117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8518,37 +8518,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4712162162162163</v>
+        <v>0.5670574074074075</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>112</v>
+        <v>-131</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>122</v>
+        <v>-116</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8584,17 +8584,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5421288461538462</v>
+        <v>0.4740990990990991</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-118</v>
+        <v>111</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-108</v>
+        <v>122</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5318634146341463</v>
+        <v>0.5425442307692308</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-114</v>
+        <v>-119</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8731,22 +8731,22 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5317609756097561</v>
+        <v>0.4764383561643836</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-114</v>
+        <v>110</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-105</v>
+        <v>119</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -8802,17 +8802,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4777419354838709</v>
+        <v>0.4379831932773109</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8848,37 +8848,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5076960784313725</v>
+        <v>0.6204000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-103</v>
+        <v>-163</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>104</v>
+        <v>-150</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8914,17 +8914,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -8934,17 +8934,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6204000000000001</v>
+        <v>0.4919138755980862</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-163</v>
+        <v>103</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-150</v>
+        <v>109</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8985,32 +8985,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4381702127659575</v>
+        <v>0.5075247524752474</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>128</v>
+        <v>-103</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9051,12 +9051,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9066,17 +9066,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4926923076923077</v>
+        <v>0.5667777777777777</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>103</v>
+        <v>-131</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>-125</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9277,13 +9277,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4926923076923077</v>
+        <v>0.4919138755980862</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>103</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5072884615384615</v>
+        <v>0.5080673076923077</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-103</v>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4526146788990826</v>
+        <v>0.4484684684684686</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5473513513513514</v>
+        <v>0.5515279279279279</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-121</v>
+        <v>-123</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-122</v>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9801,17 +9801,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5076960784313725</v>
+        <v>0.4656</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-103</v>
+        <v>115</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9867,17 +9867,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4923176470588235</v>
+        <v>0.5344</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>103</v>
+        <v>-115</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9937,13 +9937,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4259523809523809</v>
+        <v>0.43296875</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10003,13 +10003,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5740255707762557</v>
+        <v>0.5670574074074075</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-135</v>
+        <v>-131</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-119</v>
+        <v>-116</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5468500000000001</v>
+        <v>0.5512509803921568</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-121</v>
+        <v>-123</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10135,13 +10135,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.45315</v>
+        <v>0.4487623762376238</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.49975</v>
+        <v>0.50145</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>100</v>
+        <v>-101</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>100</v>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.50025</v>
+        <v>0.49855</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-100</v>
+        <v>101</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4920276497695853</v>
+        <v>0.4923041474654378</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>103</v>
@@ -10399,13 +10399,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5080050228310502</v>
+        <v>0.5077090909090909</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>-103</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-119</v>
+        <v>-120</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10461,17 +10461,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4281</v>
+        <v>0.5075247524752474</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>134</v>
+        <v>-103</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10527,14 +10527,14 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5719000000000001</v>
+        <v>0.492470588235294</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-134</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-104</v>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10597,13 +10597,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3189138576779026</v>
+        <v>0.3171863117870723</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 31.9% (fair +214). Your call.</t>
+          <t>Model 31.7% (fair +215). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10663,13 +10663,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6811004405286344</v>
+        <v>0.6827777777777778</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 68.1% (fair -214). Your call.</t>
+          <t>Model 68.3% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10729,13 +10729,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4706410256410257</v>
+        <v>0.4695744680851063</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5293865546218487</v>
+        <v>0.5304302521008404</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-138</v>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10857,17 +10857,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4992647058823529</v>
+        <v>0.4384</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10923,14 +10923,14 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5007803921568627</v>
+        <v>0.5616</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-100</v>
+        <v>-128</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-104</v>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -10993,13 +10993,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3143032786885246</v>
+        <v>0.3151417004048583</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 31.4% (fair +218). Your call.</t>
+          <t>Model 31.5% (fair +217). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11059,13 +11059,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6856787439613526</v>
+        <v>0.6848746411483253</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-218</v>
+        <v>-217</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 68.6% (fair -218). Your call.</t>
+          <t>Model 68.5% (fair -217). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11125,13 +11125,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4381702127659575</v>
+        <v>0.4379831932773109</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>128</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5618360655737705</v>
+        <v>0.5620416666666667</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>-128</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-144</v>
+        <v>-140</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11257,13 +11257,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5333653846153845</v>
+        <v>0.629</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-114</v>
+        <v>-170</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11323,13 +11323,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4666130434782609</v>
+        <v>0.371</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-107</v>
+        <v>105</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11455,13 +11455,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5986635071090046</v>
+        <v>0.5986619047619047</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-149</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11521,13 +11521,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5679193832599119</v>
+        <v>0.5667777777777777</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>-131</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11587,7 +11587,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4320704845814978</v>
+        <v>0.433215859030837</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>131</v>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11653,13 +11653,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5318634146341463</v>
+        <v>0.5507</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-114</v>
+        <v>-123</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4681220657276995</v>
+        <v>0.4493</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>113</v>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11766,32 +11766,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5222853211009174</v>
+        <v>0.546611111111111</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-109</v>
+        <v>-121</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-118</v>
+        <v>-125</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -11832,32 +11832,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4777419354838709</v>
+        <v>0.4534234234234235</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -11908,22 +11908,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.5317609756097561</v>
+        <v>0.5235844036697248</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -11974,22 +11974,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4682372093023256</v>
+        <v>0.4764383561643836</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-115</v>
+        <v>119</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12040,22 +12040,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.6000019607843138</v>
+        <v>0.5304807692307691</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-150</v>
+        <v>-113</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-155</v>
+        <v>108</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12106,22 +12106,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4</v>
+        <v>0.469478431372549</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>130</v>
+        <v>-104</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5421288461538462</v>
+        <v>0.5425442307692308</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>-108</v>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12247,10 +12247,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4578640776699029</v>
+        <v>0.4574757281553398</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>106</v>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12309,17 +12309,17 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5406</v>
+        <v>0.5459999999999999</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-118</v>
+        <v>-120</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>116</v>
+        <v>-104</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12375,17 +12375,17 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4594</v>
+        <v>0.4539800995024876</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12445,10 +12445,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4296</v>
+        <v>0.4337</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12509,10 +12509,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5704</v>
+        <v>0.5663</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-133</v>
+        <v>-131</v>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12573,13 +12573,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5326915492957747</v>
+        <v>0.5305379146919431</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-114</v>
+        <v>-113</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12639,13 +12639,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4672857142857142</v>
+        <v>0.4694258373205742</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4536</v>
+        <v>0.4513</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -12901,10 +12901,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5464</v>
+        <v>0.5487</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13353,13 +13353,13 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5694871794871795</v>
+        <v>0.5694893617021276</v>
       </c>
       <c r="G67" s="14" t="n">
         <v>-132</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -13479,17 +13479,17 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4884803921568628</v>
+        <v>0.3858</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13545,14 +13545,14 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5114862745098039</v>
+        <v>0.6142000000000001</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-105</v>
+        <v>-159</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>-104</v>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4712162162162163</v>
+        <v>0.4740990990990991</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>122</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13813,13 +13813,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5287563876651983</v>
+        <v>0.5259189189189188</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -13879,13 +13879,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4490134529147983</v>
+        <v>0.445726872246696</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5509913580246915</v>
+        <v>0.5542819672131147</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-123</v>
+        <v>-124</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14143,13 +14143,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5216</v>
+        <v>0.5273863849765258</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-109</v>
+        <v>-112</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>108</v>
+        <v>-113</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4784</v>
+        <v>0.4725821596244131</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>113</v>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14539,13 +14539,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.3491591591591592</v>
+        <v>0.3444057971014493</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +186). Your call.</t>
+          <t>Model 34.4% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14605,10 +14605,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.6508478260869565</v>
+        <v>0.6556057971014493</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-186</v>
+        <v>-190</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>-245</v>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 65.6% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -17020,7 +17020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17037,245 +17037,170 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="28" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>Baltimore Orioles offense vs Cincinnati Reds defense</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B66" s="29" t="inlineStr">
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C66" s="29" t="inlineStr">
+      <c r="C67" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D66" s="29" t="inlineStr">
+      <c r="D67" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E66" s="29" t="inlineStr">
+      <c r="E67" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F66" s="29" t="inlineStr">
+      <c r="F67" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G66" s="29" t="inlineStr">
+      <c r="G67" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H66" s="29" t="inlineStr">
+      <c r="H67" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I66" s="29" t="inlineStr">
+      <c r="I67" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J66" s="29" t="inlineStr">
+      <c r="J67" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K66" s="29" t="inlineStr">
+      <c r="K67" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L66" s="29" t="inlineStr">
+      <c r="L67" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M66" s="29" t="inlineStr">
+      <c r="M67" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N66" s="29" t="inlineStr">
+      <c r="N67" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O66" s="29" t="inlineStr">
+      <c r="O67" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P66" s="29" t="inlineStr">
+      <c r="P67" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q66" s="29" t="inlineStr">
+      <c r="Q67" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B67" s="31" t="n">
-        <v>4.603</v>
-      </c>
-      <c r="C67" s="31" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="D67" s="31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E67" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F67" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G67" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I67" s="31" t="inlineStr"/>
-      <c r="J67" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K67" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L67" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M67" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="N67" s="31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O67" s="31" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="P67" s="31" t="n">
-        <v>4.724</v>
-      </c>
-      <c r="Q67" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B68" s="31" t="n">
-        <v>8.208</v>
+        <v>4.603</v>
       </c>
       <c r="C68" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.633</v>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G68" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I68" s="31" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L68" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M68" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="N68" s="31" t="n">
+        <v>4.25</v>
       </c>
       <c r="O68" s="31" t="n">
-        <v>9</v>
+        <v>4.733</v>
       </c>
       <c r="P68" s="31" t="n">
-        <v>8.106</v>
+        <v>4.724</v>
       </c>
       <c r="Q68" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="31" t="n">
-        <v>1.271</v>
+        <v>8.208</v>
       </c>
       <c r="C69" s="31" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D69" s="31" t="inlineStr">
         <is>
@@ -17329,28 +17254,28 @@
         </is>
       </c>
       <c r="O69" s="31" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="P69" s="31" t="n">
-        <v>1.383</v>
+        <v>8.106</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>8.917</v>
+        <v>1.271</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D70" s="31" t="inlineStr">
         <is>
@@ -17404,319 +17329,319 @@
         </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>7.404</v>
+        <v>1.383</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="n">
+        <v>8.917</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>7.404</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B71" s="31" t="n">
+      <c r="B72" s="31" t="n">
         <v>0.532</v>
       </c>
-      <c r="C71" s="31" t="n">
+      <c r="C72" s="31" t="n">
         <v>0.833</v>
       </c>
-      <c r="D71" s="31" t="n">
+      <c r="D72" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="E71" s="31" t="n">
+      <c r="E72" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="F71" s="31" t="n">
+      <c r="F72" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="G71" s="31" t="n">
+      <c r="G72" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="H71" s="35" t="inlineStr">
+      <c r="H72" s="35" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="I71" s="31" t="inlineStr">
+      <c r="I72" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J71" s="32" t="inlineStr">
+      <c r="J72" s="32" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K71" s="31" t="n">
+      <c r="K72" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L71" s="31" t="n">
+      <c r="L72" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M71" s="31" t="n">
+      <c r="M72" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="N71" s="31" t="n">
+      <c r="N72" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="O71" s="31" t="n">
+      <c r="O72" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="P71" s="31" t="n">
+      <c r="P72" s="31" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="Q71" s="34" t="inlineStr">
+      <c r="Q72" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="28" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
         <is>
           <t>Cincinnati Reds offense vs Baltimore Orioles defense</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B74" s="29" t="inlineStr">
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C74" s="29" t="inlineStr">
+      <c r="C75" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D74" s="29" t="inlineStr">
+      <c r="D75" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E74" s="29" t="inlineStr">
+      <c r="E75" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F74" s="29" t="inlineStr">
+      <c r="F75" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G74" s="29" t="inlineStr">
+      <c r="G75" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H74" s="29" t="inlineStr">
+      <c r="H75" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I74" s="29" t="inlineStr">
+      <c r="I75" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J74" s="29" t="inlineStr">
+      <c r="J75" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K74" s="29" t="inlineStr">
+      <c r="K75" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L74" s="29" t="inlineStr">
+      <c r="L75" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M74" s="29" t="inlineStr">
+      <c r="M75" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N74" s="29" t="inlineStr">
+      <c r="N75" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O74" s="29" t="inlineStr">
+      <c r="O75" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P74" s="29" t="inlineStr">
+      <c r="P75" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q74" s="29" t="inlineStr">
+      <c r="Q75" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>3.767</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H75" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>4.821</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B76" s="31" t="n">
-        <v>7.404</v>
+        <v>4</v>
       </c>
       <c r="C76" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.767</v>
+      </c>
+      <c r="D76" s="31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E76" s="31" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="F76" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G76" s="31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H76" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I76" s="31" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L76" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M76" s="31" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N76" s="31" t="n">
+        <v>4.1</v>
       </c>
       <c r="O76" s="31" t="n">
-        <v>5</v>
+        <v>4.267</v>
       </c>
       <c r="P76" s="31" t="n">
-        <v>8.833</v>
+        <v>4.821</v>
       </c>
       <c r="Q76" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="31" t="n">
-        <v>1.213</v>
+        <v>7.404</v>
       </c>
       <c r="C77" s="31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D77" s="31" t="inlineStr">
         <is>
@@ -17770,28 +17695,28 @@
         </is>
       </c>
       <c r="O77" s="31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P77" s="31" t="n">
-        <v>1.062</v>
+        <v>8.833</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>9.532</v>
+        <v>1.213</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="D78" s="31" t="inlineStr">
         <is>
@@ -17845,71 +17770,146 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>8</v>
+        <v>1.062</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="n">
+        <v>9.532</v>
+      </c>
+      <c r="C79" s="31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P79" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B79" s="31" t="n">
+      <c r="B80" s="31" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="C79" s="31" t="n">
+      <c r="C80" s="31" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D79" s="31" t="n">
+      <c r="D80" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="E79" s="31" t="n">
+      <c r="E80" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="F79" s="31" t="n">
+      <c r="F80" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G79" s="31" t="n">
+      <c r="G80" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H79" s="33" t="inlineStr">
+      <c r="H80" s="33" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
+      <c r="I80" s="31" t="inlineStr"/>
+      <c r="J80" s="33" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="K79" s="31" t="n">
+      <c r="K80" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="L79" s="31" t="n">
+      <c r="L80" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M79" s="31" t="n">
+      <c r="M80" s="31" t="n">
         <v>0.867</v>
       </c>
-      <c r="N79" s="31" t="n">
+      <c r="N80" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O79" s="31" t="n">
+      <c r="O80" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="P79" s="31" t="n">
+      <c r="P80" s="31" t="n">
         <v>0.494</v>
       </c>
-      <c r="Q79" s="34" t="inlineStr">
+      <c r="Q80" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -459,7 +459,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11106150"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -519,7 +519,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10725150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -549,7 +549,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -609,7 +609,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10763250"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 08:16</t>
+          <t>2026-07-05 10:35</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1173,174 +1173,249 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>Minnesota Twins offense vs New York Yankees defense</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>Minnesota Twins offense vs New York Yankees defense</t>
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B71" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D71" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E71" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F71" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G71" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H71" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I71" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J71" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K71" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L71" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M71" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N71" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O71" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P71" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q71" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A71" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>4.857</v>
+        <v>7.776</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E72" s="31" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G72" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J72" s="32" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="L72" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M72" s="31" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N72" s="31" t="n">
-        <v>4.8</v>
+        <v>10</v>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>3.835</v>
+        <v>7.609</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>7.776</v>
+        <v>1.061</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -1394,28 +1469,28 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>7.609</v>
+        <v>0.913</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>1.061</v>
+        <v>8.939</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -1469,319 +1544,319 @@
         </is>
       </c>
       <c r="O74" s="31" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>0.913</v>
+        <v>8.435</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>8.939</v>
+        <v>0.714</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J75" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>9</v>
+        <v>0.633</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>8.435</v>
+        <v>0.514</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="C76" s="31" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="D76" s="31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E76" s="31" t="n">
-        <v>1.267</v>
-      </c>
-      <c r="F76" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G76" s="31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J76" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M76" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N76" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O76" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Minnesota Twins defense</t>
+        </is>
+      </c>
+    </row>
     <row r="78">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Minnesota Twins defense</t>
+      <c r="A78" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F78" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G78" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H78" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I78" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J78" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K78" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L78" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M78" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N78" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O78" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P78" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q78" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B79" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C79" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D79" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E79" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F79" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G79" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H79" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I79" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J79" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K79" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L79" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M79" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N79" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O79" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P79" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q79" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A79" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="n">
+        <v>4.734</v>
+      </c>
+      <c r="C79" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H79" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O79" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P79" s="31" t="n">
+        <v>5.117</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>4.734</v>
+        <v>8.109</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D80" s="31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E80" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F80" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H80" s="32" t="inlineStr">
-        <is>
-          <t>25th</t>
+        <v>9.5</v>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="33" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L80" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M80" s="31" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="N80" s="31" t="n">
-        <v>5.25</v>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>5.6</v>
+        <v>9.5</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>5.117</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.109</v>
+        <v>1.413</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -1835,28 +1910,28 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>0.918</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>1.413</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="D82" s="31" t="inlineStr">
         <is>
@@ -1910,146 +1985,71 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>0.918</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B83" s="31" t="n">
-        <v>9.130000000000001</v>
+        <v>0.622</v>
       </c>
       <c r="C83" s="31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.333</v>
+      </c>
+      <c r="D83" s="31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E83" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H83" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J83" s="35" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L83" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M83" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N83" s="31" t="n">
+        <v>0.45</v>
       </c>
       <c r="O83" s="31" t="n">
-        <v>12.5</v>
+        <v>0.633</v>
       </c>
       <c r="P83" s="31" t="n">
-        <v>8.265000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B84" s="31" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="C84" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D84" s="31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E84" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H84" s="32" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I84" s="31" t="inlineStr"/>
-      <c r="J84" s="35" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L84" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N84" s="31" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O84" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P84" s="31" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -2972,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2989,174 +2989,249 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.618</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>5.233</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>4.792</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.618</v>
+        <v>7.826</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.233</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.6</v>
+        <v>8.667</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.833</v>
+        <v>7</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.792</v>
+        <v>7.896</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.826</v>
+        <v>1.109</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>8.667</v>
+        <v>0.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -3210,28 +3285,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.896</v>
+        <v>1.354</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.109</v>
+        <v>8.196</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.667</v>
+        <v>9.667</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -3285,315 +3360,315 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.354</v>
+        <v>7.708</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>8.196</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.15</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>6.5</v>
+        <v>0.367</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>7.708</v>
+        <v>0.447</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>5.195</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>4.461</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>5.195</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>7.533</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>4th</t>
+        <v>5.5</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.85</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>4.267</v>
+        <v>8</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.461</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.438000000000001</v>
+        <v>1.104</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -3647,28 +3722,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>8</v>
+        <v>0.333</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.651999999999999</v>
+        <v>1.043</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.104</v>
+        <v>8.458</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -3722,150 +3797,75 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>0.333</v>
+        <v>9.333</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.043</v>
+        <v>7.739</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>8.458</v>
+        <v>0.447</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J82" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="O82" s="31" t="n">
-        <v>9.333</v>
+        <v>0.6</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>7.739</v>
+        <v>0.589</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3884,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3901,174 +3901,324 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.595</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>5.266</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>7.234</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>8.603999999999999</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.595</v>
+        <v>1.213</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="32" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>6.65</v>
+        <v>1</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>5.733</v>
+        <v>2</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>5.266</v>
+        <v>1.25</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.234</v>
+        <v>8.426</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -4122,387 +4272,387 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8.603999999999999</v>
+        <v>8.208</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.213</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C73" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M73" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N73" s="31" t="n">
+        <v>1.2</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.25</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>8.426</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>8.208</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>4.089</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H77" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.747</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>9.319000000000001</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>4.089</v>
+        <v>0.896</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H79" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>1.5</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.7</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>4.467</v>
+        <v>1</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.747</v>
+        <v>1.17</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>7.792</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
         <v>9</v>
@@ -4559,221 +4709,71 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>9.319000000000001</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>0.896</v>
+        <v>0.461</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.833</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>1</v>
+        <v>0.533</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.17</v>
+        <v>0.513</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>9.276999999999999</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="35" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5704,7 +5704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5721,170 +5721,245 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Detroit Tigers offense vs Texas Rangers defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>Detroit Tigers offense vs Texas Rangers defense</t>
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.289</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>4.155</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>4.289</v>
+        <v>7.755</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
+        <v>9.333</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>5</v>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>4.633</v>
+        <v>9</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>4.155</v>
+        <v>7.673</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.755</v>
+        <v>1.02</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>9.333</v>
+        <v>2.667</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -5938,28 +6013,28 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>7.673</v>
+        <v>1.163</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.02</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>2.667</v>
+        <v>7.333</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -6013,319 +6088,319 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.163</v>
+        <v>8.571</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.633</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.9</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>12</v>
+        <v>0.733</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.571</v>
+        <v>0.792</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Texas Rangers offense vs Detroit Tigers defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>Texas Rangers offense vs Detroit Tigers defense</t>
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>4.233</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>3.987</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>4.167</v>
+        <v>7.816</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>4.233</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
+        <v>8.5</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>3.55</v>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>3.987</v>
+        <v>7.592</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>7.816</v>
+        <v>1.041</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -6379,28 +6454,28 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>7.592</v>
+        <v>0.898</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.041</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -6454,146 +6529,71 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>1</v>
+        <v>7.333</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>0.898</v>
+        <v>7.776</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.592000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.2</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>7.333</v>
+        <v>0.233</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>7.776</v>
+        <v>0.355</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D82" s="31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E82" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G82" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L82" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M82" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N82" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7606,7 +7606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6558518518518518</v>
+        <v>0.655037037037037</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-191</v>
+        <v>-190</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>170</v>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5694893617021276</v>
+        <v>0.5702145922746781</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7882,13 +7882,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6848746411483253</v>
+        <v>0.6805056603773585</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-217</v>
+        <v>-213</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-109</v>
+        <v>-112</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -217). Your call.</t>
+          <t>Model 68.1% (fair -213). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6827777777777778</v>
+        <v>0.6811111111111111</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-215</v>
+        <v>-214</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>-125</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 68.3% (fair -215). Your call.</t>
+          <t>Model 68.1% (fair -214). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3444057971014493</v>
+        <v>0.3447246376811594</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>190</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +190). Your call.</t>
+          <t>Model 34.5% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8080,13 +8080,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5986619047619047</v>
+        <v>0.5986635071090046</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-149</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8212,13 +8212,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4695744680851063</v>
+        <v>0.4730042918454936</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8259,32 +8259,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5304807692307691</v>
+        <v>0.54795</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-113</v>
+        <v>-121</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8340,17 +8340,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5512509803921568</v>
+        <v>0.4865315315315316</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-123</v>
+        <v>106</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 48.7% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8386,37 +8386,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5459999999999999</v>
+        <v>0.4740990990990991</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-120</v>
+        <v>111</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-104</v>
+        <v>122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8457,32 +8457,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4923041474654378</v>
+        <v>0.5670495412844038</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>103</v>
+        <v>-131</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>117</v>
+        <v>-118</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8523,32 +8523,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5670574074074075</v>
+        <v>0.4409361702127659</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-131</v>
+        <v>127</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-116</v>
+        <v>135</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4740990990990991</v>
+        <v>0.6204000000000001</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>111</v>
+        <v>-163</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>122</v>
+        <v>-150</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -8665,22 +8665,22 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5425442307692308</v>
+        <v>0.5266274509803921</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-119</v>
+        <v>-111</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4764383561643836</v>
+        <v>0.5475990610328638</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>110</v>
+        <v>-121</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>119</v>
+        <v>-113</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8787,32 +8787,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4379831932773109</v>
+        <v>0.5258627450980392</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>128</v>
+        <v>-111</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>138</v>
+        <v>-104</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8848,17 +8848,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -8868,17 +8868,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6204000000000001</v>
+        <v>0.4924038461538461</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-163</v>
+        <v>103</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-150</v>
+        <v>108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8911,207 +8911,9 @@
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>New York Mets @ Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>0.4919138755980862</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>103</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>109</v>
-      </c>
-      <c r="I23" s="13">
-        <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
-        <v/>
-      </c>
-      <c r="J23" s="16">
-        <f>IF($H$23="","",$F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))</f>
-        <v/>
-      </c>
-      <c r="K23" s="17">
-        <f>IF($H$23="","",MAX(0,($F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))/IF($H$23&lt;0,-100/$H$23,$H$23/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L23" s="18">
-        <f>IF($H$23="","",ROUND(MIN($K$23,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M23" s="12">
-        <f>IF($J$23="","",IF($J$23&lt;0,"Pass",IF($J$23&lt;'Settings'!$B$4,"Thin",IF($J$23&lt;0.06,"✅ Sharp band",IF($J$23&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N23" s="19" t="inlineStr">
-        <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
-        </is>
-      </c>
-      <c r="O23" s="15" t="n"/>
-      <c r="P23" s="16">
-        <f>IF(OR($H$23="",$O$23=""),"",(1+IF($H$23&lt;0,-100/$H$23,$H$23/100))/(1+IF($O$23&lt;0,-100/$O$23,$O$23/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Minnesota Twins @ New York Yankees</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>Over 8.5</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>0.5075247524752474</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>-103</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>102</v>
-      </c>
-      <c r="I24" s="13">
-        <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
-        <v/>
-      </c>
-      <c r="J24" s="16">
-        <f>IF($H$24="","",$F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))</f>
-        <v/>
-      </c>
-      <c r="K24" s="17">
-        <f>IF($H$24="","",MAX(0,($F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))/IF($H$24&lt;0,-100/$H$24,$H$24/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L24" s="18">
-        <f>IF($H$24="","",ROUND(MIN($K$24,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M24" s="12">
-        <f>IF($J$24="","",IF($J$24&lt;0,"Pass",IF($J$24&lt;'Settings'!$B$4,"Thin",IF($J$24&lt;0.06,"✅ Sharp band",IF($J$24&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N24" s="19" t="inlineStr">
-        <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
-        </is>
-      </c>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="16">
-        <f>IF(OR($H$24="",$O$24=""),"",(1+IF($H$24&lt;0,-100/$H$24,$H$24/100))/(1+IF($O$24&lt;0,-100/$O$24,$O$24/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>0.5667777777777777</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>-131</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>-125</v>
-      </c>
-      <c r="I25" s="13">
-        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
-        <v/>
-      </c>
-      <c r="J25" s="16">
-        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
-        <v/>
-      </c>
-      <c r="K25" s="17">
-        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L25" s="18">
-        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M25" s="12">
-        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N25" s="19" t="inlineStr">
-        <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
-        </is>
-      </c>
-      <c r="O25" s="15" t="n"/>
-      <c r="P25" s="16">
-        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J25">
+  <conditionalFormatting sqref="J5:J22">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9133,7 +8935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9277,13 +9079,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4919138755980862</v>
+        <v>0.4924038461538461</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>103</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9343,7 +9145,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5080673076923077</v>
+        <v>0.5075999999999999</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-103</v>
@@ -9409,13 +9211,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3641</v>
+        <v>0.3654</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9439,7 +9241,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9475,13 +9277,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6359</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-175</v>
+        <v>-174</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9505,7 +9307,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9541,10 +9343,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3441481481481481</v>
+        <v>0.3449629629629629</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>170</v>
@@ -9571,7 +9373,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +191). Your call.</t>
+          <t>Model 34.5% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9607,10 +9409,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6558518518518518</v>
+        <v>0.655037037037037</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-191</v>
+        <v>-190</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>170</v>
@@ -9637,7 +9439,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9811,7 +9613,7 @@
         <v>115</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9877,7 +9679,7 @@
         <v>-115</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10003,13 +9805,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5670574074074075</v>
+        <v>0.5670495412844038</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-131</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-116</v>
+        <v>-118</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10069,13 +9871,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5512509803921568</v>
+        <v>0.54795</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-123</v>
+        <v>-121</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10099,7 +9901,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10135,10 +9937,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4487623762376238</v>
+        <v>0.452029702970297</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>102</v>
@@ -10165,7 +9967,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10201,13 +10003,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.50145</v>
+        <v>0.5001534653465347</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-101</v>
+        <v>-100</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10231,7 +10033,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10267,10 +10069,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.49855</v>
+        <v>0.49985</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -10297,7 +10099,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10333,13 +10135,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4923041474654378</v>
+        <v>0.4865315315315316</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10363,7 +10165,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 48.7% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10399,13 +10201,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5077090909090909</v>
+        <v>0.5134990990990991</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-103</v>
+        <v>-106</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10429,7 +10231,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.3% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10461,17 +10263,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5075247524752474</v>
+        <v>0.4281</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-103</v>
+        <v>134</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10495,7 +10297,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10527,14 +10329,14 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.492470588235294</v>
+        <v>0.5719000000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>103</v>
+        <v>-134</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-104</v>
@@ -10561,7 +10363,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10597,10 +10399,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3171863117870723</v>
+        <v>0.3188973384030419</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>163</v>
@@ -10627,7 +10429,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 31.7% (fair +215). Your call.</t>
+          <t>Model 31.9% (fair +214). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10663,10 +10465,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6827777777777778</v>
+        <v>0.6811111111111111</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-215</v>
+        <v>-214</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-125</v>
@@ -10693,7 +10495,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 68.3% (fair -215). Your call.</t>
+          <t>Model 68.1% (fair -214). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10729,13 +10531,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4695744680851063</v>
+        <v>0.4730042918454936</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10759,7 +10561,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10795,13 +10597,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5304302521008404</v>
+        <v>0.5269521367521368</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-138</v>
+        <v>-134</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10825,7 +10627,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10857,17 +10659,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4384</v>
+        <v>0.5321</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>128</v>
+        <v>-114</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10891,7 +10693,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10923,17 +10725,17 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5616</v>
+        <v>0.4679</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-128</v>
+        <v>114</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-104</v>
+        <v>112</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -10957,7 +10759,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -10993,13 +10795,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3151417004048583</v>
+        <v>0.31952</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11023,7 +10825,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 31.5% (fair +217). Your call.</t>
+          <t>Model 32.0% (fair +213). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11059,13 +10861,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6848746411483253</v>
+        <v>0.6805056603773585</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-217</v>
+        <v>-213</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-109</v>
+        <v>-112</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11089,7 +10891,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -217). Your call.</t>
+          <t>Model 68.1% (fair -213). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11125,13 +10927,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4379831932773109</v>
+        <v>0.4409361702127659</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11155,7 +10957,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11191,13 +10993,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5620416666666667</v>
+        <v>0.5590739495798319</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-140</v>
+        <v>-138</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11221,7 +11023,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11263,7 +11065,7 @@
         <v>-170</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11389,13 +11191,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4013600000000001</v>
+        <v>0.4013438735177866</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>149</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11455,13 +11257,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5986619047619047</v>
+        <v>0.5986635071090046</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-149</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11521,13 +11323,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5667777777777777</v>
+        <v>0.5679193832599119</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>-131</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11551,7 +11353,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11587,7 +11389,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.433215859030837</v>
+        <v>0.4320704845814978</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>131</v>
@@ -11617,7 +11419,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11649,17 +11451,17 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5507</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-123</v>
+        <v>-102</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-102</v>
+        <v>115</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11683,7 +11485,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11715,14 +11517,14 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4493</v>
+        <v>0.4955000000000001</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>113</v>
@@ -11749,7 +11551,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11766,32 +11568,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.546611111111111</v>
+        <v>0.507204854368932</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-121</v>
+        <v>-103</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-125</v>
+        <v>-106</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -11815,7 +11617,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -11832,32 +11634,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4534234234234235</v>
+        <v>0.4928155339805826</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -11881,7 +11683,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -11908,22 +11710,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.5235844036697248</v>
+        <v>0.5266274509803921</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-118</v>
+        <v>-104</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -11947,7 +11749,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -11974,22 +11776,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4764383561643836</v>
+        <v>0.4733823529411765</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12013,7 +11815,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12030,7 +11832,7 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -12040,22 +11842,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5304807692307691</v>
+        <v>0.5475990610328638</v>
       </c>
       <c r="G47" s="14" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H47" s="15" t="n">
         <v>-113</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>108</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12079,7 +11881,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12096,7 +11898,7 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
@@ -12106,22 +11908,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.469478431372549</v>
+        <v>0.4524170616113743</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-104</v>
+        <v>111</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12145,7 +11947,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12172,22 +11974,22 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5425442307692308</v>
+        <v>0.5258627450980392</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-119</v>
+        <v>-111</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12211,7 +12013,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12238,22 +12040,22 @@
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4574757281553398</v>
+        <v>0.4741666666666667</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12277,7 +12079,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12294,33 +12096,31 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5459999999999999</v>
+        <v>0.4335</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-120</v>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-104</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="H51" s="15" t="n"/>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
         <v/>
@@ -12343,7 +12143,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12360,33 +12160,31 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4539800995024876</v>
+        <v>0.5665</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>120</v>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>101</v>
-      </c>
+        <v>-131</v>
+      </c>
+      <c r="H52" s="15" t="n"/>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
         <v/>
@@ -12409,7 +12207,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12426,7 +12224,7 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -12441,16 +12239,18 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4337</v>
+        <v>0.5286966824644549</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>131</v>
-      </c>
-      <c r="H53" s="15" t="n"/>
+        <v>-112</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-111</v>
+      </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
         <v/>
@@ -12473,7 +12273,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12490,7 +12290,7 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
@@ -12505,16 +12305,18 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5663</v>
+        <v>0.4712980769230769</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-131</v>
-      </c>
-      <c r="H54" s="15" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
         <v/>
@@ -12537,7 +12339,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12564,22 +12366,22 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5305379146919431</v>
+        <v>0.4055</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-113</v>
+        <v>147</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-111</v>
+        <v>122</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12603,7 +12405,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 40.6% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12630,22 +12432,22 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4694258373205742</v>
+        <v>0.5945</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>113</v>
+        <v>-147</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12669,7 +12471,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12686,33 +12488,31 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4727</v>
+        <v>0.4536</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>112</v>
-      </c>
-      <c r="H57" s="15" t="n">
         <v>120</v>
       </c>
+      <c r="H57" s="15" t="n"/>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
         <v/>
@@ -12735,7 +12535,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -12752,33 +12552,31 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5273</v>
+        <v>0.5464</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H58" s="15" t="n">
-        <v>103</v>
-      </c>
+        <v>-120</v>
+      </c>
+      <c r="H58" s="15" t="n"/>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
         <v/>
@@ -12801,7 +12599,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -12818,12 +12616,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -12833,14 +12631,14 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4513</v>
+        <v>0.4615</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -12865,7 +12663,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -12882,12 +12680,12 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -12897,14 +12695,14 @@
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5487</v>
+        <v>0.5385</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -12929,7 +12727,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -12956,21 +12754,23 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4656</v>
+        <v>0.2601</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>115</v>
-      </c>
-      <c r="H61" s="15" t="n"/>
+        <v>284</v>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
         <v/>
@@ -12993,7 +12793,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 26.0% (fair +284). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13020,21 +12820,23 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5344</v>
+        <v>0.7399</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H62" s="15" t="n"/>
+        <v>-284</v>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>125</v>
+      </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
         <v/>
@@ -13057,7 +12859,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 74.0% (fair -284). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13074,33 +12876,31 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.263</v>
+        <v>0.406</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>280</v>
-      </c>
-      <c r="H63" s="15" t="n">
-        <v>120</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
         <v/>
@@ -13123,7 +12923,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 26.3% (fair +280). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13140,33 +12940,31 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.737</v>
+        <v>0.594</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-280</v>
-      </c>
-      <c r="H64" s="15" t="n">
-        <v>103</v>
-      </c>
+        <v>-146</v>
+      </c>
+      <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
         <v/>
@@ -13189,7 +12987,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 73.7% (fair -280). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13206,12 +13004,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -13221,16 +13019,18 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4052</v>
+        <v>0.5702145922746781</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>147</v>
-      </c>
-      <c r="H65" s="15" t="n"/>
+        <v>-133</v>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>133</v>
+      </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
         <v/>
@@ -13253,7 +13053,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13270,12 +13070,12 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -13285,14 +13085,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5948</v>
+        <v>0.4298</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-147</v>
+        <v>133</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13317,7 +13117,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13344,22 +13144,22 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5694893617021276</v>
+        <v>0.5028</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-132</v>
+        <v>-101</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -13383,7 +13183,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13410,21 +13210,23 @@
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4305</v>
+        <v>0.4972</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>132</v>
-      </c>
-      <c r="H68" s="15" t="n"/>
+        <v>101</v>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>112</v>
+      </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
         <v/>
@@ -13447,7 +13249,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +132). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13459,37 +13261,37 @@
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.3858</v>
+        <v>0.6204000000000001</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>159</v>
+        <v>-163</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>126</v>
+        <v>-150</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -13513,7 +13315,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13525,37 +13327,37 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.6142000000000001</v>
+        <v>0.3796</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-159</v>
+        <v>163</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-104</v>
+        <v>150</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -13579,7 +13381,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13596,12 +13398,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -13611,17 +13413,17 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.6204000000000001</v>
+        <v>0.4740990990990991</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-163</v>
+        <v>111</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-150</v>
+        <v>122</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -13645,7 +13447,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13662,12 +13464,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -13677,17 +13479,17 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.3796</v>
+        <v>0.5259189189189188</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>163</v>
+        <v>-111</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>150</v>
+        <v>-122</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -13711,7 +13513,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -13728,12 +13530,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -13743,17 +13545,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4740990990990991</v>
+        <v>0.4485462555066079</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -13777,7 +13579,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13794,12 +13596,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -13809,17 +13611,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5259189189189188</v>
+        <v>0.5514781512605041</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-111</v>
+        <v>-123</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-122</v>
+        <v>-138</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -13843,7 +13645,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -13860,12 +13662,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -13875,17 +13677,17 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.445726872246696</v>
+        <v>0.4872</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -13909,7 +13711,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -13926,12 +13728,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -13941,17 +13743,17 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5542819672131147</v>
+        <v>0.5128</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-124</v>
+        <v>-105</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-144</v>
+        <v>-117</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -13975,7 +13777,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -13992,12 +13794,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -14007,17 +13809,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.482</v>
+        <v>0.5235345622119816</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>107</v>
+        <v>-110</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>133</v>
+        <v>-117</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14041,7 +13843,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14058,12 +13860,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -14073,17 +13875,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.518</v>
+        <v>0.4764903846153846</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-107</v>
+        <v>110</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-117</v>
+        <v>108</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14107,7 +13909,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14124,12 +13926,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -14139,17 +13941,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5273863849765258</v>
+        <v>0.4745098039215686</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-112</v>
+        <v>111</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14173,7 +13975,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14190,12 +13992,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -14205,17 +14007,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4725821596244131</v>
+        <v>0.5254876777251185</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>112</v>
+        <v>-111</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>113</v>
+        <v>-111</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14239,7 +14041,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14256,12 +14058,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -14271,17 +14073,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4609</v>
+        <v>0.4881</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>4900</v>
+        <v>100</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14305,7 +14107,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14322,12 +14124,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -14337,17 +14139,17 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5391</v>
+        <v>0.5118941176470588</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-117</v>
+        <v>-105</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-113</v>
+        <v>-104</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14371,7 +14173,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14388,12 +14190,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -14403,17 +14205,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4878</v>
+        <v>0.3447246376811594</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14437,7 +14239,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 34.5% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14454,12 +14256,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -14469,17 +14271,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5121999999999999</v>
+        <v>0.6552507246376811</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-105</v>
+        <v>-190</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-104</v>
+        <v>-245</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14503,7 +14305,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14512,141 +14314,9 @@
         <v/>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>0.3444057971014493</v>
-      </c>
-      <c r="G85" s="14" t="n">
-        <v>190</v>
-      </c>
-      <c r="H85" s="15" t="n">
-        <v>245</v>
-      </c>
-      <c r="I85" s="13">
-        <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
-        <v/>
-      </c>
-      <c r="J85" s="16">
-        <f>IF($H$85="","",$F$85*IF($H$85&lt;0,-100/$H$85,$H$85/100)-(1-$F$85))</f>
-        <v/>
-      </c>
-      <c r="K85" s="17">
-        <f>IF($H$85="","",MAX(0,($F$85*IF($H$85&lt;0,-100/$H$85,$H$85/100)-(1-$F$85))/IF($H$85&lt;0,-100/$H$85,$H$85/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L85" s="18">
-        <f>IF($H$85="","",ROUND(MIN($K$85,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M85" s="12">
-        <f>IF($J$85="","",IF($J$85&lt;0,"Pass",IF($J$85&lt;'Settings'!$B$4,"Thin",IF($J$85&lt;0.06,"✅ Sharp band",IF($J$85&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N85" s="19" t="inlineStr">
-        <is>
-          <t>Model 34.4% (fair +190). Your call.</t>
-        </is>
-      </c>
-      <c r="O85" s="15" t="n"/>
-      <c r="P85" s="16">
-        <f>IF(OR($H$85="",$O$85=""),"",(1+IF($H$85&lt;0,-100/$H$85,$H$85/100))/(1+IF($O$85&lt;0,-100/$O$85,$O$85/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="inlineStr">
-        <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="C86" s="20" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D86" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E86" s="20" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="n">
-        <v>0.6556057971014493</v>
-      </c>
-      <c r="G86" s="14" t="n">
-        <v>-190</v>
-      </c>
-      <c r="H86" s="15" t="n">
-        <v>-245</v>
-      </c>
-      <c r="I86" s="13">
-        <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
-        <v/>
-      </c>
-      <c r="J86" s="16">
-        <f>IF($H$86="","",$F$86*IF($H$86&lt;0,-100/$H$86,$H$86/100)-(1-$F$86))</f>
-        <v/>
-      </c>
-      <c r="K86" s="17">
-        <f>IF($H$86="","",MAX(0,($F$86*IF($H$86&lt;0,-100/$H$86,$H$86/100)-(1-$F$86))/IF($H$86&lt;0,-100/$H$86,$H$86/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L86" s="18">
-        <f>IF($H$86="","",ROUND(MIN($K$86,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M86" s="12">
-        <f>IF($J$86="","",IF($J$86&lt;0,"Pass",IF($J$86&lt;'Settings'!$B$4,"Thin",IF($J$86&lt;0.06,"✅ Sharp band",IF($J$86&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N86" s="19" t="inlineStr">
-        <is>
-          <t>Model 65.6% (fair -190). Your call.</t>
-        </is>
-      </c>
-      <c r="O86" s="15" t="n"/>
-      <c r="P86" s="16">
-        <f>IF(OR($H$86="",$O$86=""),"",(1+IF($H$86&lt;0,-100/$H$86,$H$86/100))/(1+IF($O$86&lt;0,-100/$O$86,$O$86/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J86">
+  <conditionalFormatting sqref="J5:J84">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -399,7 +399,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -549,7 +549,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10763250"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -609,7 +609,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10363200"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 12:07</t>
+          <t>2026-07-05 14:05</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3901,174 +3901,249 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.595</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>5.266</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>4.595</v>
+        <v>7.234</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="32" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>6.65</v>
+        <v>9</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>5.733</v>
+        <v>5</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>5.266</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.234</v>
+        <v>1.213</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -4122,28 +4197,28 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>8.603999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.213</v>
+        <v>8.426</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -4197,315 +4272,315 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.25</v>
+        <v>8.208</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.426</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>1.2</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>11.5</v>
+        <v>0.9</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.208</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>4.089</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H77" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.747</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>4.089</v>
+        <v>7.792</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>9</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>4.7</v>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>4.467</v>
+        <v>7</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>4.747</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -4559,28 +4634,28 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>9.319000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>0.896</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -4634,146 +4709,71 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.17</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.021000000000001</v>
+        <v>0.461</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.833</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>12</v>
+        <v>0.533</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>9.276999999999999</v>
+        <v>0.513</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D82" s="31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F82" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M82" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N82" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5704,7 +5704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5721,245 +5721,170 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="28" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>Detroit Tigers offense vs Texas Rangers defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="29" t="inlineStr">
+      <c r="C68" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="29" t="inlineStr">
+      <c r="D68" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="29" t="inlineStr">
+      <c r="E68" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="29" t="inlineStr">
+      <c r="F68" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="29" t="inlineStr">
+      <c r="G68" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="29" t="inlineStr">
+      <c r="H68" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="29" t="inlineStr">
+      <c r="I68" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="29" t="inlineStr">
+      <c r="J68" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="29" t="inlineStr">
+      <c r="K68" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="29" t="inlineStr">
+      <c r="L68" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="29" t="inlineStr">
+      <c r="M68" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="29" t="inlineStr">
+      <c r="N68" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="29" t="inlineStr">
+      <c r="O68" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="29" t="inlineStr">
+      <c r="P68" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="29" t="inlineStr">
+      <c r="Q68" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="31" t="n">
-        <v>4.289</v>
-      </c>
-      <c r="C68" s="31" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="D68" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E68" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F68" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G68" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I68" s="31" t="inlineStr"/>
-      <c r="J68" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K68" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L68" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="M68" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="N68" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O68" s="31" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="P68" s="31" t="n">
-        <v>4.155</v>
-      </c>
-      <c r="Q68" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="31" t="n">
-        <v>7.755</v>
+        <v>4.289</v>
       </c>
       <c r="C69" s="31" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="D69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.033</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="O69" s="31" t="n">
-        <v>9</v>
+        <v>4.633</v>
       </c>
       <c r="P69" s="31" t="n">
-        <v>7.673</v>
+        <v>4.155</v>
       </c>
       <c r="Q69" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>1.02</v>
+        <v>7.755</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>2.667</v>
+        <v>9.333</v>
       </c>
       <c r="D70" s="31" t="inlineStr">
         <is>
@@ -6013,28 +5938,28 @@
         </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>1.163</v>
+        <v>7.673</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>7.333</v>
+        <v>2.667</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -6088,319 +6013,319 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>8.571</v>
+        <v>1.163</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="C72" s="31" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P72" s="31" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="31" t="n">
+      <c r="B73" s="31" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="C72" s="31" t="n">
+      <c r="C73" s="31" t="n">
         <v>0.633</v>
       </c>
-      <c r="D72" s="31" t="n">
+      <c r="D73" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="E72" s="31" t="n">
+      <c r="E73" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="F72" s="31" t="n">
+      <c r="F73" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="G72" s="31" t="n">
+      <c r="G73" s="31" t="n">
         <v>1.4</v>
       </c>
-      <c r="H72" s="35" t="inlineStr">
+      <c r="H73" s="35" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="I72" s="31" t="inlineStr">
+      <c r="I73" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J72" s="33" t="inlineStr">
+      <c r="J73" s="33" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K72" s="31" t="n">
+      <c r="K73" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L72" s="31" t="n">
+      <c r="L73" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="M72" s="31" t="n">
+      <c r="M73" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="N72" s="31" t="n">
+      <c r="N73" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O72" s="31" t="n">
+      <c r="O73" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="P72" s="31" t="n">
+      <c r="P73" s="31" t="n">
         <v>0.792</v>
       </c>
-      <c r="Q72" s="34" t="inlineStr">
+      <c r="Q73" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="28" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
         <is>
           <t>Texas Rangers offense vs Detroit Tigers defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B76" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="29" t="inlineStr">
+      <c r="C76" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="29" t="inlineStr">
+      <c r="D76" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="29" t="inlineStr">
+      <c r="E76" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="29" t="inlineStr">
+      <c r="F76" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="29" t="inlineStr">
+      <c r="G76" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="29" t="inlineStr">
+      <c r="H76" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="29" t="inlineStr">
+      <c r="I76" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="29" t="inlineStr">
+      <c r="J76" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="29" t="inlineStr">
+      <c r="K76" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="29" t="inlineStr">
+      <c r="L76" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="29" t="inlineStr">
+      <c r="M76" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="29" t="inlineStr">
+      <c r="N76" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="29" t="inlineStr">
+      <c r="O76" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="29" t="inlineStr">
+      <c r="P76" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="29" t="inlineStr">
+      <c r="Q76" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="C76" s="31" t="n">
-        <v>4.233</v>
-      </c>
-      <c r="D76" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E76" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F76" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G76" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H76" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M76" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N76" s="31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O76" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>3.987</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="31" t="n">
-        <v>7.816</v>
+        <v>4.167</v>
       </c>
       <c r="C77" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.233</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>3.55</v>
       </c>
       <c r="O77" s="31" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P77" s="31" t="n">
-        <v>7.592</v>
+        <v>3.987</v>
       </c>
       <c r="Q77" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>1.041</v>
+        <v>7.816</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="D78" s="31" t="inlineStr">
         <is>
@@ -6454,28 +6379,28 @@
         </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>0.898</v>
+        <v>7.592</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>8.592000000000001</v>
+        <v>1.041</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -6529,71 +6454,146 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>7.333</v>
+        <v>1</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>7.776</v>
+        <v>0.898</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="n">
+        <v>8.592000000000001</v>
+      </c>
+      <c r="C80" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="31" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="31" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="P80" s="31" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="Q80" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="31" t="n">
+      <c r="B81" s="31" t="n">
         <v>0.597</v>
       </c>
-      <c r="C80" s="31" t="n">
+      <c r="C81" s="31" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D80" s="31" t="n">
+      <c r="D81" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="E80" s="31" t="n">
+      <c r="E81" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="F80" s="31" t="n">
+      <c r="F81" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G80" s="31" t="n">
+      <c r="G81" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="32" t="inlineStr">
+      <c r="H81" s="32" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="K80" s="31" t="n">
+      <c r="K81" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L80" s="31" t="n">
+      <c r="L81" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="M80" s="31" t="n">
+      <c r="M81" s="31" t="n">
         <v>0.267</v>
       </c>
-      <c r="N80" s="31" t="n">
+      <c r="N81" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="O80" s="31" t="n">
+      <c r="O81" s="31" t="n">
         <v>0.233</v>
       </c>
-      <c r="P80" s="31" t="n">
+      <c r="P81" s="31" t="n">
         <v>0.355</v>
       </c>
-      <c r="Q80" s="34" t="inlineStr">
+      <c r="Q81" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7731,12 +7731,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6558555133079847</v>
+        <v>0.6258052434456929</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-191</v>
+        <v>-167</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7812,17 +7812,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6128838951310862</v>
+        <v>0.6525390625</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-158</v>
+        <v>-188</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7863,29 +7863,29 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5695154185022027</v>
+        <v>0.6829515418502202</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-132</v>
+        <v>-215</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>127</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 68.3% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7929,32 +7929,32 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6783818181818182</v>
+        <v>0.5745945945945947</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-211</v>
+        <v>-135</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-120</v>
+        <v>122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 67.8% (fair -211). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6809017699115045</v>
+        <v>0.6872489082969432</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-213</v>
+        <v>-220</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-126</v>
+        <v>-129</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 68.1% (fair -213). Your call.</t>
+          <t>Model 68.7% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3447246376811594</v>
+        <v>0.3444057971014493</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>190</v>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 34.4% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8146,13 +8146,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5987177033492822</v>
+        <v>0.6039241706161137</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-149</v>
+        <v>-152</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 60.4% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8254,17 +8254,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8274,17 +8274,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.482511013215859</v>
+        <v>0.4976712328767124</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8325,32 +8325,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5670607655502392</v>
+        <v>0.4823555555555555</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-131</v>
+        <v>107</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-109</v>
+        <v>125</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8391,32 +8391,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5476313725490196</v>
+        <v>0.4886036036036037</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-121</v>
+        <v>105</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-104</v>
+        <v>122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5572903846153845</v>
+        <v>0.5588480769230769</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-108</v>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8523,32 +8523,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4909174311926606</v>
+        <v>0.5670302325581396</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>104</v>
+        <v>-131</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>118</v>
+        <v>-115</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4704405286343613</v>
+        <v>0.4417226890756302</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros -1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.3871111111111111</v>
+        <v>0.4419574468085106</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5525859154929578</v>
+        <v>0.554752534562212</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-124</v>
+        <v>-125</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8782,17 +8782,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -8802,17 +8802,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4404661016949152</v>
+        <v>0.6264375000000001</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>127</v>
+        <v>-168</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>136</v>
+        <v>-156</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 62.6% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8848,17 +8848,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -8868,17 +8868,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6227812500000001</v>
+        <v>0.51075</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-165</v>
+        <v>-104</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-156</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5052</v>
+        <v>0.51075</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>100</v>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9145,13 +9145,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4948</v>
+        <v>0.4892307692307692</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3641</v>
+        <v>0.3599</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>133</v>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
+          <t>Model 36.0% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9277,13 +9277,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6359</v>
+        <v>0.6401</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-175</v>
+        <v>-178</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>-105</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 64.0% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9343,10 +9343,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3441428571428572</v>
+        <v>0.3474642857142857</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>180</v>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +191). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9409,13 +9409,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6558555133079847</v>
+        <v>0.6525390625</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-191</v>
+        <v>-188</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
@@ -9613,7 +9613,7 @@
         <v>115</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
@@ -9679,7 +9679,7 @@
         <v>-115</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9805,13 +9805,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5670607655502392</v>
+        <v>0.5670302325581396</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-131</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-109</v>
+        <v>-115</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5572903846153845</v>
+        <v>0.5588480769230769</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-108</v>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9937,13 +9937,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4427184466019418</v>
+        <v>0.4411538461538461</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10009,7 +10009,7 @@
         <v>137</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10135,13 +10135,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4909174311926606</v>
+        <v>0.4823555555555555</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10201,13 +10201,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5090727272727272</v>
+        <v>0.5176592920353983</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-104</v>
+        <v>-107</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-120</v>
+        <v>-126</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10267,13 +10267,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5202</v>
+        <v>0.5091</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4798</v>
+        <v>0.4909</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10399,13 +10399,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3191011235955056</v>
+        <v>0.3170342205323194</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 31.9% (fair +213). Your call.</t>
+          <t>Model 31.7% (fair +215). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10465,13 +10465,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6809017699115045</v>
+        <v>0.6829515418502202</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-213</v>
+        <v>-215</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-126</v>
+        <v>127</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 68.1% (fair -213). Your call.</t>
+          <t>Model 68.3% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10531,13 +10531,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.482511013215859</v>
+        <v>0.4886036036036037</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10597,13 +10597,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5175</v>
+        <v>0.5113558558558559</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-107</v>
+        <v>-105</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10663,13 +10663,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.521</v>
+        <v>0.5199</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10729,13 +10729,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.479</v>
+        <v>0.4801</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>127</v>
+        <v>-105</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.321596958174905</v>
+        <v>0.3127376425855514</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>163</v>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 32.2% (fair +211). Your call.</t>
+          <t>Model 31.3% (fair +220). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6783818181818182</v>
+        <v>0.6872489082969432</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-211</v>
+        <v>-220</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-120</v>
+        <v>-129</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 67.8% (fair -211). Your call.</t>
+          <t>Model 68.7% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -10927,13 +10927,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4404661016949152</v>
+        <v>0.4419574468085106</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -10993,13 +10993,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5595378151260504</v>
+        <v>0.5580610169491526</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-138</v>
+        <v>-136</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11059,13 +11059,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.6408</v>
+        <v>0.6323</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-178</v>
+        <v>-172</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -178). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11125,10 +11125,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.3592</v>
+        <v>0.3677</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>105</v>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +178). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4013043478260869</v>
+        <v>0.3960546875</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 39.6% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11257,13 +11257,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5987177033492822</v>
+        <v>0.6039241706161137</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-149</v>
+        <v>-152</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 60.4% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11323,10 +11323,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5683110132158591</v>
+        <v>0.566520704845815</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>-127</v>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -132). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11389,13 +11389,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4316740088105727</v>
+        <v>0.4335111111111111</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +132). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-124</v>
+        <v>-102</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>117</v>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4461000000000001</v>
+        <v>0.4955000000000001</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>113</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11587,13 +11587,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4866826923076923</v>
+        <v>0.4878260869565217</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -11653,13 +11653,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5133215686274509</v>
+        <v>0.5122043478260869</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>-105</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-104</v>
+        <v>-107</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -11715,17 +11715,17 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.5118</v>
+        <v>0.4541</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-105</v>
+        <v>120</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -11781,17 +11781,17 @@
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4882</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>105</v>
+        <v>-120</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3871111111111111</v>
+        <v>0.3741851851851852</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>170</v>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 37.4% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6128838951310862</v>
+        <v>0.6258052434456929</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-158</v>
+        <v>-167</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>167</v>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -11983,13 +11983,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5525859154929578</v>
+        <v>0.554752534562212</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-124</v>
+        <v>-125</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12049,13 +12049,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4474418604651163</v>
+        <v>0.4452534562211982</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +123). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12111,17 +12111,17 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5476313725490196</v>
+        <v>0.4739</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-121</v>
+        <v>111</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-104</v>
+        <v>107</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12177,17 +12177,17 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4523529411764706</v>
+        <v>0.5261</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>121</v>
+        <v>-111</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12513,7 +12513,7 @@
         <v>147</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -12579,7 +12579,7 @@
         <v>-147</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>101</v>
+        <v>-101</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4656</v>
+        <v>0.4632</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -12831,10 +12831,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5344</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -12895,13 +12895,13 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.263</v>
+        <v>0.2592</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 26.3% (fair +280). Your call.</t>
+          <t>Model 25.9% (fair +286). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -12961,13 +12961,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.737</v>
+        <v>0.7408</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-280</v>
+        <v>-286</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>101</v>
+        <v>-101</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 73.7% (fair -280). Your call.</t>
+          <t>Model 74.1% (fair -286). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13027,10 +13027,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4052</v>
+        <v>0.406</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13091,10 +13091,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5948</v>
+        <v>0.594</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-147</v>
+        <v>-146</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13155,13 +13155,13 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5695154185022027</v>
+        <v>0.5745945945945947</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-132</v>
+        <v>-135</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13221,10 +13221,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4305</v>
+        <v>0.4254</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +132). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13285,13 +13285,13 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4854</v>
+        <v>0.5026</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>106</v>
+        <v>-101</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -13315,7 +13315,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13351,13 +13351,13 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4974</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-106</v>
+        <v>101</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>127</v>
+        <v>-105</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -13381,7 +13381,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13417,10 +13417,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.6227812500000001</v>
+        <v>0.6264375000000001</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-165</v>
+        <v>-168</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>-156</v>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 62.6% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13483,13 +13483,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.3772</v>
+        <v>0.3735546875</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 37.4% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -13549,13 +13549,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4704405286343613</v>
+        <v>0.4976712328767124</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.529545945945946</v>
+        <v>0.5023432432432432</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-113</v>
+        <v>-101</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>-122</v>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -13681,13 +13681,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4458590308370044</v>
+        <v>0.4417226890756302</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -13747,13 +13747,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5541691358024692</v>
+        <v>0.5583201680672268</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-124</v>
+        <v>-126</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-143</v>
+        <v>-138</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5273626728110599</v>
+        <v>0.5133276995305164</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14011,13 +14011,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4726291079812207</v>
+        <v>0.4866826923076923</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4848529411764705</v>
+        <v>0.4843627450980392</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>106</v>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5151058823529411</v>
+        <v>0.5156666666666667</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>-106</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14341,7 +14341,7 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.3447246376811594</v>
+        <v>0.3444057971014493</v>
       </c>
       <c r="G85" s="14" t="n">
         <v>190</v>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 34.4% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.6552507246376811</v>
+        <v>0.6556057971014493</v>
       </c>
       <c r="G86" s="14" t="n">
         <v>-190</v>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 65.6% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15914,7 +15914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15931,170 +15931,320 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>5.085</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.433</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>8.811999999999999</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>5.085</v>
+        <v>1.188</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>3</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.5</v>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.733</v>
+        <v>3.5</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>5.125</v>
+        <v>1.56</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.811999999999999</v>
+        <v>9.708</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -16148,394 +16298,394 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>9.039999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.188</v>
+        <v>0.545</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.4</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="32" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>3.5</v>
+        <v>0.433</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.56</v>
+        <v>0.41</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>9.708</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J77" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.768</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="P74" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H75" s="32" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="32" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="P78" s="31" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>5.275</v>
+        <v>1.26</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J79" s="32" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>5.567</v>
+        <v>1</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.768</v>
+        <v>0.896</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.52</v>
+        <v>7.98</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -16589,221 +16739,71 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.792</v>
+        <v>9.292</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.26</v>
+        <v>0.833</v>
       </c>
       <c r="C81" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M81" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>0.896</v>
+        <v>0.416</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>9.292</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -519,7 +519,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10687050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 14:05</t>
+          <t>2026-07-05 15:31</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2989,174 +2989,249 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.618</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>5.233</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>4.792</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.618</v>
+        <v>7.826</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.233</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.6</v>
+        <v>8.667</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.833</v>
+        <v>7</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.792</v>
+        <v>7.896</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.826</v>
+        <v>1.109</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>8.667</v>
+        <v>0.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -3210,28 +3285,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.896</v>
+        <v>1.354</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.109</v>
+        <v>8.196</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.667</v>
+        <v>9.667</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -3285,315 +3360,315 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.354</v>
+        <v>7.708</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>8.196</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.15</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>6.5</v>
+        <v>0.367</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>7.708</v>
+        <v>0.447</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>5.195</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>4.461</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>5.195</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>7.533</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>4th</t>
+        <v>5.5</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.85</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>4.267</v>
+        <v>8</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.461</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.438000000000001</v>
+        <v>1.104</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -3647,28 +3722,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>8</v>
+        <v>0.333</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.651999999999999</v>
+        <v>1.043</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.104</v>
+        <v>8.458</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -3722,150 +3797,75 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>0.333</v>
+        <v>9.333</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.043</v>
+        <v>7.739</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>8.458</v>
+        <v>0.447</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J82" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="O82" s="31" t="n">
-        <v>9.333</v>
+        <v>0.6</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>7.739</v>
+        <v>0.589</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7606,7 +7606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7858,17 +7858,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -7878,17 +7878,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Toronto Blue Jays +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6829515418502202</v>
+        <v>0.5872834645669291</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-215</v>
+        <v>-142</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 68.3% (fair -215). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5745945945945947</v>
+        <v>0.5710810810810811</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-135</v>
+        <v>-133</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>122</v>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6872489082969432</v>
+        <v>0.6829410714285714</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-220</v>
+        <v>-215</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-129</v>
+        <v>-124</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 68.7% (fair -220). Your call.</t>
+          <t>Model 68.3% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8056,37 +8056,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3444057971014493</v>
+        <v>0.6870235807860262</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>190</v>
+        <v>-220</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>245</v>
+        <v>-129</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +190). Your call.</t>
+          <t>Model 68.7% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8122,37 +8122,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6039241706161137</v>
+        <v>0.3307536231884058</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-152</v>
+        <v>202</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-111</v>
+        <v>245</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -152). Your call.</t>
+          <t>Model 33.1% (fair +202). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8188,17 +8188,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8208,17 +8208,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>San Francisco Giants -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4329644268774703</v>
+        <v>0.4127037037037037</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8254,37 +8254,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4976712328767124</v>
+        <v>0.598694930875576</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>101</v>
+        <v>-149</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>119</v>
+        <v>-117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8320,17 +8320,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8340,17 +8340,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4823555555555555</v>
+        <v>0.5002739726027396</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>107</v>
+        <v>-100</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4886036036036037</v>
+        <v>0.488963963963964</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>105</v>
@@ -8457,12 +8457,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8472,17 +8472,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5588480769230769</v>
+        <v>0.4823555555555555</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-127</v>
+        <v>107</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-108</v>
+        <v>125</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8538,17 +8538,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5670302325581396</v>
+        <v>0.4259683794466403</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-131</v>
+        <v>135</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-115</v>
+        <v>153</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8584,17 +8584,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4417226890756302</v>
+        <v>0.5588480769230769</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>126</v>
+        <v>-127</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>138</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4419574468085106</v>
+        <v>0.5740372093023256</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>126</v>
+        <v>-135</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>135</v>
+        <v>-115</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8716,37 +8716,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.554752534562212</v>
+        <v>0.5309</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-125</v>
+        <v>-113</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-117</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -8802,17 +8802,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.6264375000000001</v>
+        <v>0.4497863247863248</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-168</v>
+        <v>122</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-156</v>
+        <v>134</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -168). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8848,37 +8848,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.51075</v>
+        <v>0.5373067961165049</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-104</v>
+        <v>-116</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8911,9 +8911,471 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Cubs -1.5</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.4013076923076923</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>149</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="I23" s="13">
+        <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="16">
+        <f>IF($H$23="","",$F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>IF($H$23="","",MAX(0,($F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))/IF($H$23&lt;0,-100/$H$23,$H$23/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IF($H$23="","",ROUND(MIN($K$23,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IF($J$23="","",IF($J$23&lt;0,"Pass",IF($J$23&lt;'Settings'!$B$4,"Thin",IF($J$23&lt;0.06,"✅ Sharp band",IF($J$23&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.1% (fair +149). Your call.</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="16">
+        <f>IF(OR($H$23="",$O$23=""),"",(1+IF($H$23&lt;0,-100/$H$23,$H$23/100))/(1+IF($O$23&lt;0,-100/$O$23,$O$23/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>New York Mets @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.5113235294117646</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I24" s="13">
+        <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>IF($H$24="","",$F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>IF($H$24="","",MAX(0,($F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))/IF($H$24&lt;0,-100/$H$24,$H$24/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L24" s="18">
+        <f>IF($H$24="","",ROUND(MIN($K$24,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IF($J$24="","",IF($J$24&lt;0,"Pass",IF($J$24&lt;'Settings'!$B$4,"Thin",IF($J$24&lt;0.06,"✅ Sharp band",IF($J$24&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.1% (fair -105). Your call.</t>
+        </is>
+      </c>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="16">
+        <f>IF(OR($H$24="",$O$24=""),"",(1+IF($H$24&lt;0,-100/$H$24,$H$24/100))/(1+IF($O$24&lt;0,-100/$O$24,$O$24/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.5306549019607842</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.1% (fair -113). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.4465665236051502</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.7% (fair +124). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.5534441860465117</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I27" s="13">
+        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L27" s="18">
+        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.3% (fair -124). Your call.</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="16">
+        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.6264984375</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-156</v>
+      </c>
+      <c r="I28" s="13">
+        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.6% (fair -168). Your call.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16">
+        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.493125</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I29" s="13">
+        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.3% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16">
+        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J22">
+  <conditionalFormatting sqref="J5:J29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -8935,7 +9397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9475,10 +9937,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4346351931330472</v>
+        <v>0.4358798283261803</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>133</v>
@@ -9505,7 +9967,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9541,10 +10003,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5653356223175966</v>
+        <v>0.5641369098712447</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-133</v>
@@ -9571,7 +10033,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9607,7 +10069,7 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4656</v>
+        <v>0.4653</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>115</v>
@@ -9637,7 +10099,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9673,7 +10135,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5344</v>
+        <v>0.5347</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>-115</v>
@@ -9703,7 +10165,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9739,10 +10201,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4329644268774703</v>
+        <v>0.4259683794466403</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>153</v>
@@ -9769,7 +10231,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9805,10 +10267,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5670302325581396</v>
+        <v>0.5740372093023256</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-131</v>
+        <v>-135</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-115</v>
@@ -9835,7 +10297,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10465,13 +10927,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6829515418502202</v>
+        <v>0.6829410714285714</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>-215</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>127</v>
+        <v>-124</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10531,7 +10993,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4886036036036037</v>
+        <v>0.488963963963964</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>105</v>
@@ -10597,7 +11059,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5113558558558559</v>
+        <v>0.5110261261261261</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>-105</v>
@@ -10663,10 +11125,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5199</v>
+        <v>0.5082</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-108</v>
+        <v>-103</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>117</v>
@@ -10693,7 +11155,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10729,10 +11191,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4801</v>
+        <v>0.4918</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-105</v>
@@ -10759,7 +11221,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -10795,7 +11257,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3127376425855514</v>
+        <v>0.3129657794676806</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>220</v>
@@ -10861,7 +11323,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6872489082969432</v>
+        <v>0.6870235807860262</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-220</v>
@@ -10927,13 +11389,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4419574468085106</v>
+        <v>0.4465665236051502</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -10957,7 +11419,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -10993,13 +11455,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5580610169491526</v>
+        <v>0.5534043478260869</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-126</v>
+        <v>-124</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-136</v>
+        <v>-130</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11023,7 +11485,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11059,10 +11521,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.6323</v>
+        <v>0.6408</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-172</v>
+        <v>-178</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>113</v>
@@ -11089,7 +11551,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11125,10 +11587,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.3677</v>
+        <v>0.3592</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>105</v>
@@ -11155,7 +11617,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +172). Your call.</t>
+          <t>Model 35.9% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11191,13 +11653,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3960546875</v>
+        <v>0.4013076923076923</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11221,7 +11683,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +152). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11257,13 +11719,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6039241706161137</v>
+        <v>0.598694930875576</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-152</v>
+        <v>-149</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-111</v>
+        <v>-117</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11287,7 +11749,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -152). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11323,13 +11785,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.566520704845815</v>
+        <v>0.5632222222222222</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-131</v>
+        <v>-129</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11353,7 +11815,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11389,13 +11851,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4335111111111111</v>
+        <v>0.4368018018018018</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11419,7 +11881,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11461,7 +11923,7 @@
         <v>-102</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11527,7 +11989,7 @@
         <v>102</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -11587,13 +12049,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4878260869565217</v>
+        <v>0.4862980769230769</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -11617,7 +12079,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -11653,13 +12115,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5122043478260869</v>
+        <v>0.513675</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -11683,7 +12145,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -11715,7 +12177,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
@@ -11725,7 +12187,7 @@
         <v>120</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -11781,7 +12243,7 @@
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
@@ -11983,13 +12445,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.554752534562212</v>
+        <v>0.5534441860465117</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12013,7 +12475,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12049,10 +12511,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4452534562211982</v>
+        <v>0.4465437788018433</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>117</v>
@@ -12079,7 +12541,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12121,7 +12583,7 @@
         <v>111</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12247,10 +12709,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4335</v>
+        <v>0.4296</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13">
@@ -12275,7 +12737,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12311,10 +12773,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5665</v>
+        <v>0.5704</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-131</v>
+        <v>-133</v>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13">
@@ -12339,7 +12801,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12375,13 +12837,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5323732394366197</v>
+        <v>0.5321161137440759</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>-114</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12441,7 +12903,7 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4676303317535545</v>
+        <v>0.4679146919431278</v>
       </c>
       <c r="G56" s="14" t="n">
         <v>114</v>
@@ -12507,13 +12969,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4055</v>
+        <v>0.4727</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -12537,7 +12999,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +147). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -12573,13 +13035,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5945</v>
+        <v>0.5273</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-147</v>
+        <v>-112</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-101</v>
+        <v>115</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -12603,7 +13065,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -12639,10 +13101,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4536</v>
+        <v>0.451</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -12667,7 +13129,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -12703,10 +13165,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5464</v>
+        <v>0.549</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -12731,7 +13193,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -12901,7 +13363,7 @@
         <v>286</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -12967,7 +13429,7 @@
         <v>-286</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>-101</v>
+        <v>115</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -13027,10 +13489,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.406</v>
+        <v>0.3989</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13055,7 +13517,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13091,10 +13553,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.594</v>
+        <v>0.6011</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-146</v>
+        <v>-151</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13119,7 +13581,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13155,10 +13617,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5745945945945947</v>
+        <v>0.5710810810810811</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-135</v>
+        <v>-133</v>
       </c>
       <c r="H67" s="15" t="n">
         <v>122</v>
@@ -13185,7 +13647,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13221,10 +13683,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4254</v>
+        <v>0.4289</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -13249,7 +13711,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13285,7 +13747,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5026</v>
+        <v>0.5036</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>-101</v>
@@ -13315,7 +13777,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.4% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13351,7 +13813,7 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4974</v>
+        <v>0.4964</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>101</v>
@@ -13381,7 +13843,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 49.6% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13417,7 +13879,7 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.6264375000000001</v>
+        <v>0.6264984375</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>-168</v>
@@ -13483,7 +13945,7 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.3735546875</v>
+        <v>0.373515625</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>168</v>
@@ -13530,32 +13992,32 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4976712328767124</v>
+        <v>0.5354</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>101</v>
+        <v>-115</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -13579,7 +14041,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13596,32 +14058,32 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5023432432432432</v>
+        <v>0.4646</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-101</v>
+        <v>115</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-122</v>
+        <v>105</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -13645,7 +14107,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -13662,32 +14124,32 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4417226890756302</v>
+        <v>0.5067492957746479</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>126</v>
+        <v>-103</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>138</v>
+        <v>-113</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -13711,7 +14173,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -13728,32 +14190,32 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5583201680672268</v>
+        <v>0.493235294117647</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-126</v>
+        <v>103</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-138</v>
+        <v>104</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -13777,7 +14239,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -13794,12 +14256,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -13809,17 +14271,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4700460829493088</v>
+        <v>0.5002739726027396</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>113</v>
+        <v>-100</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -13843,7 +14305,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -13860,12 +14322,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -13875,17 +14337,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5299506912442397</v>
+        <v>0.4997054054054054</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-113</v>
+        <v>100</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -13909,7 +14371,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -13926,12 +14388,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -13941,17 +14403,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5133276995305164</v>
+        <v>0.4497863247863248</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-105</v>
+        <v>122</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-113</v>
+        <v>134</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -13975,7 +14437,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -13992,12 +14454,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -14007,17 +14469,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4866826923076923</v>
+        <v>0.5502315789473684</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>105</v>
+        <v>-122</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>108</v>
+        <v>-128</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14041,7 +14503,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14058,32 +14520,32 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4745098039215686</v>
+        <v>0.5114643564356435</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>111</v>
+        <v>-105</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>104</v>
+        <v>-102</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14107,7 +14569,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +111). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14124,32 +14586,32 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5254876777251185</v>
+        <v>0.4885294117647059</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-111</v>
+        <v>105</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-111</v>
+        <v>104</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14173,7 +14635,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14190,32 +14652,32 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4843627450980392</v>
+        <v>0.3952</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14239,7 +14701,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14256,32 +14718,32 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5156666666666667</v>
+        <v>0.60483536121673</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-106</v>
+        <v>-153</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-104</v>
+        <v>-163</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14305,7 +14767,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14322,12 +14784,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -14337,17 +14799,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.3444057971014493</v>
+        <v>0.4708450704225352</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14371,7 +14833,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +190). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14388,12 +14850,12 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -14403,17 +14865,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.6556057971014493</v>
+        <v>0.5291958525345622</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-190</v>
+        <v>-112</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-245</v>
+        <v>-117</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14437,7 +14899,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -190). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14446,9 +14908,1329 @@
         <v/>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>0.4886480769230769</v>
+      </c>
+      <c r="G87" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I87" s="13">
+        <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
+        <v/>
+      </c>
+      <c r="J87" s="16">
+        <f>IF($H$87="","",$F$87*IF($H$87&lt;0,-100/$H$87,$H$87/100)-(1-$F$87))</f>
+        <v/>
+      </c>
+      <c r="K87" s="17">
+        <f>IF($H$87="","",MAX(0,($F$87*IF($H$87&lt;0,-100/$H$87,$H$87/100)-(1-$F$87))/IF($H$87&lt;0,-100/$H$87,$H$87/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L87" s="18">
+        <f>IF($H$87="","",ROUND(MIN($K$87,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M87" s="12">
+        <f>IF($J$87="","",IF($J$87&lt;0,"Pass",IF($J$87&lt;'Settings'!$B$4,"Thin",IF($J$87&lt;0.06,"✅ Sharp band",IF($J$87&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N87" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.9% (fair +105). Your call.</t>
+        </is>
+      </c>
+      <c r="O87" s="15" t="n"/>
+      <c r="P87" s="16">
+        <f>IF(OR($H$87="",$O$87=""),"",(1+IF($H$87&lt;0,-100/$H$87,$H$87/100))/(1+IF($O$87&lt;0,-100/$O$87,$O$87/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>New York Mets @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E88" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>0.5113235294117646</v>
+      </c>
+      <c r="G88" s="14" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I88" s="13">
+        <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
+        <v/>
+      </c>
+      <c r="J88" s="16">
+        <f>IF($H$88="","",$F$88*IF($H$88&lt;0,-100/$H$88,$H$88/100)-(1-$F$88))</f>
+        <v/>
+      </c>
+      <c r="K88" s="17">
+        <f>IF($H$88="","",MAX(0,($F$88*IF($H$88&lt;0,-100/$H$88,$H$88/100)-(1-$F$88))/IF($H$88&lt;0,-100/$H$88,$H$88/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L88" s="18">
+        <f>IF($H$88="","",ROUND(MIN($K$88,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M88" s="12">
+        <f>IF($J$88="","",IF($J$88&lt;0,"Pass",IF($J$88&lt;'Settings'!$B$4,"Thin",IF($J$88&lt;0.06,"✅ Sharp band",IF($J$88&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N88" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.1% (fair -105). Your call.</t>
+        </is>
+      </c>
+      <c r="O88" s="15" t="n"/>
+      <c r="P88" s="16">
+        <f>IF(OR($H$88="",$O$88=""),"",(1+IF($H$88&lt;0,-100/$H$88,$H$88/100))/(1+IF($O$88&lt;0,-100/$O$88,$O$88/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves -1.5</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>0.3662222222222222</v>
+      </c>
+      <c r="G89" s="14" t="n">
+        <v>173</v>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="I89" s="13">
+        <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
+        <v/>
+      </c>
+      <c r="J89" s="16">
+        <f>IF($H$89="","",$F$89*IF($H$89&lt;0,-100/$H$89,$H$89/100)-(1-$F$89))</f>
+        <v/>
+      </c>
+      <c r="K89" s="17">
+        <f>IF($H$89="","",MAX(0,($F$89*IF($H$89&lt;0,-100/$H$89,$H$89/100)-(1-$F$89))/IF($H$89&lt;0,-100/$H$89,$H$89/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L89" s="18">
+        <f>IF($H$89="","",ROUND(MIN($K$89,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M89" s="12">
+        <f>IF($J$89="","",IF($J$89&lt;0,"Pass",IF($J$89&lt;'Settings'!$B$4,"Thin",IF($J$89&lt;0.06,"✅ Sharp band",IF($J$89&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N89" s="19" t="inlineStr">
+        <is>
+          <t>Model 36.6% (fair +173). Your call.</t>
+        </is>
+      </c>
+      <c r="O89" s="15" t="n"/>
+      <c r="P89" s="16">
+        <f>IF(OR($H$89="",$O$89=""),"",(1+IF($H$89&lt;0,-100/$H$89,$H$89/100))/(1+IF($O$89&lt;0,-100/$O$89,$O$89/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>New York Mets @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>New York Mets +1.5</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>0.6338035087719298</v>
+      </c>
+      <c r="G90" s="14" t="n">
+        <v>-173</v>
+      </c>
+      <c r="H90" s="15" t="n">
+        <v>-185</v>
+      </c>
+      <c r="I90" s="13">
+        <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
+        <v/>
+      </c>
+      <c r="J90" s="16">
+        <f>IF($H$90="","",$F$90*IF($H$90&lt;0,-100/$H$90,$H$90/100)-(1-$F$90))</f>
+        <v/>
+      </c>
+      <c r="K90" s="17">
+        <f>IF($H$90="","",MAX(0,($F$90*IF($H$90&lt;0,-100/$H$90,$H$90/100)-(1-$F$90))/IF($H$90&lt;0,-100/$H$90,$H$90/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L90" s="18">
+        <f>IF($H$90="","",ROUND(MIN($K$90,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M90" s="12">
+        <f>IF($J$90="","",IF($J$90&lt;0,"Pass",IF($J$90&lt;'Settings'!$B$4,"Thin",IF($J$90&lt;0.06,"✅ Sharp band",IF($J$90&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N90" s="19" t="inlineStr">
+        <is>
+          <t>Model 63.4% (fair -173). Your call.</t>
+        </is>
+      </c>
+      <c r="O90" s="15" t="n"/>
+      <c r="P90" s="16">
+        <f>IF(OR($H$90="",$O$90=""),"",(1+IF($H$90&lt;0,-100/$H$90,$H$90/100))/(1+IF($O$90&lt;0,-100/$O$90,$O$90/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>0.5068470588235293</v>
+      </c>
+      <c r="G91" s="14" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I91" s="13">
+        <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
+        <v/>
+      </c>
+      <c r="J91" s="16">
+        <f>IF($H$91="","",$F$91*IF($H$91&lt;0,-100/$H$91,$H$91/100)-(1-$F$91))</f>
+        <v/>
+      </c>
+      <c r="K91" s="17">
+        <f>IF($H$91="","",MAX(0,($F$91*IF($H$91&lt;0,-100/$H$91,$H$91/100)-(1-$F$91))/IF($H$91&lt;0,-100/$H$91,$H$91/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L91" s="18">
+        <f>IF($H$91="","",ROUND(MIN($K$91,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M91" s="12">
+        <f>IF($J$91="","",IF($J$91&lt;0,"Pass",IF($J$91&lt;'Settings'!$B$4,"Thin",IF($J$91&lt;0.06,"✅ Sharp band",IF($J$91&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N91" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.7% (fair -103). Your call.</t>
+        </is>
+      </c>
+      <c r="O91" s="15" t="n"/>
+      <c r="P91" s="16">
+        <f>IF(OR($H$91="",$O$91=""),"",(1+IF($H$91&lt;0,-100/$H$91,$H$91/100))/(1+IF($O$91&lt;0,-100/$O$91,$O$91/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D92" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>0.493125</v>
+      </c>
+      <c r="G92" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I92" s="13">
+        <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
+        <v/>
+      </c>
+      <c r="J92" s="16">
+        <f>IF($H$92="","",$F$92*IF($H$92&lt;0,-100/$H$92,$H$92/100)-(1-$F$92))</f>
+        <v/>
+      </c>
+      <c r="K92" s="17">
+        <f>IF($H$92="","",MAX(0,($F$92*IF($H$92&lt;0,-100/$H$92,$H$92/100)-(1-$F$92))/IF($H$92&lt;0,-100/$H$92,$H$92/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L92" s="18">
+        <f>IF($H$92="","",ROUND(MIN($K$92,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M92" s="12">
+        <f>IF($J$92="","",IF($J$92&lt;0,"Pass",IF($J$92&lt;'Settings'!$B$4,"Thin",IF($J$92&lt;0.06,"✅ Sharp band",IF($J$92&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N92" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.3% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O92" s="15" t="n"/>
+      <c r="P92" s="16">
+        <f>IF(OR($H$92="",$O$92=""),"",(1+IF($H$92&lt;0,-100/$H$92,$H$92/100))/(1+IF($O$92&lt;0,-100/$O$92,$O$92/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Over 8</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>0.5373067961165049</v>
+      </c>
+      <c r="G93" s="14" t="n">
+        <v>-116</v>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>-106</v>
+      </c>
+      <c r="I93" s="13">
+        <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
+        <v/>
+      </c>
+      <c r="J93" s="16">
+        <f>IF($H$93="","",$F$93*IF($H$93&lt;0,-100/$H$93,$H$93/100)-(1-$F$93))</f>
+        <v/>
+      </c>
+      <c r="K93" s="17">
+        <f>IF($H$93="","",MAX(0,($F$93*IF($H$93&lt;0,-100/$H$93,$H$93/100)-(1-$F$93))/IF($H$93&lt;0,-100/$H$93,$H$93/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L93" s="18">
+        <f>IF($H$93="","",ROUND(MIN($K$93,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M93" s="12">
+        <f>IF($J$93="","",IF($J$93&lt;0,"Pass",IF($J$93&lt;'Settings'!$B$4,"Thin",IF($J$93&lt;0.06,"✅ Sharp band",IF($J$93&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N93" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.7% (fair -116). Your call.</t>
+        </is>
+      </c>
+      <c r="O93" s="15" t="n"/>
+      <c r="P93" s="16">
+        <f>IF(OR($H$93="",$O$93=""),"",(1+IF($H$93&lt;0,-100/$H$93,$H$93/100))/(1+IF($O$93&lt;0,-100/$O$93,$O$93/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>Under 8</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>0.4626923076923077</v>
+      </c>
+      <c r="G94" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I94" s="13">
+        <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
+        <v/>
+      </c>
+      <c r="J94" s="16">
+        <f>IF($H$94="","",$F$94*IF($H$94&lt;0,-100/$H$94,$H$94/100)-(1-$F$94))</f>
+        <v/>
+      </c>
+      <c r="K94" s="17">
+        <f>IF($H$94="","",MAX(0,($F$94*IF($H$94&lt;0,-100/$H$94,$H$94/100)-(1-$F$94))/IF($H$94&lt;0,-100/$H$94,$H$94/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L94" s="18">
+        <f>IF($H$94="","",ROUND(MIN($K$94,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M94" s="12">
+        <f>IF($J$94="","",IF($J$94&lt;0,"Pass",IF($J$94&lt;'Settings'!$B$4,"Thin",IF($J$94&lt;0.06,"✅ Sharp band",IF($J$94&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N94" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.3% (fair +116). Your call.</t>
+        </is>
+      </c>
+      <c r="O94" s="15" t="n"/>
+      <c r="P94" s="16">
+        <f>IF(OR($H$94="",$O$94=""),"",(1+IF($H$94&lt;0,-100/$H$94,$H$94/100))/(1+IF($O$94&lt;0,-100/$O$94,$O$94/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals +1.5</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>0.6185942965779467</v>
+      </c>
+      <c r="G95" s="14" t="n">
+        <v>-162</v>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>-163</v>
+      </c>
+      <c r="I95" s="13">
+        <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
+        <v/>
+      </c>
+      <c r="J95" s="16">
+        <f>IF($H$95="","",$F$95*IF($H$95&lt;0,-100/$H$95,$H$95/100)-(1-$F$95))</f>
+        <v/>
+      </c>
+      <c r="K95" s="17">
+        <f>IF($H$95="","",MAX(0,($F$95*IF($H$95&lt;0,-100/$H$95,$H$95/100)-(1-$F$95))/IF($H$95&lt;0,-100/$H$95,$H$95/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L95" s="18">
+        <f>IF($H$95="","",ROUND(MIN($K$95,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M95" s="12">
+        <f>IF($J$95="","",IF($J$95&lt;0,"Pass",IF($J$95&lt;'Settings'!$B$4,"Thin",IF($J$95&lt;0.06,"✅ Sharp band",IF($J$95&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N95" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.9% (fair -162). Your call.</t>
+        </is>
+      </c>
+      <c r="O95" s="15" t="n"/>
+      <c r="P95" s="16">
+        <f>IF(OR($H$95="",$O$95=""),"",(1+IF($H$95&lt;0,-100/$H$95,$H$95/100))/(1+IF($O$95&lt;0,-100/$O$95,$O$95/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers -1.5</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="G96" s="14" t="n">
+        <v>162</v>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="I96" s="13">
+        <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
+        <v/>
+      </c>
+      <c r="J96" s="16">
+        <f>IF($H$96="","",$F$96*IF($H$96&lt;0,-100/$H$96,$H$96/100)-(1-$F$96))</f>
+        <v/>
+      </c>
+      <c r="K96" s="17">
+        <f>IF($H$96="","",MAX(0,($F$96*IF($H$96&lt;0,-100/$H$96,$H$96/100)-(1-$F$96))/IF($H$96&lt;0,-100/$H$96,$H$96/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L96" s="18">
+        <f>IF($H$96="","",ROUND(MIN($K$96,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M96" s="12">
+        <f>IF($J$96="","",IF($J$96&lt;0,"Pass",IF($J$96&lt;'Settings'!$B$4,"Thin",IF($J$96&lt;0.06,"✅ Sharp band",IF($J$96&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N96" s="19" t="inlineStr">
+        <is>
+          <t>Model 38.1% (fair +162). Your call.</t>
+        </is>
+      </c>
+      <c r="O96" s="15" t="n"/>
+      <c r="P96" s="16">
+        <f>IF(OR($H$96="",$O$96=""),"",(1+IF($H$96&lt;0,-100/$H$96,$H$96/100))/(1+IF($O$96&lt;0,-100/$O$96,$O$96/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>0.4712254901960785</v>
+      </c>
+      <c r="G97" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I97" s="13">
+        <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
+        <v/>
+      </c>
+      <c r="J97" s="16">
+        <f>IF($H$97="","",$F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))</f>
+        <v/>
+      </c>
+      <c r="K97" s="17">
+        <f>IF($H$97="","",MAX(0,($F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))/IF($H$97&lt;0,-100/$H$97,$H$97/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L97" s="18">
+        <f>IF($H$97="","",ROUND(MIN($K$97,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M97" s="12">
+        <f>IF($J$97="","",IF($J$97&lt;0,"Pass",IF($J$97&lt;'Settings'!$B$4,"Thin",IF($J$97&lt;0.06,"✅ Sharp band",IF($J$97&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N97" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.1% (fair +112). Your call.</t>
+        </is>
+      </c>
+      <c r="O97" s="15" t="n"/>
+      <c r="P97" s="16">
+        <f>IF(OR($H$97="",$O$97=""),"",(1+IF($H$97&lt;0,-100/$H$97,$H$97/100))/(1+IF($O$97&lt;0,-100/$O$97,$O$97/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>0.5287846153846153</v>
+      </c>
+      <c r="G98" s="14" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I98" s="13">
+        <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
+        <v/>
+      </c>
+      <c r="J98" s="16">
+        <f>IF($H$98="","",$F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF($H$98="","",MAX(0,($F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))/IF($H$98&lt;0,-100/$H$98,$H$98/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L98" s="18">
+        <f>IF($H$98="","",ROUND(MIN($K$98,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M98" s="12">
+        <f>IF($J$98="","",IF($J$98&lt;0,"Pass",IF($J$98&lt;'Settings'!$B$4,"Thin",IF($J$98&lt;0.06,"✅ Sharp band",IF($J$98&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N98" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.9% (fair -112). Your call.</t>
+        </is>
+      </c>
+      <c r="O98" s="15" t="n"/>
+      <c r="P98" s="16">
+        <f>IF(OR($H$98="",$O$98=""),"",(1+IF($H$98&lt;0,-100/$H$98,$H$98/100))/(1+IF($O$98&lt;0,-100/$O$98,$O$98/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>0.4693137254901961</v>
+      </c>
+      <c r="G99" s="14" t="n">
+        <v>113</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I99" s="13">
+        <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
+        <v/>
+      </c>
+      <c r="J99" s="16">
+        <f>IF($H$99="","",$F$99*IF($H$99&lt;0,-100/$H$99,$H$99/100)-(1-$F$99))</f>
+        <v/>
+      </c>
+      <c r="K99" s="17">
+        <f>IF($H$99="","",MAX(0,($F$99*IF($H$99&lt;0,-100/$H$99,$H$99/100)-(1-$F$99))/IF($H$99&lt;0,-100/$H$99,$H$99/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L99" s="18">
+        <f>IF($H$99="","",ROUND(MIN($K$99,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M99" s="12">
+        <f>IF($J$99="","",IF($J$99&lt;0,"Pass",IF($J$99&lt;'Settings'!$B$4,"Thin",IF($J$99&lt;0.06,"✅ Sharp band",IF($J$99&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N99" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.9% (fair +113). Your call.</t>
+        </is>
+      </c>
+      <c r="O99" s="15" t="n"/>
+      <c r="P99" s="16">
+        <f>IF(OR($H$99="",$O$99=""),"",(1+IF($H$99&lt;0,-100/$H$99,$H$99/100))/(1+IF($O$99&lt;0,-100/$O$99,$O$99/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>0.5306549019607842</v>
+      </c>
+      <c r="G100" s="14" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I100" s="13">
+        <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
+        <v/>
+      </c>
+      <c r="J100" s="16">
+        <f>IF($H$100="","",$F$100*IF($H$100&lt;0,-100/$H$100,$H$100/100)-(1-$F$100))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF($H$100="","",MAX(0,($F$100*IF($H$100&lt;0,-100/$H$100,$H$100/100)-(1-$F$100))/IF($H$100&lt;0,-100/$H$100,$H$100/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L100" s="18">
+        <f>IF($H$100="","",ROUND(MIN($K$100,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M100" s="12">
+        <f>IF($J$100="","",IF($J$100&lt;0,"Pass",IF($J$100&lt;'Settings'!$B$4,"Thin",IF($J$100&lt;0.06,"✅ Sharp band",IF($J$100&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N100" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.1% (fair -113). Your call.</t>
+        </is>
+      </c>
+      <c r="O100" s="15" t="n"/>
+      <c r="P100" s="16">
+        <f>IF(OR($H$100="",$O$100=""),"",(1+IF($H$100&lt;0,-100/$H$100,$H$100/100))/(1+IF($O$100&lt;0,-100/$O$100,$O$100/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Over 8</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>0.4690682926829268</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <v>113</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I101" s="13">
+        <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
+        <v/>
+      </c>
+      <c r="J101" s="16">
+        <f>IF($H$101="","",$F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF($H$101="","",MAX(0,($F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))/IF($H$101&lt;0,-100/$H$101,$H$101/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L101" s="18">
+        <f>IF($H$101="","",ROUND(MIN($K$101,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M101" s="12">
+        <f>IF($J$101="","",IF($J$101&lt;0,"Pass",IF($J$101&lt;'Settings'!$B$4,"Thin",IF($J$101&lt;0.06,"✅ Sharp band",IF($J$101&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N101" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.9% (fair +113). Your call.</t>
+        </is>
+      </c>
+      <c r="O101" s="15" t="n"/>
+      <c r="P101" s="16">
+        <f>IF(OR($H$101="",$O$101=""),"",(1+IF($H$101&lt;0,-100/$H$101,$H$101/100))/(1+IF($O$101&lt;0,-100/$O$101,$O$101/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>Under 8</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>0.5309</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I102" s="13">
+        <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
+        <v/>
+      </c>
+      <c r="J102" s="16">
+        <f>IF($H$102="","",$F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF($H$102="","",MAX(0,($F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))/IF($H$102&lt;0,-100/$H$102,$H$102/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L102" s="18">
+        <f>IF($H$102="","",ROUND(MIN($K$102,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M102" s="12">
+        <f>IF($J$102="","",IF($J$102&lt;0,"Pass",IF($J$102&lt;'Settings'!$B$4,"Thin",IF($J$102&lt;0.06,"✅ Sharp band",IF($J$102&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N102" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.1% (fair -113). Your call.</t>
+        </is>
+      </c>
+      <c r="O102" s="15" t="n"/>
+      <c r="P102" s="16">
+        <f>IF(OR($H$102="",$O$102=""),"",(1+IF($H$102&lt;0,-100/$H$102,$H$102/100))/(1+IF($O$102&lt;0,-100/$O$102,$O$102/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants -1.5</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>0.4127037037037037</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <v>142</v>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="I103" s="13">
+        <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
+        <v/>
+      </c>
+      <c r="J103" s="16">
+        <f>IF($H$103="","",$F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))</f>
+        <v/>
+      </c>
+      <c r="K103" s="17">
+        <f>IF($H$103="","",MAX(0,($F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))/IF($H$103&lt;0,-100/$H$103,$H$103/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L103" s="18">
+        <f>IF($H$103="","",ROUND(MIN($K$103,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M103" s="12">
+        <f>IF($J$103="","",IF($J$103&lt;0,"Pass",IF($J$103&lt;'Settings'!$B$4,"Thin",IF($J$103&lt;0.06,"✅ Sharp band",IF($J$103&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N103" s="19" t="inlineStr">
+        <is>
+          <t>Model 41.3% (fair +142). Your call.</t>
+        </is>
+      </c>
+      <c r="O103" s="15" t="n"/>
+      <c r="P103" s="16">
+        <f>IF(OR($H$103="",$O$103=""),"",(1+IF($H$103&lt;0,-100/$H$103,$H$103/100))/(1+IF($O$103&lt;0,-100/$O$103,$O$103/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays +1.5</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>0.5872834645669291</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>-142</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>154</v>
+      </c>
+      <c r="I104" s="13">
+        <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
+        <v/>
+      </c>
+      <c r="J104" s="16">
+        <f>IF($H$104="","",$F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))</f>
+        <v/>
+      </c>
+      <c r="K104" s="17">
+        <f>IF($H$104="","",MAX(0,($F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))/IF($H$104&lt;0,-100/$H$104,$H$104/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L104" s="18">
+        <f>IF($H$104="","",ROUND(MIN($K$104,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M104" s="12">
+        <f>IF($J$104="","",IF($J$104&lt;0,"Pass",IF($J$104&lt;'Settings'!$B$4,"Thin",IF($J$104&lt;0.06,"✅ Sharp band",IF($J$104&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N104" s="19" t="inlineStr">
+        <is>
+          <t>Model 58.7% (fair -142). Your call.</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="n"/>
+      <c r="P104" s="16">
+        <f>IF(OR($H$104="",$O$104=""),"",(1+IF($H$104&lt;0,-100/$H$104,$H$104/100))/(1+IF($O$104&lt;0,-100/$O$104,$O$104/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>0.3307536231884058</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>245</v>
+      </c>
+      <c r="I105" s="13">
+        <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
+        <v/>
+      </c>
+      <c r="J105" s="16">
+        <f>IF($H$105="","",$F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF($H$105="","",MAX(0,($F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))/IF($H$105&lt;0,-100/$H$105,$H$105/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L105" s="18">
+        <f>IF($H$105="","",ROUND(MIN($K$105,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M105" s="12">
+        <f>IF($J$105="","",IF($J$105&lt;0,"Pass",IF($J$105&lt;'Settings'!$B$4,"Thin",IF($J$105&lt;0.06,"✅ Sharp band",IF($J$105&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N105" s="19" t="inlineStr">
+        <is>
+          <t>Model 33.1% (fair +202). Your call.</t>
+        </is>
+      </c>
+      <c r="O105" s="15" t="n"/>
+      <c r="P105" s="16">
+        <f>IF(OR($H$105="",$O$105=""),"",(1+IF($H$105&lt;0,-100/$H$105,$H$105/100))/(1+IF($O$105&lt;0,-100/$O$105,$O$105/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>0.6692405797101449</v>
+      </c>
+      <c r="G106" s="14" t="n">
+        <v>-202</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>-245</v>
+      </c>
+      <c r="I106" s="13">
+        <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
+        <v/>
+      </c>
+      <c r="J106" s="16">
+        <f>IF($H$106="","",$F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))</f>
+        <v/>
+      </c>
+      <c r="K106" s="17">
+        <f>IF($H$106="","",MAX(0,($F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))/IF($H$106&lt;0,-100/$H$106,$H$106/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L106" s="18">
+        <f>IF($H$106="","",ROUND(MIN($K$106,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M106" s="12">
+        <f>IF($J$106="","",IF($J$106&lt;0,"Pass",IF($J$106&lt;'Settings'!$B$4,"Thin",IF($J$106&lt;0.06,"✅ Sharp band",IF($J$106&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N106" s="19" t="inlineStr">
+        <is>
+          <t>Model 66.9% (fair -202). Your call.</t>
+        </is>
+      </c>
+      <c r="O106" s="15" t="n"/>
+      <c r="P106" s="16">
+        <f>IF(OR($H$106="",$O$106=""),"",(1+IF($H$106&lt;0,-100/$H$106,$H$106/100))/(1+IF($O$106&lt;0,-100/$O$106,$O$106/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J86">
+  <conditionalFormatting sqref="J5:J106">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -399,7 +399,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10496550"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -519,7 +519,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10687050"/>
+    <ext cx="10125075" cy="10953750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 15:31</t>
+          <t>2026-07-05 17:01</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2989,249 +2989,174 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.618</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>5.233</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>4.792</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.826</v>
+        <v>4.618</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.233</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.6</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>7</v>
+        <v>4.833</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>7.896</v>
+        <v>4.792</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.109</v>
+        <v>7.826</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>0.667</v>
+        <v>8.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -3285,28 +3210,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.354</v>
+        <v>7.896</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.196</v>
+        <v>1.109</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>9.667</v>
+        <v>0.667</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -3360,315 +3285,315 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>7.708</v>
+        <v>1.354</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.196</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>7.708</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.867</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="35" t="inlineStr">
+      <c r="H75" s="35" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.367</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.447</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>5.195</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>7.533</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>4.461</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>8.438000000000001</v>
+        <v>5.195</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.533</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>4th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>4.85</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>8</v>
+        <v>4.267</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>8.651999999999999</v>
+        <v>4.461</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.104</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -3722,28 +3647,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>0.333</v>
+        <v>8</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.043</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.458</v>
+        <v>1.104</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -3797,75 +3722,150 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>9.333</v>
+        <v>0.333</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>7.739</v>
+        <v>1.043</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8.458</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>7.739</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.447</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J82" s="32" t="inlineStr">
+      <c r="J83" s="32" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.589</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7726,17 +7726,17 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6258052434456929</v>
+        <v>0.6973529411764706</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-167</v>
+        <v>-230</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -167). Your call.</t>
+          <t>Model 69.7% (fair -230). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7812,17 +7812,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6525390625</v>
+        <v>0.6258052434456929</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-188</v>
+        <v>-167</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7858,17 +7858,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -7878,17 +7878,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays +1.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5872834645669291</v>
+        <v>0.6525390625</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-142</v>
+        <v>-188</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6829410714285714</v>
+        <v>0.6903035714285713</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-215</v>
+        <v>-223</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-124</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 68.3% (fair -215). Your call.</t>
+          <t>Model 69.0% (fair -223). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3307536231884058</v>
+        <v>0.3507246376811594</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>245</v>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 33.1% (fair +202). Your call.</t>
+          <t>Model 35.1% (fair +185). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8188,17 +8188,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8208,17 +8208,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants -1.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4127037037037037</v>
+        <v>0.5986410138248848</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>142</v>
+        <v>-149</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>170</v>
+        <v>-117</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8254,37 +8254,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.598694930875576</v>
+        <v>0.5292307692307692</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-149</v>
+        <v>-112</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-117</v>
+        <v>108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8320,17 +8320,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8340,17 +8340,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5002739726027396</v>
+        <v>0.4854222222222223</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-100</v>
+        <v>106</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8391,32 +8391,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.488963963963964</v>
+        <v>0.4310671936758893</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8452,17 +8452,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8472,17 +8472,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4823555555555555</v>
+        <v>0.496986301369863</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8523,32 +8523,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4259683794466403</v>
+        <v>0.488963963963964</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8608,10 +8608,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5588480769230769</v>
+        <v>0.5573942307692307</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-108</v>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8674,10 +8674,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5740372093023256</v>
+        <v>0.5689558139534885</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-135</v>
+        <v>-132</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>-115</v>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8721,32 +8721,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5309</v>
+        <v>0.3586394557823129</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-113</v>
+        <v>179</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8806,10 +8806,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4497863247863248</v>
+        <v>0.4489316239316239</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>134</v>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8848,37 +8848,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5373067961165049</v>
+        <v>0.4013461538461539</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-116</v>
+        <v>149</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-106</v>
+        <v>160</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8914,37 +8914,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4013076923076923</v>
+        <v>0.5103921568627451</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>149</v>
+        <v>-104</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8980,37 +8980,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5113235294117646</v>
+        <v>0.4463519313304721</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-105</v>
+        <v>124</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9046,17 +9046,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9066,17 +9066,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5306549019607842</v>
+        <v>0.554193023255814</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-113</v>
+        <v>-124</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-104</v>
+        <v>-115</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9112,37 +9112,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4465665236051502</v>
+        <v>0.6413399239543726</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>124</v>
+        <v>-179</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>133</v>
+        <v>-163</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9178,37 +9178,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5534441860465117</v>
+        <v>0.51455</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-124</v>
+        <v>-106</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-115</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9315,32 +9315,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>San Francisco Giants +1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.493125</v>
+        <v>0.6457481481481482</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>103</v>
+        <v>-182</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>108</v>
+        <v>-170</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 64.6% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9397,7 +9397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P106"/>
+  <dimension ref="A1:P110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4358798283261803</v>
+        <v>0.4334763948497854</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>133</v>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5641369098712447</v>
+        <v>0.5664772532188841</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-129</v>
+        <v>-131</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-133</v>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4653</v>
+        <v>0.4688</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>119</v>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5347</v>
+        <v>0.5312</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4259683794466403</v>
+        <v>0.4310671936758893</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>153</v>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5740372093023256</v>
+        <v>0.5689558139534885</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-135</v>
+        <v>-132</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-115</v>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5588480769230769</v>
+        <v>0.5573942307692307</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-108</v>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4411538461538461</v>
+        <v>0.4426442307692308</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>108</v>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4227</v>
+        <v>0.4242</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>127</v>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10531,10 +10531,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5772999999999999</v>
+        <v>0.5758</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-137</v>
+        <v>-136</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>106</v>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10597,10 +10597,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4823555555555555</v>
+        <v>0.4854222222222223</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>125</v>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10663,10 +10663,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5176592920353983</v>
+        <v>0.5145929203539824</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-126</v>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5091</v>
+        <v>0.4924</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-104</v>
+        <v>103</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>122</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4909</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>104</v>
+        <v>-103</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>122</v>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3170342205323194</v>
+        <v>0.3096958174904943</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>163</v>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 31.7% (fair +215). Your call.</t>
+          <t>Model 31.0% (fair +223). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6829410714285714</v>
+        <v>0.6903035714285713</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-215</v>
+        <v>-223</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-124</v>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 68.3% (fair -215). Your call.</t>
+          <t>Model 69.0% (fair -223). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4465665236051502</v>
+        <v>0.4463519313304721</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>124</v>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5534043478260869</v>
+        <v>0.5536304347826088</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>-124</v>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.6408</v>
+        <v>0.629</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-178</v>
+        <v>-170</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>113</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -178). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.3592</v>
+        <v>0.371</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>105</v>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +178). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4013076923076923</v>
+        <v>0.4013461538461539</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>149</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.598694930875576</v>
+        <v>0.5986410138248848</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-149</v>
@@ -12049,13 +12049,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4862980769230769</v>
+        <v>0.4885507246376811</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12115,13 +12115,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.513675</v>
+        <v>0.5114242718446602</v>
       </c>
       <c r="G44" s="14" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H44" s="15" t="n">
         <v>-106</v>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-108</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12187,7 +12187,7 @@
         <v>120</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>105</v>
+        <v>-103</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12253,7 +12253,7 @@
         <v>-120</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5534441860465117</v>
+        <v>0.554193023255814</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>-124</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12511,13 +12511,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4465437788018433</v>
+        <v>0.4457798165137615</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>124</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12583,7 +12583,7 @@
         <v>111</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4296</v>
+        <v>0.4335</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5704</v>
+        <v>0.5665</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-133</v>
+        <v>-131</v>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12837,13 +12837,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5321161137440759</v>
+        <v>0.526551923076923</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-114</v>
+        <v>-111</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12903,13 +12903,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4679146919431278</v>
+        <v>0.4734134615384615</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12933,7 +12933,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12969,10 +12969,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4727</v>
+        <v>0.4055</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>133</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 40.6% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5273</v>
+        <v>0.5945</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-112</v>
+        <v>-147</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13101,10 +13101,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.451</v>
+        <v>0.4477</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13165,10 +13165,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.549</v>
+        <v>0.5523</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-122</v>
+        <v>-123</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13429,7 +13429,7 @@
         <v>-286</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -13489,10 +13489,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.3989</v>
+        <v>0.406</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.6011</v>
+        <v>0.594</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-151</v>
+        <v>-146</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14143,13 +14143,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5067492957746479</v>
+        <v>0.5032384615384615</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-103</v>
+        <v>-101</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.493235294117647</v>
+        <v>0.496764705882353</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>104</v>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14275,10 +14275,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5002739726027396</v>
+        <v>0.496986301369863</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-100</v>
+        <v>101</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>119</v>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14341,13 +14341,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4997054054054054</v>
+        <v>0.5030425925925925</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>100</v>
+        <v>-101</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-122</v>
+        <v>-116</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14388,32 +14388,32 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4497863247863248</v>
+        <v>0.5103921568627451</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14454,32 +14454,32 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5502315789473684</v>
+        <v>0.4896136150234742</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-122</v>
+        <v>104</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-128</v>
+        <v>-113</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14520,32 +14520,32 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5114643564356435</v>
+        <v>0.3026618705035971</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-105</v>
+        <v>230</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-102</v>
+        <v>178</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 30.3% (fair +230). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14586,32 +14586,32 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4885294117647059</v>
+        <v>0.6973529411764706</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>105</v>
+        <v>-230</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 69.7% (fair -230). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14662,22 +14662,22 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.3952</v>
+        <v>0.4489316239316239</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14728,22 +14728,22 @@
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.60483536121673</v>
+        <v>0.5510736842105264</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-153</v>
+        <v>-123</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-163</v>
+        <v>-128</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14784,32 +14784,32 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4708450704225352</v>
+        <v>0.5136356435643564</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>112</v>
+        <v>-106</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>113</v>
+        <v>-102</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14850,32 +14850,32 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5291958525345622</v>
+        <v>0.4863725490196078</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-112</v>
+        <v>106</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-117</v>
+        <v>104</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14916,32 +14916,32 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4886480769230769</v>
+        <v>0.39796</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-108</v>
+        <v>150</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14982,32 +14982,32 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5113235294117646</v>
+        <v>0.6020015625</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-105</v>
+        <v>-151</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>104</v>
+        <v>-156</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 60.2% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15058,22 +15058,22 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.3662222222222222</v>
+        <v>0.4708450704225352</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +173). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15124,22 +15124,22 @@
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.6338035087719298</v>
+        <v>0.5291958525345622</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-173</v>
+        <v>-112</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-185</v>
+        <v>-117</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -173). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15180,32 +15180,32 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5068470588235293</v>
+        <v>0.4854288461538461</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-103</v>
+        <v>106</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15246,32 +15246,32 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.493125</v>
+        <v>0.51455</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>103</v>
+        <v>-106</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15312,32 +15312,32 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5373067961165049</v>
+        <v>0.3682962962962962</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-116</v>
+        <v>172</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>-106</v>
+        <v>170</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15361,7 +15361,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15378,32 +15378,32 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4626923076923077</v>
+        <v>0.6317079136690648</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>116</v>
+        <v>-172</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>108</v>
+        <v>-178</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15454,22 +15454,22 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.6185942965779467</v>
+        <v>0.5087423076923077</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-162</v>
+        <v>-104</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>-163</v>
+        <v>-108</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15520,22 +15520,22 @@
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.3814</v>
+        <v>0.4912980769230769</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15576,32 +15576,32 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4712254901960785</v>
+        <v>0.5345</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>112</v>
+        <v>-115</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15642,32 +15642,32 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5287846153846153</v>
+        <v>0.4655</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-112</v>
+        <v>115</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-108</v>
+        <v>105</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15708,32 +15708,32 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4693137254901961</v>
+        <v>0.6413399239543726</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>113</v>
+        <v>-179</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>104</v>
+        <v>-163</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -15774,32 +15774,32 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5306549019607842</v>
+        <v>0.3586394557823129</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-113</v>
+        <v>179</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>-104</v>
+        <v>194</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -15840,32 +15840,32 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4690682926829268</v>
+        <v>0.4654326923076923</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>-105</v>
+        <v>108</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -15906,32 +15906,32 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5309</v>
+        <v>0.534588625592417</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>100</v>
+        <v>-111</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -15982,22 +15982,22 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants -1.5</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4127037037037037</v>
+        <v>0.4781862745098039</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16021,7 +16021,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16048,22 +16048,22 @@
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays +1.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5872834645669291</v>
+        <v>0.5217843137254902</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-142</v>
+        <v>-109</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>154</v>
+        <v>-104</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16104,32 +16104,32 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.3307536231884058</v>
+        <v>0.4707585365853659</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>245</v>
+        <v>-105</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 33.1% (fair +202). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16170,32 +16170,32 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.6692405797101449</v>
+        <v>0.5292307692307692</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-202</v>
+        <v>-112</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-245</v>
+        <v>108</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 66.9% (fair -202). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16228,9 +16228,273 @@
         <v/>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants +1.5</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>0.6457481481481482</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>-182</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>-170</v>
+      </c>
+      <c r="I107" s="13">
+        <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
+        <v/>
+      </c>
+      <c r="J107" s="16">
+        <f>IF($H$107="","",$F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))</f>
+        <v/>
+      </c>
+      <c r="K107" s="17">
+        <f>IF($H$107="","",MAX(0,($F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))/IF($H$107&lt;0,-100/$H$107,$H$107/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L107" s="18">
+        <f>IF($H$107="","",ROUND(MIN($K$107,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M107" s="12">
+        <f>IF($J$107="","",IF($J$107&lt;0,"Pass",IF($J$107&lt;'Settings'!$B$4,"Thin",IF($J$107&lt;0.06,"✅ Sharp band",IF($J$107&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N107" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.6% (fair -182). Your call.</t>
+        </is>
+      </c>
+      <c r="O107" s="15" t="n"/>
+      <c r="P107" s="16">
+        <f>IF(OR($H$107="",$O$107=""),"",(1+IF($H$107&lt;0,-100/$H$107,$H$107/100))/(1+IF($O$107&lt;0,-100/$O$107,$O$107/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays -1.5</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>0.3542205323193917</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>182</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>163</v>
+      </c>
+      <c r="I108" s="13">
+        <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
+        <v/>
+      </c>
+      <c r="J108" s="16">
+        <f>IF($H$108="","",$F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))</f>
+        <v/>
+      </c>
+      <c r="K108" s="17">
+        <f>IF($H$108="","",MAX(0,($F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))/IF($H$108&lt;0,-100/$H$108,$H$108/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L108" s="18">
+        <f>IF($H$108="","",ROUND(MIN($K$108,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M108" s="12">
+        <f>IF($J$108="","",IF($J$108&lt;0,"Pass",IF($J$108&lt;'Settings'!$B$4,"Thin",IF($J$108&lt;0.06,"✅ Sharp band",IF($J$108&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N108" s="19" t="inlineStr">
+        <is>
+          <t>Model 35.4% (fair +182). Your call.</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="n"/>
+      <c r="P108" s="16">
+        <f>IF(OR($H$108="",$O$108=""),"",(1+IF($H$108&lt;0,-100/$H$108,$H$108/100))/(1+IF($O$108&lt;0,-100/$O$108,$O$108/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>0.3507246376811594</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>185</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>245</v>
+      </c>
+      <c r="I109" s="13">
+        <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
+        <v/>
+      </c>
+      <c r="J109" s="16">
+        <f>IF($H$109="","",$F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF($H$109="","",MAX(0,($F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))/IF($H$109&lt;0,-100/$H$109,$H$109/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L109" s="18">
+        <f>IF($H$109="","",ROUND(MIN($K$109,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M109" s="12">
+        <f>IF($J$109="","",IF($J$109&lt;0,"Pass",IF($J$109&lt;'Settings'!$B$4,"Thin",IF($J$109&lt;0.06,"✅ Sharp band",IF($J$109&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N109" s="19" t="inlineStr">
+        <is>
+          <t>Model 35.1% (fair +185). Your call.</t>
+        </is>
+      </c>
+      <c r="O109" s="15" t="n"/>
+      <c r="P109" s="16">
+        <f>IF(OR($H$109="",$O$109=""),"",(1+IF($H$109&lt;0,-100/$H$109,$H$109/100))/(1+IF($O$109&lt;0,-100/$O$109,$O$109/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>0.6492855072463768</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>-245</v>
+      </c>
+      <c r="I110" s="13">
+        <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
+        <v/>
+      </c>
+      <c r="J110" s="16">
+        <f>IF($H$110="","",$F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF($H$110="","",MAX(0,($F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))/IF($H$110&lt;0,-100/$H$110,$H$110/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L110" s="18">
+        <f>IF($H$110="","",ROUND(MIN($K$110,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M110" s="12">
+        <f>IF($J$110="","",IF($J$110&lt;0,"Pass",IF($J$110&lt;'Settings'!$B$4,"Thin",IF($J$110&lt;0.06,"✅ Sharp band",IF($J$110&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N110" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.9% (fair -185). Your call.</t>
+        </is>
+      </c>
+      <c r="O110" s="15" t="n"/>
+      <c r="P110" s="16">
+        <f>IF(OR($H$110="",$O$110=""),"",(1+IF($H$110&lt;0,-100/$H$110,$H$110/100))/(1+IF($O$110&lt;0,-100/$O$110,$O$110/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J106">
+  <conditionalFormatting sqref="J5:J110">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -16334,28 +16598,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2491</v>
+        <v>0.2495</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4561</v>
+        <v>0.4565</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-2.42</v>
+        <v>-2.17</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-1.06</v>
+        <v>-0.95</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5147</v>
+        <v>0.5145999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -16365,28 +16629,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2504</v>
+        <v>0.2508</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4709</v>
+        <v>0.4712</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0.23</v>
+        <v>0.48</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>3.93</v>
+        <v>4.13</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5345</v>
+        <v>0.5341</v>
       </c>
     </row>
     <row r="7">
@@ -16469,7 +16733,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=299, ECE 0.050 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=302, ECE 0.055 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -16545,16 +16809,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>0.3712</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.5667</v>
+        <v>0.5806</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>0.1954</v>
+        <v>0.2094</v>
       </c>
     </row>
     <row r="20">
@@ -16564,16 +16828,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4588</v>
+        <v>0.4586</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4388</v>
+        <v>0.4343</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.02</v>
+        <v>-0.0243</v>
       </c>
     </row>
     <row r="21">
@@ -16583,16 +16847,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5419</v>
+        <v>0.542</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5268</v>
+        <v>0.5221</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0151</v>
+        <v>-0.0199</v>
       </c>
     </row>
     <row r="22">
@@ -17696,7 +17960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17713,320 +17977,170 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>5.085</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>5.125</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>8.811999999999999</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.188</v>
+        <v>5.085</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.433</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.5</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>3.5</v>
+        <v>4.733</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.56</v>
+        <v>5.125</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>9.708</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -18080,394 +18194,394 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>9.708</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.545</v>
       </c>
-      <c r="C73" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.267</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="H73" s="32" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="32" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="32" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.433</v>
       </c>
-      <c r="P73" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.41</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>5.275</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="32" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>4.768</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>1.26</v>
+        <v>5.275</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.2</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>4.9</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>1</v>
+        <v>5.567</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>0.896</v>
+        <v>4.768</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>7.98</v>
+        <v>8.52</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -18521,71 +18635,221 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>9.292</v>
+        <v>7.792</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="31" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>9.292</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.833</v>
       </c>
-      <c r="C81" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="D81" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="E81" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="F81" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="35" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K81" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L81" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M81" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="N81" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O81" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="P81" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.416</v>
       </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -399,7 +399,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -519,7 +519,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10534650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -549,7 +549,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10506075"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -579,7 +579,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="10677525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 17:01</t>
+          <t>2026-07-05 18:02</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2989,174 +2989,324 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.618</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.233</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>4.792</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>7.826</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>7.896</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.618</v>
+        <v>1.109</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.233</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.6</v>
+        <v>0.667</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.833</v>
+        <v>0.5</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.792</v>
+        <v>1.354</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.826</v>
+        <v>8.196</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>8.667</v>
+        <v>9.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -3210,390 +3360,390 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.896</v>
+        <v>7.708</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.109</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.15</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.354</v>
+        <v>0.447</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>8.196</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>7.708</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>5.195</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.461</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>8.438000000000001</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>5.195</v>
+        <v>1.104</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>7.533</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>4th</t>
+        <v>0.5</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.85</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>4.267</v>
+        <v>0.333</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.461</v>
+        <v>1.043</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.438000000000001</v>
+        <v>8.458</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -3647,225 +3797,75 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>8</v>
+        <v>9.333</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.651999999999999</v>
+        <v>7.739</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.104</v>
+        <v>0.447</v>
       </c>
       <c r="C81" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="D81" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.043</v>
+        <v>0.589</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>7.739</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3884,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3901,249 +3901,174 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C69" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E69" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F69" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G69" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H69" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I69" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J69" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K69" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L69" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M69" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N69" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O69" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P69" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q69" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>4.595</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="32" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>5.266</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>7.234</v>
+        <v>4.595</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.667</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>6.65</v>
       </c>
       <c r="O70" s="31" t="n">
-        <v>5</v>
+        <v>5.733</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>8.603999999999999</v>
+        <v>5.266</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.213</v>
+        <v>7.234</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -4197,28 +4122,28 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.25</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.426</v>
+        <v>1.213</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -4272,315 +4197,315 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8.208</v>
+        <v>1.25</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>8.426</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B74" s="31" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="C73" s="31" t="n">
+      <c r="C74" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D74" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E74" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F74" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G74" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K74" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L74" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M74" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N74" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O74" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="P73" s="31" t="n">
+      <c r="P74" s="31" t="n">
         <v>0.8159999999999999</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q74" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C77" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F77" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G77" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H77" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="29" t="inlineStr">
+      <c r="I77" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="29" t="inlineStr">
+      <c r="J77" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K77" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L77" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr">
+      <c r="M77" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="29" t="inlineStr">
+      <c r="N77" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="29" t="inlineStr">
+      <c r="O77" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="P77" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="29" t="inlineStr">
+      <c r="Q77" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>4.089</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H77" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>4.747</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>7.792</v>
+        <v>4.089</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.767</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H78" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>4.7</v>
       </c>
       <c r="O78" s="31" t="n">
-        <v>7</v>
+        <v>4.467</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>9.319000000000001</v>
+        <v>4.747</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>0.896</v>
+        <v>7.792</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -4634,28 +4559,28 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>1.17</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.021000000000001</v>
+        <v>0.896</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -4709,71 +4634,146 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>9.276999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="n">
+        <v>8.021000000000001</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P81" s="31" t="n">
+        <v>9.276999999999999</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n">
+      <c r="B82" s="31" t="n">
         <v>0.461</v>
       </c>
-      <c r="C81" s="31" t="n">
+      <c r="C82" s="31" t="n">
         <v>0.833</v>
       </c>
-      <c r="D81" s="31" t="n">
+      <c r="D82" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="E81" s="31" t="n">
+      <c r="E82" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="F81" s="31" t="n">
+      <c r="F82" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G82" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H81" s="33" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="K81" s="31" t="n">
+      <c r="K82" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="31" t="n">
+      <c r="L82" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M81" s="31" t="n">
+      <c r="M82" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="N81" s="31" t="n">
+      <c r="N82" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O81" s="31" t="n">
+      <c r="O82" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="P81" s="31" t="n">
+      <c r="P82" s="31" t="n">
         <v>0.513</v>
       </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4792,7 +4792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4809,174 +4809,249 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Houston Astros defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Houston Astros defense</t>
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>4.975</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.733</v>
+        <v>8.778</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G71" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.8</v>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.975</v>
+        <v>7.625</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.778</v>
+        <v>0.956</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -5030,28 +5105,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.625</v>
+        <v>1.292</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>0.956</v>
+        <v>7.244</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -5105,319 +5180,319 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.292</v>
+        <v>8.417</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>7.244</v>
+        <v>0.548</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.633</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J74" s="32" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.5</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>11</v>
+        <v>0.633</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>8.417</v>
+        <v>0.649</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Houston Astros offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>4.873</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I75" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J75" s="32" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Houston Astros offense vs Tampa Bay Rays defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>4.427</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>4.873</v>
+        <v>8.083</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
+        <v>8</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>3.5</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>3.867</v>
+        <v>12</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.427</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.083</v>
+        <v>1.417</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -5471,28 +5546,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.467000000000001</v>
+        <v>1.444</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.417</v>
+        <v>7.729</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -5546,146 +5621,71 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.444</v>
+        <v>7.778</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>7.729</v>
+        <v>0.701</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.767</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>0.4</v>
       </c>
       <c r="O82" s="31" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>7.778</v>
+        <v>0.507</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7750,13 +7750,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6973529411764706</v>
+        <v>0.6918148148148148</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-230</v>
+        <v>-224</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.7% (fair -230). Your call.</t>
+          <t>Model 69.2% (fair -224). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7812,17 +7812,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6258052434456929</v>
+        <v>0.6599609375</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-167</v>
+        <v>-194</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -167). Your call.</t>
+          <t>Model 66.0% (fair -194). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7863,12 +7863,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -7878,17 +7878,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6525390625</v>
+        <v>0.6215355805243445</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-188</v>
+        <v>-164</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 62.2% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7924,37 +7924,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5710810810810811</v>
+        <v>0.6312307692307692</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-133</v>
+        <v>-171</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7995,32 +7995,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6903035714285713</v>
+        <v>0.5710810810810811</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-223</v>
+        <v>-133</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-124</v>
+        <v>122</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 69.0% (fair -223). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8076,17 +8076,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6870235807860262</v>
+        <v>0.6950642857142858</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-220</v>
+        <v>-228</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-129</v>
+        <v>-124</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 68.7% (fair -220). Your call.</t>
+          <t>Model 69.5% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8122,37 +8122,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3507246376811594</v>
+        <v>0.6870235807860262</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>185</v>
+        <v>-220</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>245</v>
+        <v>-129</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 35.1% (fair +185). Your call.</t>
+          <t>Model 68.7% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8188,37 +8188,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5986410138248848</v>
+        <v>0.3507246376811594</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-149</v>
+        <v>185</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-117</v>
+        <v>245</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 35.1% (fair +185). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8325,32 +8325,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4854222222222223</v>
+        <v>0.4343083003952569</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8391,12 +8391,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8406,17 +8406,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4310671936758893</v>
+        <v>0.5913622119815668</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>132</v>
+        <v>-145</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>153</v>
+        <v>-117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8452,17 +8452,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8472,17 +8472,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.496986301369863</v>
+        <v>0.4869333333333333</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8584,17 +8584,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5573942307692307</v>
+        <v>0.5026291079812207</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-126</v>
+        <v>-101</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-108</v>
+        <v>113</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5689558139534885</v>
+        <v>0.5555769230769231</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-132</v>
+        <v>-125</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8716,17 +8716,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3586394557823129</v>
+        <v>0.4086538461538461</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +179). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8782,37 +8782,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4489316239316239</v>
+        <v>0.5656930232558141</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>123</v>
+        <v>-130</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>134</v>
+        <v>-115</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8848,37 +8848,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4013461538461539</v>
+        <v>0.5393414634146342</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>149</v>
+        <v>-117</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>160</v>
+        <v>-105</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -8934,17 +8934,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5103921568627451</v>
+        <v>0.5260574257425743</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-104</v>
+        <v>-111</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>104</v>
+        <v>-102</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4463519313304721</v>
+        <v>0.554193023255814</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>124</v>
+        <v>-124</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>133</v>
+        <v>-115</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9051,12 +9051,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9066,17 +9066,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.554193023255814</v>
+        <v>0.4446351931330472</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-124</v>
+        <v>125</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-115</v>
+        <v>133</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9117,32 +9117,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6413399239543726</v>
+        <v>0.4548017621145374</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-179</v>
+        <v>120</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-163</v>
+        <v>127</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9183,26 +9183,26 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.51455</v>
+        <v>0.51545</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>-106</v>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6264984375</v>
+        <v>0.62668125</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>-168</v>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -168). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9310,37 +9310,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants +1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.6457481481481482</v>
+        <v>0.51405</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-182</v>
+        <v>-106</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-170</v>
+        <v>100</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -182). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.51075</v>
+        <v>0.51405</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>100</v>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4892307692307692</v>
+        <v>0.4859134615384615</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>108</v>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3599</v>
+        <v>0.375</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>133</v>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 36.0% (fair +178). Your call.</t>
+          <t>Model 37.5% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6401</v>
+        <v>0.625</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-178</v>
+        <v>-167</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>-105</v>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 64.0% (fair -178). Your call.</t>
+          <t>Model 62.5% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3474642857142857</v>
+        <v>0.3400357142857143</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>180</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +188). Your call.</t>
+          <t>Model 34.0% (fair +194). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6525390625</v>
+        <v>0.6599609375</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-188</v>
+        <v>-194</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>156</v>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 66.0% (fair -194). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4334763948497854</v>
+        <v>0.4328755364806867</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>131</v>
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5664772532188841</v>
+        <v>0.5671622317596567</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-131</v>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4688</v>
+        <v>0.4895</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>119</v>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5312</v>
+        <v>0.5105</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-113</v>
+        <v>-104</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4310671936758893</v>
+        <v>0.4343083003952569</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>153</v>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5689558139534885</v>
+        <v>0.5656930232558141</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-132</v>
+        <v>-130</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-115</v>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5573942307692307</v>
+        <v>0.5555769230769231</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-108</v>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10399,10 +10399,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4426442307692308</v>
+        <v>0.4444230769230769</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>108</v>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4242</v>
+        <v>0.4173</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>127</v>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10531,10 +10531,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5758</v>
+        <v>0.5827</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-136</v>
+        <v>-140</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>106</v>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10597,10 +10597,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4854222222222223</v>
+        <v>0.4869333333333333</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>125</v>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10663,10 +10663,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5145929203539824</v>
+        <v>0.5130318584070797</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-126</v>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4924</v>
+        <v>0.4793</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>122</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5206999999999999</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-103</v>
+        <v>-109</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>122</v>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3096958174904943</v>
+        <v>0.3049429657794677</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>163</v>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 31.0% (fair +223). Your call.</t>
+          <t>Model 30.5% (fair +228). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6903035714285713</v>
+        <v>0.6950642857142858</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-223</v>
+        <v>-228</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-124</v>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 69.0% (fair -223). Your call.</t>
+          <t>Model 69.5% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11389,10 +11389,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4463519313304721</v>
+        <v>0.4446351931330472</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>133</v>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5536304347826088</v>
+        <v>0.5553826086956523</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-124</v>
+        <v>-125</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-130</v>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.629</v>
+        <v>0.6367</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-170</v>
+        <v>-175</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>113</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -170). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.371</v>
+        <v>0.3633</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>105</v>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +170). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4013461538461539</v>
+        <v>0.4086538461538461</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>160</v>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5986410138248848</v>
+        <v>0.5913622119815668</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-149</v>
+        <v>-145</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-117</v>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5632222222222222</v>
+        <v>0.5654444444444444</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>-125</v>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4368018018018018</v>
+        <v>0.4345945945945947</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>122</v>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5406</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>113</v>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11983,10 +11983,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4955000000000001</v>
+        <v>0.4594</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>115</v>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4885507246376811</v>
+        <v>0.4882125603864733</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>105</v>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5114242718446602</v>
+        <v>0.5117844660194175</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>-105</v>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4541</v>
+        <v>0.5006</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>120</v>
+        <v>-100</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>-103</v>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12247,10 +12247,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.4994</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-120</v>
+        <v>100</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>117</v>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12313,10 +12313,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3741851851851852</v>
+        <v>0.3784444444444444</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>170</v>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 37.4% (fair +167). Your call.</t>
+          <t>Model 37.8% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6258052434456929</v>
+        <v>0.6215355805243445</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-167</v>
+        <v>-164</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>167</v>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -167). Your call.</t>
+          <t>Model 62.2% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13101,10 +13101,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4477</v>
+        <v>0.4536</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13165,10 +13165,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5523</v>
+        <v>0.5464</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-123</v>
+        <v>-120</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4632</v>
+        <v>0.4656</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5344</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-116</v>
+        <v>-115</v>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.2592</v>
+        <v>0.263</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>133</v>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 25.9% (fair +286). Your call.</t>
+          <t>Model 26.3% (fair +280). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13423,10 +13423,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.7408</v>
+        <v>0.737</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-286</v>
+        <v>-280</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>113</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 74.1% (fair -286). Your call.</t>
+          <t>Model 73.7% (fair -280). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13489,10 +13489,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.406</v>
+        <v>0.4052</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.594</v>
+        <v>0.5948</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.6264984375</v>
+        <v>0.62668125</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>-168</v>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 62.6% (fair -168). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.373515625</v>
+        <v>0.3733203125</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>168</v>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 37.4% (fair +168). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5354</v>
+        <v>0.5285</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>108</v>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14077,10 +14077,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4646</v>
+        <v>0.4715</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>105</v>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14143,13 +14143,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5032384615384615</v>
+        <v>0.5056352112676057</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.496764705882353</v>
+        <v>0.4944117647058823</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>104</v>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14275,13 +14275,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.496986301369863</v>
+        <v>0.5026291079812207</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>101</v>
+        <v>-101</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14341,13 +14341,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5030425925925925</v>
+        <v>0.4973591549295774</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-101</v>
+        <v>101</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-116</v>
+        <v>-113</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14403,17 +14403,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5103921568627451</v>
+        <v>0.4871</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-104</v>
+        <v>105</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14469,17 +14469,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4896136150234742</v>
+        <v>0.5129</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>104</v>
+        <v>-105</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14539,13 +14539,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.3026618705035971</v>
+        <v>0.3082167832167831</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 30.3% (fair +230). Your call.</t>
+          <t>Model 30.8% (fair +224). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14605,13 +14605,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.6973529411764706</v>
+        <v>0.6918148148148148</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-230</v>
+        <v>-224</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 69.7% (fair -230). Your call.</t>
+          <t>Model 69.2% (fair -224). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14671,13 +14671,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4489316239316239</v>
+        <v>0.4548017621145374</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14737,13 +14737,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5510736842105264</v>
+        <v>0.545204845814978</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-123</v>
+        <v>-120</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-128</v>
+        <v>-127</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14803,10 +14803,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5136356435643564</v>
+        <v>0.5260574257425743</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-106</v>
+        <v>-111</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>-102</v>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4863725490196078</v>
+        <v>0.4739705882352941</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>104</v>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14935,10 +14935,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.39796</v>
+        <v>0.39688</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>150</v>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15001,13 +15001,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6020015625</v>
+        <v>0.6031</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 60.3% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15067,13 +15067,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4708450704225352</v>
+        <v>0.4715813953488373</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>112</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15133,7 +15133,7 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5291958525345622</v>
+        <v>0.5283870967741935</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>-112</v>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15199,10 +15199,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4854288461538461</v>
+        <v>0.4959173076923076</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>-108</v>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15265,10 +15265,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.51455</v>
+        <v>0.5041</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-106</v>
+        <v>-102</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>100</v>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3682962962962962</v>
+        <v>0.3687407407407408</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>170</v>
@@ -15361,7 +15361,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +172). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15397,13 +15397,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6317079136690648</v>
+        <v>0.6312307692307692</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-172</v>
+        <v>-171</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-178</v>
+        <v>160</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15463,7 +15463,7 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5087423076923077</v>
+        <v>0.510351923076923</v>
       </c>
       <c r="G95" s="14" t="n">
         <v>-104</v>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4912980769230769</v>
+        <v>0.4896153846153846</v>
       </c>
       <c r="G96" s="14" t="n">
         <v>104</v>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15591,17 +15591,17 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5345</v>
+        <v>0.5393414634146342</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>113</v>
+        <v>-105</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15657,17 +15657,17 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4655</v>
+        <v>0.4606572769953052</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.6413399239543726</v>
+        <v>0.6221889733840305</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-179</v>
+        <v>-165</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>-163</v>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -15793,13 +15793,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.3586394557823129</v>
+        <v>0.3777734375</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +179). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -15859,13 +15859,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4654326923076923</v>
+        <v>0.4705365853658537</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.1% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -15925,10 +15925,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.534588625592417</v>
+        <v>0.5294331753554502</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>-111</v>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.9% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -15991,13 +15991,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4781862745098039</v>
+        <v>0.48455</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16021,7 +16021,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16057,13 +16057,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5217843137254902</v>
+        <v>0.51545</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-109</v>
+        <v>-106</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16598,28 +16598,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2495</v>
+        <v>0.2497</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4565</v>
+        <v>0.4569</v>
       </c>
       <c r="F5" s="23" t="n">
         <v>-2.17</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-0.95</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5192</v>
       </c>
     </row>
     <row r="6">
@@ -16629,16 +16629,16 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2508</v>
+        <v>0.251</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4712</v>
+        <v>0.4715</v>
       </c>
       <c r="F6" s="23" t="n">
         <v>0.48</v>
@@ -16647,10 +16647,10 @@
         <v>0.25</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>4.13</v>
+        <v>4.21</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5341</v>
+        <v>0.5393</v>
       </c>
     </row>
     <row r="7">
@@ -16733,7 +16733,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=302, ECE 0.055 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=305, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -16828,16 +16828,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4586</v>
+        <v>0.4583</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4343</v>
+        <v>0.4356</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.0243</v>
+        <v>-0.0227</v>
       </c>
     </row>
     <row r="21">
@@ -16847,16 +16847,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.542</v>
+        <v>0.5419</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5221</v>
+        <v>0.5263</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0199</v>
+        <v>-0.0156</v>
       </c>
     </row>
     <row r="22">
@@ -17960,7 +17960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17977,170 +17977,320 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>5.085</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.433</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>8.811999999999999</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>5.085</v>
+        <v>1.188</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>3</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.5</v>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.733</v>
+        <v>3.5</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>5.125</v>
+        <v>1.56</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.811999999999999</v>
+        <v>9.708</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -18194,394 +18344,394 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>9.039999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.188</v>
+        <v>0.545</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.4</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="32" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>3.5</v>
+        <v>0.433</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.56</v>
+        <v>0.41</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>9.708</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J77" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>5.567</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.768</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="P74" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H75" s="32" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="32" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="P78" s="31" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>5.275</v>
+        <v>1.26</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J79" s="32" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>5.567</v>
+        <v>1</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.768</v>
+        <v>0.896</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.52</v>
+        <v>7.98</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -18635,221 +18785,71 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.792</v>
+        <v>9.292</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.26</v>
+        <v>0.833</v>
       </c>
       <c r="C81" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M81" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>0.896</v>
+        <v>0.416</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>9.292</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -399,7 +399,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10496550"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -519,7 +519,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10534650"/>
+    <ext cx="10125075" cy="10953750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -579,7 +579,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10677525"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -609,7 +609,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10506075"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 18:02</t>
+          <t>2026-07-05 19:06</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2989,324 +2989,174 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>4.618</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>5.233</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>4.792</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>7.826</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>7.896</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.109</v>
+        <v>4.618</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.233</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.6</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>0.5</v>
+        <v>4.833</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.354</v>
+        <v>4.792</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.196</v>
+        <v>7.826</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>9.667</v>
+        <v>8.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -3360,390 +3210,390 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.708</v>
+        <v>7.896</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.196</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>7.708</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="C73" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.867</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="35" t="inlineStr">
+      <c r="H75" s="35" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.367</v>
       </c>
-      <c r="P73" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.447</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>5.195</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>7.533</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>4.461</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>8.438000000000001</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>8.651999999999999</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>1.104</v>
+        <v>5.195</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.533</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>4th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>4.85</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>0.333</v>
+        <v>4.267</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>1.043</v>
+        <v>4.461</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.458</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -3797,75 +3647,225 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>9.333</v>
+        <v>8</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.739</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>0.447</v>
+        <v>1.104</v>
       </c>
       <c r="C81" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D81" s="31" t="n">
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="P81" s="31" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8.458</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>7.739</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="C83" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="E81" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="F81" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H81" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J81" s="32" t="inlineStr">
+      <c r="J83" s="32" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K81" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L81" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M81" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="N81" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="O81" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="P81" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.589</v>
       </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4792,7 +4792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4809,249 +4809,174 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Houston Astros defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>4.975</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>8.778</v>
+        <v>4.733</v>
       </c>
       <c r="C71" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G71" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.8</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>7.625</v>
+        <v>4.975</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>0.956</v>
+        <v>8.778</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -5105,28 +5030,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.292</v>
+        <v>7.625</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>7.244</v>
+        <v>0.956</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -5180,319 +5105,319 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.417</v>
+        <v>1.292</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.548</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.633</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J74" s="32" t="inlineStr">
+      <c r="J75" s="32" t="inlineStr">
         <is>
           <t>23rd</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.633</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.649</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Houston Astros offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>4.873</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>4.427</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>8.083</v>
+        <v>4.873</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.667</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>3.5</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>12</v>
+        <v>3.867</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>8.467000000000001</v>
+        <v>4.427</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.417</v>
+        <v>8.083</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -5546,28 +5471,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.444</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>7.729</v>
+        <v>1.417</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -5621,71 +5546,146 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>7.778</v>
+        <v>1.444</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.701</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.767</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.507</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5704,7 +5704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5721,245 +5721,170 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>Detroit Tigers offense vs Texas Rangers defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C69" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E69" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F69" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G69" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H69" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I69" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J69" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K69" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L69" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M69" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N69" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O69" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P69" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q69" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>4.289</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>4.155</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>7.755</v>
+        <v>4.289</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.033</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="O70" s="31" t="n">
-        <v>9</v>
+        <v>4.633</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>7.673</v>
+        <v>4.155</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.02</v>
+        <v>7.755</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>2.667</v>
+        <v>9.333</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -6013,28 +5938,28 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.163</v>
+        <v>7.673</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>7.333</v>
+        <v>2.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -6088,319 +6013,319 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8.571</v>
+        <v>1.163</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B74" s="31" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="C73" s="31" t="n">
+      <c r="C74" s="31" t="n">
         <v>0.633</v>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D74" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E74" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F74" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G74" s="31" t="n">
         <v>1.4</v>
       </c>
-      <c r="H73" s="35" t="inlineStr">
+      <c r="H74" s="35" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr">
+      <c r="I74" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J73" s="33" t="inlineStr">
+      <c r="J74" s="33" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K74" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L74" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M74" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N74" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O74" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="P73" s="31" t="n">
+      <c r="P74" s="31" t="n">
         <v>0.792</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q74" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>Texas Rangers offense vs Detroit Tigers defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C77" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F77" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G77" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H77" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="29" t="inlineStr">
+      <c r="I77" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="29" t="inlineStr">
+      <c r="J77" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K77" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L77" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr">
+      <c r="M77" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="29" t="inlineStr">
+      <c r="N77" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="29" t="inlineStr">
+      <c r="O77" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="P77" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="29" t="inlineStr">
+      <c r="Q77" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>4.233</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>3.987</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>7.816</v>
+        <v>4.167</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.233</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>3.55</v>
       </c>
       <c r="O78" s="31" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>7.592</v>
+        <v>3.987</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>1.041</v>
+        <v>7.816</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -6454,28 +6379,28 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>0.898</v>
+        <v>7.592</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.592000000000001</v>
+        <v>1.041</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -6529,71 +6454,146 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>7.333</v>
+        <v>1</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.776</v>
+        <v>0.898</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="n">
+        <v>8.592000000000001</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="P81" s="31" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n">
+      <c r="B82" s="31" t="n">
         <v>0.597</v>
       </c>
-      <c r="C81" s="31" t="n">
+      <c r="C82" s="31" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D81" s="31" t="n">
+      <c r="D82" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="E81" s="31" t="n">
+      <c r="E82" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="F81" s="31" t="n">
+      <c r="F82" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G82" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="32" t="inlineStr">
+      <c r="H82" s="32" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="K81" s="31" t="n">
+      <c r="K82" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L81" s="31" t="n">
+      <c r="L82" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="M81" s="31" t="n">
+      <c r="M82" s="31" t="n">
         <v>0.267</v>
       </c>
-      <c r="N81" s="31" t="n">
+      <c r="N82" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="O81" s="31" t="n">
+      <c r="O82" s="31" t="n">
         <v>0.233</v>
       </c>
-      <c r="P81" s="31" t="n">
+      <c r="P82" s="31" t="n">
         <v>0.355</v>
       </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7750,13 +7750,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6918148148148148</v>
+        <v>0.7047122302158272</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-224</v>
+        <v>-239</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.2% (fair -224). Your call.</t>
+          <t>Model 70.5% (fair -239). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6599609375</v>
+        <v>0.66453125</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-194</v>
+        <v>-198</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>156</v>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 66.5% (fair -198). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6215355805243445</v>
+        <v>0.615805243445693</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-164</v>
+        <v>-160</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>167</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -164). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7924,37 +7924,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6312307692307692</v>
+        <v>0.5695045045045045</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-171</v>
+        <v>-132</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7995,32 +7995,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5710810810810811</v>
+        <v>0.6950642857142858</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-133</v>
+        <v>-228</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>122</v>
+        <v>-124</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 69.5% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8076,17 +8076,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6950642857142858</v>
+        <v>0.6871362445414847</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-228</v>
+        <v>-220</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-124</v>
+        <v>-129</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -228). Your call.</t>
+          <t>Model 68.7% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8122,37 +8122,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6870235807860262</v>
+        <v>0.3507246376811594</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-220</v>
+        <v>185</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-129</v>
+        <v>245</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 68.7% (fair -220). Your call.</t>
+          <t>Model 35.1% (fair +185). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8193,32 +8193,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.3507246376811594</v>
+        <v>0.5292307692307692</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>185</v>
+        <v>-112</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>245</v>
+        <v>108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 35.1% (fair +185). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8254,37 +8254,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5292307692307692</v>
+        <v>0.4343083003952569</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-112</v>
+        <v>130</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8325,32 +8325,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4343083003952569</v>
+        <v>0.4869333333333333</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5913622119815668</v>
+        <v>0.5890437788018433</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-145</v>
+        <v>-143</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>-117</v>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8457,12 +8457,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8472,17 +8472,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4869333333333333</v>
+        <v>0.4887387387387388</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.488963963963964</v>
+        <v>0.5555769230769231</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>105</v>
+        <v>-125</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>122</v>
+        <v>-108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8584,37 +8584,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5026291079812207</v>
+        <v>0.4109615384615384</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-101</v>
+        <v>143</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8650,17 +8650,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5555769230769231</v>
+        <v>0.5111961722488039</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-125</v>
+        <v>-105</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-108</v>
+        <v>109</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4086538461538461</v>
+        <v>0.5656930232558141</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>145</v>
+        <v>-130</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>160</v>
+        <v>-115</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8782,37 +8782,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5656930232558141</v>
+        <v>0.538419512195122</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-130</v>
+        <v>-117</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8853,12 +8853,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -8868,17 +8868,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5393414634146342</v>
+        <v>0.5084466019417476</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-117</v>
+        <v>-103</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-105</v>
+        <v>106</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8914,37 +8914,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5260574257425743</v>
+        <v>0.5571883720930233</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-111</v>
+        <v>-126</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -8995,22 +8995,22 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.554193023255814</v>
+        <v>0.3841851851851852</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-124</v>
+        <v>160</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-115</v>
+        <v>170</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 38.4% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9046,37 +9046,37 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4446351931330472</v>
+        <v>0.5229772277227723</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>125</v>
+        <v>-110</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>133</v>
+        <v>-102</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9112,17 +9112,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9132,17 +9132,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4548017621145374</v>
+        <v>0.4437339055793991</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9178,17 +9178,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -9198,11 +9198,11 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.51545</v>
+        <v>0.5157</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>-106</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9249,12 +9249,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.62668125</v>
+        <v>0.51545</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-168</v>
+        <v>-106</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-156</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9310,17 +9310,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -9330,17 +9330,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.51405</v>
+        <v>0.6280828125</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-106</v>
+        <v>-169</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>100</v>
+        <v>-156</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.51405</v>
+        <v>0.5157</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-106</v>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4859134615384615</v>
+        <v>0.4842788461538462</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>106</v>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.375</v>
+        <v>0.3745</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>167</v>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.625</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>-167</v>
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3400357142857143</v>
+        <v>0.3354642857142858</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>180</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 34.0% (fair +194). Your call.</t>
+          <t>Model 33.5% (fair +198). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6599609375</v>
+        <v>0.66453125</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-194</v>
+        <v>-198</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>156</v>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 66.5% (fair -198). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10993,7 +10993,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.488963963963964</v>
+        <v>0.4887387387387388</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>105</v>
@@ -11059,7 +11059,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5110261261261261</v>
+        <v>0.5113009009009009</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>-105</v>
@@ -11125,10 +11125,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5082</v>
+        <v>0.5235</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-103</v>
+        <v>-110</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>117</v>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4918</v>
+        <v>0.4765</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-105</v>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3129657794676806</v>
+        <v>0.312851711026616</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>220</v>
@@ -11323,7 +11323,7 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6870235807860262</v>
+        <v>0.6871362445414847</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-220</v>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4446351931330472</v>
+        <v>0.4437339055793991</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>125</v>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5553826086956523</v>
+        <v>0.5562304347826087</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>-125</v>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.6367</v>
+        <v>0.6405</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-175</v>
+        <v>-178</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>113</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 64.0% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.3633</v>
+        <v>0.3595</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>105</v>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 36.0% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4086538461538461</v>
+        <v>0.4109615384615384</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>160</v>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5913622119815668</v>
+        <v>0.5890437788018433</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-145</v>
+        <v>-143</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-117</v>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5654444444444444</v>
+        <v>0.5643333333333334</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>-130</v>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11851,7 +11851,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4345945945945947</v>
+        <v>0.4356756756756757</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>130</v>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.6% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5406</v>
+        <v>0.5189</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>113</v>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11983,10 +11983,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4594</v>
+        <v>0.4811</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>115</v>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12049,10 +12049,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4882125603864733</v>
+        <v>0.4854106280193236</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>107</v>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5117844660194175</v>
+        <v>0.5146145631067961</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>-106</v>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.5006</v>
+        <v>0.4803</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-100</v>
+        <v>108</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>-103</v>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12247,10 +12247,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4994</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>117</v>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12313,10 +12313,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3784444444444444</v>
+        <v>0.3841851851851852</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>170</v>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +164). Your call.</t>
+          <t>Model 38.4% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6215355805243445</v>
+        <v>0.615805243445693</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-164</v>
+        <v>-160</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>167</v>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -164). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12445,10 +12445,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.554193023255814</v>
+        <v>0.5571883720930233</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-124</v>
+        <v>-126</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>-115</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4457798165137615</v>
+        <v>0.4427981651376148</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>118</v>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4739</v>
+        <v>0.5417</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>111</v>
+        <v>-118</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>105</v>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5261</v>
+        <v>0.4583</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-111</v>
+        <v>118</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>113</v>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13617,10 +13617,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5710810810810811</v>
+        <v>0.5695045045045045</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-133</v>
+        <v>-132</v>
       </c>
       <c r="H67" s="15" t="n">
         <v>122</v>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4289</v>
+        <v>0.4305</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5036</v>
+        <v>0.4854</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-101</v>
+        <v>106</v>
       </c>
       <c r="H69" s="15" t="n">
         <v>117</v>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -101). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -13813,10 +13813,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4964</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>101</v>
+        <v>-106</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>-105</v>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -13879,10 +13879,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.62668125</v>
+        <v>0.6280828125</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>-156</v>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13945,10 +13945,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.3733203125</v>
+        <v>0.3719140625</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H72" s="15" t="n">
         <v>156</v>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14011,13 +14011,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5285</v>
+        <v>0.5709</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-112</v>
+        <v>-133</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14077,13 +14077,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4715</v>
+        <v>0.4291</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14143,13 +14143,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5056352112676057</v>
+        <v>0.5004346153846153</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14209,13 +14209,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.4944117647058823</v>
+        <v>0.499609756097561</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14275,13 +14275,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5026291079812207</v>
+        <v>0.5111961722488039</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-101</v>
+        <v>-105</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14341,13 +14341,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4973591549295774</v>
+        <v>0.4887849056603774</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14403,17 +14403,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4871</v>
+        <v>0.5084466019417476</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>105</v>
+        <v>-103</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14469,14 +14469,14 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5129</v>
+        <v>0.4915557692307692</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-105</v>
+        <v>103</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>-108</v>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14539,10 +14539,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.3082167832167831</v>
+        <v>0.2953146853146853</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>186</v>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 30.8% (fair +224). Your call.</t>
+          <t>Model 29.5% (fair +239). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14605,13 +14605,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.6918148148148148</v>
+        <v>0.7047122302158272</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-224</v>
+        <v>-239</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 69.2% (fair -224). Your call.</t>
+          <t>Model 70.5% (fair -239). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14671,13 +14671,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4548017621145374</v>
+        <v>0.454</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>120</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.545204845814978</v>
+        <v>0.5459881057268723</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>-120</v>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14803,10 +14803,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5260574257425743</v>
+        <v>0.5229772277227723</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>-102</v>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4739705882352941</v>
+        <v>0.4770098039215686</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>104</v>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14935,13 +14935,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.39688</v>
+        <v>0.39359375</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15001,10 +15001,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6031</v>
+        <v>0.6063847908745248</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-152</v>
+        <v>-154</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>-163</v>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15067,13 +15067,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4715813953488373</v>
+        <v>0.4712442396313364</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>112</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15133,7 +15133,7 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5283870967741935</v>
+        <v>0.5287645161290322</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>-112</v>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15199,7 +15199,7 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4959173076923076</v>
+        <v>0.4960730769230769</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>102</v>
@@ -15265,13 +15265,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5041</v>
+        <v>0.5039303482587065</v>
       </c>
       <c r="G92" s="14" t="n">
         <v>-102</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3687407407407408</v>
+        <v>0.3685925925925926</v>
       </c>
       <c r="G93" s="14" t="n">
         <v>171</v>
@@ -15397,13 +15397,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6312307692307692</v>
+        <v>0.6314517985611511</v>
       </c>
       <c r="G94" s="14" t="n">
         <v>-171</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>160</v>
+        <v>-178</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15463,7 +15463,7 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.510351923076923</v>
+        <v>0.5101442307692308</v>
       </c>
       <c r="G95" s="14" t="n">
         <v>-104</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4896153846153846</v>
+        <v>0.4899038461538461</v>
       </c>
       <c r="G96" s="14" t="n">
         <v>104</v>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5393414634146342</v>
+        <v>0.538419512195122</v>
       </c>
       <c r="G97" s="14" t="n">
         <v>-117</v>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15661,7 +15661,7 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4606572769953052</v>
+        <v>0.4615962441314554</v>
       </c>
       <c r="G98" s="14" t="n">
         <v>117</v>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.6221889733840305</v>
+        <v>0.6213832699619771</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-165</v>
+        <v>-164</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>-163</v>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -15793,10 +15793,10 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.3777734375</v>
+        <v>0.3786328125</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H100" s="15" t="n">
         <v>156</v>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -15859,13 +15859,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4705365853658537</v>
+        <v>0.4681730769230769</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +113). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -15925,10 +15925,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5294331753554502</v>
+        <v>0.5318004739336492</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>-111</v>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -113). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -16255,10 +16255,10 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.6457481481481482</v>
+        <v>0.6439851851851851</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-182</v>
+        <v>-181</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>-170</v>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -182). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -16321,13 +16321,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.3542205323193917</v>
+        <v>0.356</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -16351,7 +16351,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +182). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -16598,28 +16598,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2497</v>
+        <v>0.2491</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4569</v>
+        <v>0.4615</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-2.17</v>
+        <v>-0.08</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
     </row>
     <row r="6">
@@ -16629,28 +16629,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.251</v>
+        <v>0.2504</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4715</v>
+        <v>0.4769</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0.48</v>
+        <v>2.57</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.25</v>
+        <v>1.32</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>4.21</v>
+        <v>4.84</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5393</v>
+        <v>0.5444</v>
       </c>
     </row>
     <row r="7">
@@ -16733,7 +16733,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=305, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=309, ECE 0.054 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -16828,16 +16828,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4583</v>
+        <v>0.4577</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4356</v>
+        <v>0.4231</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.0227</v>
+        <v>-0.0346</v>
       </c>
     </row>
     <row r="21">
@@ -16847,16 +16847,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5419</v>
+        <v>0.5417</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5263</v>
+        <v>0.5304</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0156</v>
+        <v>-0.0112</v>
       </c>
     </row>
     <row r="22">
@@ -17960,7 +17960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17977,320 +17977,170 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Pittsburgh Pirates offense vs Washington Nationals defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>5.085</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>5.125</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>8.811999999999999</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>1.188</v>
+        <v>5.085</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.433</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.5</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>3.5</v>
+        <v>4.733</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>1.56</v>
+        <v>5.125</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>9.708</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -18344,394 +18194,394 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>9.708</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.545</v>
       </c>
-      <c r="C73" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.267</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="H73" s="32" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="32" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="32" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.433</v>
       </c>
-      <c r="P73" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.41</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Washington Nationals offense vs Pittsburgh Pirates defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>5.275</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="32" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>5.567</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>4.768</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>1.26</v>
+        <v>5.275</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.2</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>4.9</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>1</v>
+        <v>5.567</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>0.896</v>
+        <v>4.768</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>7.98</v>
+        <v>8.52</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -18785,71 +18635,221 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>9.292</v>
+        <v>7.792</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="31" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>9.292</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.833</v>
       </c>
-      <c r="C81" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="D81" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="E81" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="F81" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="35" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K81" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L81" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M81" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="N81" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="O81" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="P81" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.416</v>
       </c>
-      <c r="Q81" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-05.xlsx
+++ b/data/output/workbook/2026-07-05.xlsx
@@ -339,7 +339,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -519,7 +519,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10534650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -549,7 +549,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10763250"/>
+    <ext cx="10125075" cy="10277475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05 19:06</t>
+          <t>2026-07-05 22:48</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2989,174 +2989,324 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals offense vs Chicago Cubs defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.618</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.233</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>4.792</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>7.826</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>7.896</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.618</v>
+        <v>1.109</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5.233</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.6</v>
+        <v>0.667</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4.833</v>
+        <v>0.5</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.792</v>
+        <v>1.354</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.826</v>
+        <v>8.196</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>8.667</v>
+        <v>9.667</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -3210,390 +3360,390 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.896</v>
+        <v>7.708</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.109</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.15</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>0.5</v>
+        <v>0.367</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.354</v>
+        <v>0.447</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>8.196</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>7.708</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs St. Louis Cardinals defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>5.195</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.461</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>8.438000000000001</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>5.195</v>
+        <v>1.104</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>7.533</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>4th</t>
+        <v>0.5</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.85</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>4.267</v>
+        <v>0.333</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>4.461</v>
+        <v>1.043</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.438000000000001</v>
+        <v>8.458</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -3647,225 +3797,75 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>8</v>
+        <v>9.333</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.651999999999999</v>
+        <v>7.739</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.104</v>
+        <v>0.447</v>
       </c>
       <c r="C81" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="D81" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H81" s="33" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.043</v>
+        <v>0.589</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>7.739</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="32" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3884,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3901,879 +3901,879 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D66" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F66" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G66" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H66" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I66" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J66" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K66" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L66" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M66" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N66" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O66" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P66" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q66" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="n">
+        <v>4.595</v>
+      </c>
+      <c r="C67" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="D67" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E67" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F67" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G67" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I67" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J67" s="32" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K67" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L67" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M67" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N67" s="31" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O67" s="31" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="P67" s="31" t="n">
+        <v>5.266</v>
+      </c>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>7.234</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P68" s="31" t="n">
+        <v>8.603999999999999</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>4.595</v>
+        <v>8.426</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="32" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>6.65</v>
+        <v>5</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>5.733</v>
+        <v>11.5</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>5.266</v>
+        <v>8.208</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B74" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E74" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F74" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G74" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H74" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I74" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J74" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K74" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L74" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M74" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N74" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O74" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P74" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q74" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>4.089</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H75" s="32" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O75" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>4.747</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B71" s="31" t="n">
-        <v>7.234</v>
-      </c>
-      <c r="C71" s="31" t="n">
+      <c r="B76" s="31" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="C76" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>8.603999999999999</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
+      <c r="D76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P76" s="31" t="n">
+        <v>9.319000000000001</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B72" s="31" t="n">
-        <v>1.213</v>
-      </c>
-      <c r="C72" s="31" t="n">
+      <c r="B77" s="31" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="P72" s="31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
+      <c r="P77" s="31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n">
-        <v>8.426</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P73" s="31" t="n">
-        <v>8.208</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>4.089</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>9</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>4.7</v>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>4.467</v>
+        <v>12</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>4.747</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>7.792</v>
+        <v>0.461</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.833</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>0.55</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>7</v>
+        <v>0.533</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>9.319000000000001</v>
+        <v>0.513</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="C80" s="31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" s="31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B81" s="31" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C81" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="P81" s="31" t="n">
-        <v>9.276999999999999</v>
-      </c>
-      <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D82" s="31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F82" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M82" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N82" s="31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7750,13 +7750,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7047122302158272</v>
+        <v>0.7076923076923076</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-239</v>
+        <v>-242</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 70.5% (fair -239). Your call.</t>
+          <t>Model 70.8% (fair -242). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.66453125</v>
+        <v>0.66953125</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-198</v>
+        <v>-203</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>156</v>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 66.5% (fair -198). Your call.</t>
+          <t>Model 67.0% (fair -203). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.615805243445693</v>
+        <v>0.6082022471910112</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-160</v>
+        <v>-155</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>167</v>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7924,37 +7924,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5695045045045045</v>
+        <v>0.5846007604562738</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-132</v>
+        <v>-141</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6950642857142858</v>
+        <v>0.6999357142857143</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-228</v>
+        <v>-233</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-124</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -228). Your call.</t>
+          <t>Model 70.0% (fair -233). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8061,32 +8061,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6871362445414847</v>
+        <v>0.5695045045045045</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-220</v>
+        <v>-132</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-129</v>
+        <v>122</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 68.7% (fair -220). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8122,37 +8122,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3507246376811594</v>
+        <v>0.6828550218340611</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>185</v>
+        <v>-215</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>245</v>
+        <v>-129</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 35.1% (fair +185). Your call.</t>
+          <t>Model 68.3% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8193,32 +8193,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>San Diego Padres -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5292307692307692</v>
+        <v>0.4154074074074073</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-112</v>
+        <v>141</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8254,37 +8254,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4343083003952569</v>
+        <v>0.3968705035971222</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8325,32 +8325,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4869333333333333</v>
+        <v>0.4358102766798418</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8391,32 +8391,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5890437788018433</v>
+        <v>0.4869333333333333</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-143</v>
+        <v>105</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-117</v>
+        <v>125</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8457,32 +8457,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4887387387387388</v>
+        <v>0.5890437788018433</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>105</v>
+        <v>-143</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>122</v>
+        <v>-117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5555769230769231</v>
+        <v>0.4896846846846847</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-125</v>
+        <v>104</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-108</v>
+        <v>122</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8589,32 +8589,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4109615384615384</v>
+        <v>0.5550057692307692</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>143</v>
+        <v>-125</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>160</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8650,37 +8650,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5111961722488039</v>
+        <v>0.4109615384615384</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-105</v>
+        <v>143</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8716,37 +8716,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5656930232558141</v>
+        <v>0.5110526315789474</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-130</v>
+        <v>-105</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-115</v>
+        <v>109</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8782,37 +8782,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.538419512195122</v>
+        <v>0.3918148148148148</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-117</v>
+        <v>155</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-105</v>
+        <v>170</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8848,37 +8848,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5084466019417476</v>
+        <v>0.5641953488372093</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-103</v>
+        <v>-129</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>106</v>
+        <v>-115</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8914,37 +8914,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5571883720930233</v>
+        <v>0.5484285714285714</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-126</v>
+        <v>-121</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8980,37 +8980,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros -1.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.3841851851851852</v>
+        <v>0.5346825242718446</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>160</v>
+        <v>-115</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>170</v>
+        <v>-106</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9046,37 +9046,37 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5229772277227723</v>
+        <v>0.5557976744186046</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-110</v>
+        <v>-125</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9112,17 +9112,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9132,17 +9132,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4437339055793991</v>
+        <v>0.51845</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>125</v>
+        <v>-108</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9178,37 +9178,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5157</v>
+        <v>0.5080882352941176</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-106</v>
+        <v>-103</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9244,17 +9244,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.51545</v>
+        <v>0.4437339055793991</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-106</v>
+        <v>125</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9315,32 +9315,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>San Francisco Giants +1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.6280828125</v>
+        <v>0.6505333333333332</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-169</v>
+        <v>-186</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-156</v>
+        <v>-170</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 65.1% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9397,7 +9397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P110"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5157</v>
+        <v>0.5159</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>100</v>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4842788461538462</v>
+        <v>0.4840865384615384</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>108</v>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3745</v>
+        <v>0.3484</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>133</v>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 34.8% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6516</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-167</v>
+        <v>-187</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>-105</v>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 65.2% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3354642857142858</v>
+        <v>0.3304642857142858</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>180</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 33.5% (fair +198). Your call.</t>
+          <t>Model 33.0% (fair +203). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9871,10 +9871,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.66453125</v>
+        <v>0.66953125</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-198</v>
+        <v>-203</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>156</v>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 66.5% (fair -198). Your call.</t>
+          <t>Model 67.0% (fair -203). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4328755364806867</v>
+        <v>0.4322317596566524</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>131</v>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5671622317596567</v>
+        <v>0.5677901287553648</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-131</v>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4895</v>
+        <v>0.4823</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>119</v>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5105</v>
+        <v>0.5177</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-104</v>
+        <v>-107</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4343083003952569</v>
+        <v>0.4358102766798418</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>153</v>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5656930232558141</v>
+        <v>0.5641953488372093</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-115</v>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5555769230769231</v>
+        <v>0.5550057692307692</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>-125</v>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10399,7 +10399,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4444230769230769</v>
+        <v>0.4449519230769231</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>125</v>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4173</v>
+        <v>0.4218</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>127</v>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10531,10 +10531,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5827</v>
+        <v>0.5782</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-140</v>
+        <v>-137</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>106</v>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5130318584070797</v>
+        <v>0.5130876106194691</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>-105</v>
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4793</v>
+        <v>0.4727</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>122</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5206999999999999</v>
+        <v>0.5273</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-109</v>
+        <v>-112</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>122</v>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3049429657794677</v>
+        <v>0.3000380228136882</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>163</v>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 30.5% (fair +228). Your call.</t>
+          <t>Model 30.0% (fair +233). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6950642857142858</v>
+        <v>0.6999357142857143</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-228</v>
+        <v>-233</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>-124</v>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -228). Your call.</t>
+          <t>Model 70.0% (fair -233). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4887387387387388</v>
+        <v>0.4896846846846847</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>122</v>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5113009009009009</v>
+        <v>0.5103117117117117</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-122</v>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11125,10 +11125,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5235</v>
+        <v>0.5565</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-110</v>
+        <v>-125</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>117</v>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4765</v>
+        <v>0.4435</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-105</v>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11257,10 +11257,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.312851711026616</v>
+        <v>0.317148288973384</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>163</v>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 31.3% (fair +220). Your call.</t>
+          <t>Model 31.7% (fair +215). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11323,10 +11323,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6871362445414847</v>
+        <v>0.6828550218340611</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-220</v>
+        <v>-215</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>-129</v>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 68.7% (fair -220). Your call.</t>
+          <t>Model 68.3% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5643333333333334</v>
+        <v>0.5636111111111111</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>-125</v>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -130). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4356756756756757</v>
+        <v>0.4363963963963964</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>122</v>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +130). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5189</v>
+        <v>0.4762</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-108</v>
+        <v>110</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>113</v>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11983,10 +11983,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4811</v>
+        <v>0.5238</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>108</v>
+        <v>-110</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>115</v>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12049,10 +12049,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4854106280193236</v>
+        <v>0.4796618357487922</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>107</v>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5146145631067961</v>
+        <v>0.5203262135922331</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-106</v>
+        <v>-108</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>-106</v>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4803</v>
+        <v>0.4299</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>-103</v>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12247,10 +12247,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-108</v>
+        <v>-133</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>117</v>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12313,10 +12313,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3841851851851852</v>
+        <v>0.3918148148148148</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>170</v>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.615805243445693</v>
+        <v>0.6082022471910112</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-160</v>
+        <v>-155</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>167</v>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12445,10 +12445,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.5571883720930233</v>
+        <v>0.5557976744186046</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>-115</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4427981651376148</v>
+        <v>0.4442201834862386</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>118</v>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5417</v>
+        <v>0.5326</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-118</v>
+        <v>-114</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>105</v>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4583</v>
+        <v>0.4674</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>113</v>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4335</v>
+        <v>0.4445</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5665</v>
+        <v>0.5555</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-131</v>
+        <v>-125</v>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.526551923076923</v>
+        <v>0.5283692307692308</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>-108</v>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4734134615384615</v>
+        <v>0.4715865384615384</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>108</v>
@@ -12933,7 +12933,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12969,10 +12969,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4055</v>
+        <v>0.4587</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>133</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +147). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13035,10 +13035,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5945</v>
+        <v>0.5413</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-147</v>
+        <v>-118</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>113</v>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13101,10 +13101,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4536</v>
+        <v>0.4448</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13165,10 +13165,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5464</v>
+        <v>0.5552</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4656</v>
+        <v>0.4573</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5344</v>
+        <v>0.5427</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-115</v>
+        <v>-119</v>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.263</v>
+        <v>0.2626</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>133</v>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 26.3% (fair +280). Your call.</t>
+          <t>Model 26.3% (fair +281). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13423,10 +13423,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.737</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-280</v>
+        <v>-281</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>113</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 73.7% (fair -280). Your call.</t>
+          <t>Model 73.7% (fair -281). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13489,10 +13489,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4052</v>
+        <v>0.4155</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5948</v>
+        <v>0.5845</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-147</v>
+        <v>-141</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13879,10 +13879,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.6280828125</v>
+        <v>0.6275343750000001</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-169</v>
+        <v>-168</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>-156</v>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 62.8% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.3719140625</v>
+        <v>0.3724615384615385</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 37.2% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5709</v>
+        <v>0.5282</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-133</v>
+        <v>-112</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>113</v>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14077,13 +14077,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4291</v>
+        <v>0.4718</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14143,13 +14143,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5004346153846153</v>
+        <v>0.49455</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-100</v>
+        <v>102</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14209,13 +14209,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.499609756097561</v>
+        <v>0.50545</v>
       </c>
       <c r="G76" s="14" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H76" s="15" t="n">
         <v>100</v>
-      </c>
-      <c r="H76" s="15" t="n">
-        <v>105</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5111961722488039</v>
+        <v>0.5110526315789474</v>
       </c>
       <c r="G77" s="14" t="n">
         <v>-105</v>
@@ -14341,13 +14341,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4887849056603774</v>
+        <v>0.4889260663507109</v>
       </c>
       <c r="G78" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14407,13 +14407,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5084466019417476</v>
+        <v>0.4880568720379146</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-103</v>
+        <v>105</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14473,13 +14473,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4915557692307692</v>
+        <v>0.5118953051643192</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>103</v>
+        <v>-105</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14539,13 +14539,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.2953146853146853</v>
+        <v>0.2922857142857143</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 29.5% (fair +239). Your call.</t>
+          <t>Model 29.2% (fair +242). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14605,13 +14605,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.7047122302158272</v>
+        <v>0.7076923076923076</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-239</v>
+        <v>-242</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 70.5% (fair -239). Your call.</t>
+          <t>Model 70.8% (fair -242). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14671,13 +14671,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.454</v>
+        <v>0.4577927927927928</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14737,13 +14737,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5459881057268723</v>
+        <v>0.5422405405405405</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14803,13 +14803,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5229772277227723</v>
+        <v>0.5132</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-102</v>
+        <v>101</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14869,13 +14869,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4770098039215686</v>
+        <v>0.4868</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14935,13 +14935,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.39359375</v>
+        <v>0.3924806201550387</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15001,10 +15001,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6063847908745248</v>
+        <v>0.6075003802281369</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-154</v>
+        <v>-155</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>-163</v>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15067,7 +15067,7 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4712442396313364</v>
+        <v>0.4716129032258065</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>112</v>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15133,7 +15133,7 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5287645161290322</v>
+        <v>0.5283870967741935</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>-112</v>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15199,10 +15199,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4960730769230769</v>
+        <v>0.5010576923076923</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>102</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>-108</v>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15265,13 +15265,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5039303482587065</v>
+        <v>0.4989705882352941</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3685925925925926</v>
+        <v>0.368037037037037</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>170</v>
@@ -15361,7 +15361,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15397,10 +15397,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6314517985611511</v>
+        <v>0.6319640287769784</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>-178</v>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15463,10 +15463,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5101442307692308</v>
+        <v>0.5076519230769231</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>-108</v>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15529,10 +15529,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4899038461538461</v>
+        <v>0.4923557692307692</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>108</v>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15591,17 +15591,17 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.538419512195122</v>
+        <v>0.5694</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-117</v>
+        <v>-132</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-105</v>
+        <v>117</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -117). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15657,17 +15657,17 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4615962441314554</v>
+        <v>0.4306</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +117). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15727,13 +15727,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.6213832699619771</v>
+        <v>0.61936875</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-164</v>
+        <v>-163</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 61.9% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -15793,13 +15793,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.3786328125</v>
+        <v>0.3806299212598425</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 38.1% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -15859,13 +15859,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4681730769230769</v>
+        <v>0.4653110047846891</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -15925,13 +15925,13 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5318004739336492</v>
+        <v>0.5346825242718446</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-111</v>
+        <v>-106</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -15972,32 +15972,32 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.48455</v>
+        <v>0.3396</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16021,7 +16021,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 34.0% (fair +194). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16038,32 +16038,32 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.51545</v>
+        <v>0.6604</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-106</v>
+        <v>-194</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 66.0% (fair -194). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16104,32 +16104,32 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>San Diego Padres -1.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4707585365853659</v>
+        <v>0.4154074074074073</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>-105</v>
+        <v>170</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16170,32 +16170,32 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5292307692307692</v>
+        <v>0.5846007604562738</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-112</v>
+        <v>-141</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16246,22 +16246,22 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants +1.5</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.6439851851851851</v>
+        <v>0.4815207920792079</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-181</v>
+        <v>108</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-170</v>
+        <v>-102</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -16312,22 +16312,22 @@
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays -1.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.356</v>
+        <v>0.51845</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>181</v>
+        <v>-108</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -16351,7 +16351,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -16368,32 +16368,32 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.3507246376811594</v>
+        <v>0.3843</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>245</v>
+        <v>117</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 35.1% (fair +185). Your call.</t>
+          <t>Model 38.4% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -16434,32 +16434,32 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C110" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.6492855072463768</v>
+        <v>0.6157</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-185</v>
+        <v>-160</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-245</v>
+        <v>108</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -16483,7 +16483,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 64.9% (fair -185). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -16492,9 +16492,537 @@
         <v/>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants +1.5</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>0.6505333333333332</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>-186</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>-170</v>
+      </c>
+      <c r="I111" s="13">
+        <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
+        <v/>
+      </c>
+      <c r="J111" s="16">
+        <f>IF($H$111="","",$F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF($H$111="","",MAX(0,($F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))/IF($H$111&lt;0,-100/$H$111,$H$111/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L111" s="18">
+        <f>IF($H$111="","",ROUND(MIN($K$111,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M111" s="12">
+        <f>IF($J$111="","",IF($J$111&lt;0,"Pass",IF($J$111&lt;'Settings'!$B$4,"Thin",IF($J$111&lt;0.06,"✅ Sharp band",IF($J$111&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N111" s="19" t="inlineStr">
+        <is>
+          <t>Model 65.1% (fair -186). Your call.</t>
+        </is>
+      </c>
+      <c r="O111" s="15" t="n"/>
+      <c r="P111" s="16">
+        <f>IF(OR($H$111="",$O$111=""),"",(1+IF($H$111&lt;0,-100/$H$111,$H$111/100))/(1+IF($O$111&lt;0,-100/$O$111,$O$111/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays -1.5</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>0.349467680608365</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>186</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>163</v>
+      </c>
+      <c r="I112" s="13">
+        <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
+        <v/>
+      </c>
+      <c r="J112" s="16">
+        <f>IF($H$112="","",$F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))</f>
+        <v/>
+      </c>
+      <c r="K112" s="17">
+        <f>IF($H$112="","",MAX(0,($F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))/IF($H$112&lt;0,-100/$H$112,$H$112/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L112" s="18">
+        <f>IF($H$112="","",ROUND(MIN($K$112,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M112" s="12">
+        <f>IF($J$112="","",IF($J$112&lt;0,"Pass",IF($J$112&lt;'Settings'!$B$4,"Thin",IF($J$112&lt;0.06,"✅ Sharp band",IF($J$112&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N112" s="19" t="inlineStr">
+        <is>
+          <t>Model 34.9% (fair +186). Your call.</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="n"/>
+      <c r="P112" s="16">
+        <f>IF(OR($H$112="",$O$112=""),"",(1+IF($H$112&lt;0,-100/$H$112,$H$112/100))/(1+IF($O$112&lt;0,-100/$O$112,$O$112/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>0.3968705035971222</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>178</v>
+      </c>
+      <c r="I113" s="13">
+        <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
+        <v/>
+      </c>
+      <c r="J113" s="16">
+        <f>IF($H$113="","",$F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF($H$113="","",MAX(0,($F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))/IF($H$113&lt;0,-100/$H$113,$H$113/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L113" s="18">
+        <f>IF($H$113="","",ROUND(MIN($K$113,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M113" s="12">
+        <f>IF($J$113="","",IF($J$113&lt;0,"Pass",IF($J$113&lt;'Settings'!$B$4,"Thin",IF($J$113&lt;0.06,"✅ Sharp band",IF($J$113&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N113" s="19" t="inlineStr">
+        <is>
+          <t>Model 39.7% (fair +152). Your call.</t>
+        </is>
+      </c>
+      <c r="O113" s="15" t="n"/>
+      <c r="P113" s="16">
+        <f>IF(OR($H$113="",$O$113=""),"",(1+IF($H$113&lt;0,-100/$H$113,$H$113/100))/(1+IF($O$113&lt;0,-100/$O$113,$O$113/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>0.6031510791366906</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <v>-152</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>-178</v>
+      </c>
+      <c r="I114" s="13">
+        <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
+        <v/>
+      </c>
+      <c r="J114" s="16">
+        <f>IF($H$114="","",$F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))</f>
+        <v/>
+      </c>
+      <c r="K114" s="17">
+        <f>IF($H$114="","",MAX(0,($F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))/IF($H$114&lt;0,-100/$H$114,$H$114/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L114" s="18">
+        <f>IF($H$114="","",ROUND(MIN($K$114,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M114" s="12">
+        <f>IF($J$114="","",IF($J$114&lt;0,"Pass",IF($J$114&lt;'Settings'!$B$4,"Thin",IF($J$114&lt;0.06,"✅ Sharp band",IF($J$114&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N114" s="19" t="inlineStr">
+        <is>
+          <t>Model 60.3% (fair -152). Your call.</t>
+        </is>
+      </c>
+      <c r="O114" s="15" t="n"/>
+      <c r="P114" s="16">
+        <f>IF(OR($H$114="",$O$114=""),"",(1+IF($H$114&lt;0,-100/$H$114,$H$114/100))/(1+IF($O$114&lt;0,-100/$O$114,$O$114/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Over 10.5</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>0.4919</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I115" s="13">
+        <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
+        <v/>
+      </c>
+      <c r="J115" s="16">
+        <f>IF($H$115="","",$F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))</f>
+        <v/>
+      </c>
+      <c r="K115" s="17">
+        <f>IF($H$115="","",MAX(0,($F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))/IF($H$115&lt;0,-100/$H$115,$H$115/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L115" s="18">
+        <f>IF($H$115="","",ROUND(MIN($K$115,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M115" s="12">
+        <f>IF($J$115="","",IF($J$115&lt;0,"Pass",IF($J$115&lt;'Settings'!$B$4,"Thin",IF($J$115&lt;0.06,"✅ Sharp band",IF($J$115&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N115" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.2% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O115" s="15" t="n"/>
+      <c r="P115" s="16">
+        <f>IF(OR($H$115="",$O$115=""),"",(1+IF($H$115&lt;0,-100/$H$115,$H$115/100))/(1+IF($O$115&lt;0,-100/$O$115,$O$115/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Under 10.5</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>0.5080882352941176</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I116" s="13">
+        <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
+        <v/>
+      </c>
+      <c r="J116" s="16">
+        <f>IF($H$116="","",$F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF($H$116="","",MAX(0,($F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))/IF($H$116&lt;0,-100/$H$116,$H$116/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L116" s="18">
+        <f>IF($H$116="","",ROUND(MIN($K$116,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M116" s="12">
+        <f>IF($J$116="","",IF($J$116&lt;0,"Pass",IF($J$116&lt;'Settings'!$B$4,"Thin",IF($J$116&lt;0.06,"✅ Sharp band",IF($J$116&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N116" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.8% (fair -103). Your call.</t>
+        </is>
+      </c>
+      <c r="O116" s="15" t="n"/>
+      <c r="P116" s="16">
+        <f>IF(OR($H$116="",$O$116=""),"",(1+IF($H$116&lt;0,-100/$H$116,$H$116/100))/(1+IF($O$116&lt;0,-100/$O$116,$O$116/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers -1.5</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>0.4515714285714286</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="I117" s="13">
+        <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
+        <v/>
+      </c>
+      <c r="J117" s="16">
+        <f>IF($H$117="","",$F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))</f>
+        <v/>
+      </c>
+      <c r="K117" s="17">
+        <f>IF($H$117="","",MAX(0,($F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))/IF($H$117&lt;0,-100/$H$117,$H$117/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L117" s="18">
+        <f>IF($H$117="","",ROUND(MIN($K$117,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M117" s="12">
+        <f>IF($J$117="","",IF($J$117&lt;0,"Pass",IF($J$117&lt;'Settings'!$B$4,"Thin",IF($J$117&lt;0.06,"✅ Sharp band",IF($J$117&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N117" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.2% (fair +121). Your call.</t>
+        </is>
+      </c>
+      <c r="O117" s="15" t="n"/>
+      <c r="P117" s="16">
+        <f>IF(OR($H$117="",$O$117=""),"",(1+IF($H$117&lt;0,-100/$H$117,$H$117/100))/(1+IF($O$117&lt;0,-100/$O$117,$O$117/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies +1.5</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>0.5484285714285714</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I118" s="13">
+        <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
+        <v/>
+      </c>
+      <c r="J118" s="16">
+        <f>IF($H$118="","",$F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>IF($H$118="","",MAX(0,($F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))/IF($H$118&lt;0,-100/$H$118,$H$118/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L118" s="18">
+        <f>IF($H$118="","",ROUND(MIN($K$118,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M118" s="12">
+        <f>IF($J$118="","",IF($J$118&lt;0,"Pass",IF($J$118&lt;'Settings'!$B$4,"Thin",IF($J$118&lt;0.06,"✅ Sharp band",IF($J$118&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N118" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.8% (fair -121). Your call.</t>
+        </is>
+      </c>
+      <c r="O118" s="15" t="n"/>
+      <c r="P118" s="16">
+        <f>IF(OR($H$118="",$O$118=""),"",(1+IF($H$118&lt;0,-100/$H$118,$H$118/100))/(1+IF($O$118&lt;0,-100/$O$118,$O$118/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J110">
+  <conditionalFormatting sqref="J5:J118">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -16598,10 +17126,10 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2491</v>
+        <v>0.2493</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>234</v>
@@ -16629,10 +17157,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2504</v>
+        <v>0.2505</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>195</v>
@@ -16733,7 +17261,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=309, ECE 0.054 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=313, ECE 0.054 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -16847,16 +17375,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5417</v>
+        <v>0.5423</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5304</v>
+        <v>0.5294</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0112</v>
+        <v>-0.0128</v>
       </c>
     </row>
     <row r="22">
@@ -17052,7 +17580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17069,245 +17597,170 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>New York Mets offense vs Atlanta Braves defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>3.827</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>3.767</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>3.803</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.306</v>
+        <v>3.827</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.767</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H71" s="32" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.55</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>7.312</v>
+        <v>3.803</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>0.9389999999999999</v>
+        <v>7.306</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -17361,28 +17814,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>1.25</v>
+        <v>8.5</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.062</v>
+        <v>7.312</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.407999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -17436,319 +17889,319 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>9.5</v>
+        <v>1.25</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.561999999999999</v>
+        <v>1.062</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.561999999999999</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.519</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.433</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.133</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="32" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.554</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Atlanta Braves offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>4.921</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>6.467</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>4.704</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>8.958</v>
+        <v>4.921</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.1</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>6.467</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>5.95</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>7.918</v>
+        <v>4.704</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.333</v>
+        <v>8.958</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>2</v>
+        <v>8.25</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -17802,28 +18255,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>0.918</v>
+        <v>7.918</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>7.688</v>
+        <v>1.333</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>6.25</v>
+        <v>2</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -17877,71 +18330,146 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>9.061</v>
+        <v>0.918</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.581</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="H82" s="35" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="35" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.633</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.506</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
